--- a/database/IRBR3.xlsx
+++ b/database/IRBR3.xlsx
@@ -452,16 +452,16 @@
         <v>42947</v>
       </c>
       <c r="B2" t="n">
-        <v>197.0598602294922</v>
+        <v>197.0598754882812</v>
       </c>
       <c r="C2" t="n">
-        <v>199.1455052304281</v>
+        <v>199.1455206507133</v>
       </c>
       <c r="D2" t="n">
-        <v>188.8518371039546</v>
+        <v>188.851851727178</v>
       </c>
       <c r="E2" t="n">
-        <v>190.130140835655</v>
+        <v>190.1301555578603</v>
       </c>
       <c r="F2" t="n">
         <v>1448107</v>
@@ -492,16 +492,16 @@
         <v>42949</v>
       </c>
       <c r="B4" t="n">
-        <v>198.1363372802734</v>
+        <v>198.1363220214844</v>
       </c>
       <c r="C4" t="n">
-        <v>198.3381726063799</v>
+        <v>198.3381573320472</v>
       </c>
       <c r="D4" t="n">
-        <v>195.7142999782507</v>
+        <v>195.7142849059865</v>
       </c>
       <c r="E4" t="n">
-        <v>197.7999450700959</v>
+        <v>197.799929837213</v>
       </c>
       <c r="F4" t="n">
         <v>146838</v>
@@ -512,16 +512,16 @@
         <v>42950</v>
       </c>
       <c r="B5" t="n">
-        <v>197.3962860107422</v>
+        <v>197.3962707519531</v>
       </c>
       <c r="C5" t="n">
-        <v>198.2036273625824</v>
+        <v>198.2036120413857</v>
       </c>
       <c r="D5" t="n">
-        <v>196.050703702263</v>
+        <v>196.0506885474878</v>
       </c>
       <c r="E5" t="n">
-        <v>196.7907666081165</v>
+        <v>196.7907513961343</v>
       </c>
       <c r="F5" t="n">
         <v>88032</v>
@@ -572,16 +572,16 @@
         <v>42955</v>
       </c>
       <c r="B8" t="n">
-        <v>189.3900909423828</v>
+        <v>189.3900756835938</v>
       </c>
       <c r="C8" t="n">
-        <v>193.6286596728857</v>
+        <v>193.6286440726034</v>
       </c>
       <c r="D8" t="n">
-        <v>188.4481793418572</v>
+        <v>188.4481641589561</v>
       </c>
       <c r="E8" t="n">
-        <v>193.6286596728857</v>
+        <v>193.6286440726034</v>
       </c>
       <c r="F8" t="n">
         <v>262129</v>
@@ -592,16 +592,16 @@
         <v>42956</v>
       </c>
       <c r="B9" t="n">
-        <v>186.6989593505859</v>
+        <v>186.6989440917969</v>
       </c>
       <c r="C9" t="n">
-        <v>190.399301184239</v>
+        <v>190.3992856230233</v>
       </c>
       <c r="D9" t="n">
-        <v>183.7386939169119</v>
+        <v>183.7386789000635</v>
       </c>
       <c r="E9" t="n">
-        <v>189.7265166285739</v>
+        <v>189.7265011223444</v>
       </c>
       <c r="F9" t="n">
         <v>202188</v>
@@ -612,16 +612,16 @@
         <v>42957</v>
       </c>
       <c r="B10" t="n">
-        <v>189.9955902099609</v>
+        <v>189.99560546875</v>
       </c>
       <c r="C10" t="n">
-        <v>191.1393237123501</v>
+        <v>191.1393390629938</v>
       </c>
       <c r="D10" t="n">
-        <v>185.5551863055493</v>
+        <v>185.5552012077239</v>
       </c>
       <c r="E10" t="n">
-        <v>186.2952491600364</v>
+        <v>186.2952641216464</v>
       </c>
       <c r="F10" t="n">
         <v>83768</v>
@@ -632,16 +632,16 @@
         <v>42958</v>
       </c>
       <c r="B11" t="n">
-        <v>191.0720520019531</v>
+        <v>191.0720672607422</v>
       </c>
       <c r="C11" t="n">
-        <v>192.1485204896907</v>
+        <v>192.1485358344453</v>
       </c>
       <c r="D11" t="n">
-        <v>188.3809008657267</v>
+        <v>188.3809159096037</v>
       </c>
       <c r="E11" t="n">
-        <v>191.1393304456402</v>
+        <v>191.139345709802</v>
       </c>
       <c r="F11" t="n">
         <v>48476</v>
@@ -652,16 +652,16 @@
         <v>42961</v>
       </c>
       <c r="B12" t="n">
-        <v>191.0720520019531</v>
+        <v>191.0720672607422</v>
       </c>
       <c r="C12" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812573853854</v>
       </c>
       <c r="D12" t="n">
-        <v>188.784571527849</v>
+        <v>188.7845866039625</v>
       </c>
       <c r="E12" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812573853854</v>
       </c>
       <c r="F12" t="n">
         <v>42790</v>
@@ -672,16 +672,16 @@
         <v>42962</v>
       </c>
       <c r="B13" t="n">
-        <v>191.0720520019531</v>
+        <v>191.0720672607422</v>
       </c>
       <c r="C13" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812573853854</v>
       </c>
       <c r="D13" t="n">
-        <v>190.4665460087698</v>
+        <v>190.4665612192039</v>
       </c>
       <c r="E13" t="n">
-        <v>192.0812420460037</v>
+        <v>192.0812573853854</v>
       </c>
       <c r="F13" t="n">
         <v>72604</v>
@@ -752,16 +752,16 @@
         <v>42968</v>
       </c>
       <c r="B17" t="n">
-        <v>192.5522003173828</v>
+        <v>192.5521850585938</v>
       </c>
       <c r="C17" t="n">
-        <v>193.0231494456094</v>
+        <v>193.0231341495</v>
       </c>
       <c r="D17" t="n">
-        <v>187.3044412937635</v>
+        <v>187.3044264508328</v>
       </c>
       <c r="E17" t="n">
-        <v>191.8121374015981</v>
+        <v>191.8121222014553</v>
       </c>
       <c r="F17" t="n">
         <v>257303</v>
@@ -812,16 +812,16 @@
         <v>42971</v>
       </c>
       <c r="B20" t="n">
-        <v>195.1087951660156</v>
+        <v>195.1087799072266</v>
       </c>
       <c r="C20" t="n">
-        <v>195.1087951660156</v>
+        <v>195.1087799072266</v>
       </c>
       <c r="D20" t="n">
-        <v>186.5643788351274</v>
+        <v>186.5643642445678</v>
       </c>
       <c r="E20" t="n">
-        <v>190.2647202006093</v>
+        <v>190.2647053206587</v>
       </c>
       <c r="F20" t="n">
         <v>496726</v>
@@ -832,16 +832,16 @@
         <v>42972</v>
       </c>
       <c r="B21" t="n">
-        <v>200.4911041259766</v>
+        <v>200.4910888671875</v>
       </c>
       <c r="C21" t="n">
-        <v>200.4911041259766</v>
+        <v>200.4910888671875</v>
       </c>
       <c r="D21" t="n">
-        <v>193.4941057093546</v>
+        <v>193.4940909830865</v>
       </c>
       <c r="E21" t="n">
-        <v>194.5705608247986</v>
+        <v>194.5705460166047</v>
       </c>
       <c r="F21" t="n">
         <v>198745</v>
@@ -852,16 +852,16 @@
         <v>42975</v>
       </c>
       <c r="B22" t="n">
-        <v>203.5186462402344</v>
+        <v>203.5186767578125</v>
       </c>
       <c r="C22" t="n">
-        <v>204.0568737591456</v>
+        <v>204.0569043574309</v>
       </c>
       <c r="D22" t="n">
-        <v>198.4727230842086</v>
+        <v>198.4727528451515</v>
       </c>
       <c r="E22" t="n">
-        <v>200.8947603080535</v>
+        <v>200.8947904321805</v>
       </c>
       <c r="F22" t="n">
         <v>228259</v>
@@ -872,16 +872,16 @@
         <v>42976</v>
       </c>
       <c r="B23" t="n">
-        <v>202.9804077148438</v>
+        <v>202.9804229736328</v>
       </c>
       <c r="C23" t="n">
-        <v>207.0171409315435</v>
+        <v>207.0171564937888</v>
       </c>
       <c r="D23" t="n">
-        <v>199.1455098201045</v>
+        <v>199.1455247906101</v>
       </c>
       <c r="E23" t="n">
-        <v>202.9804077148438</v>
+        <v>202.9804229736328</v>
       </c>
       <c r="F23" t="n">
         <v>110895</v>
@@ -912,16 +912,16 @@
         <v>42978</v>
       </c>
       <c r="B25" t="n">
-        <v>201.8366851806641</v>
+        <v>201.8367004394531</v>
       </c>
       <c r="C25" t="n">
-        <v>204.0568872315007</v>
+        <v>204.0569026581363</v>
       </c>
       <c r="D25" t="n">
-        <v>201.0293304602493</v>
+        <v>201.0293456580026</v>
       </c>
       <c r="E25" t="n">
-        <v>202.3749127351105</v>
+        <v>202.3749280345894</v>
       </c>
       <c r="F25" t="n">
         <v>24192</v>
@@ -932,16 +932,16 @@
         <v>42979</v>
       </c>
       <c r="B26" t="n">
-        <v>200.2219696044922</v>
+        <v>200.2220001220703</v>
       </c>
       <c r="C26" t="n">
-        <v>202.5094498765773</v>
+        <v>202.5094807428103</v>
       </c>
       <c r="D26" t="n">
-        <v>199.2800580873137</v>
+        <v>199.2800884613269</v>
       </c>
       <c r="E26" t="n">
-        <v>201.9039439368693</v>
+        <v>201.9039747108118</v>
       </c>
       <c r="F26" t="n">
         <v>102209</v>
@@ -952,16 +952,16 @@
         <v>42982</v>
       </c>
       <c r="B27" t="n">
-        <v>201.8366851806641</v>
+        <v>201.8367004394531</v>
       </c>
       <c r="C27" t="n">
-        <v>202.8458618452511</v>
+        <v>202.8458771803336</v>
       </c>
       <c r="D27" t="n">
-        <v>199.8183184627449</v>
+        <v>199.818333568946</v>
       </c>
       <c r="E27" t="n">
-        <v>200.4911029058029</v>
+        <v>200.4911180628663</v>
       </c>
       <c r="F27" t="n">
         <v>26931</v>
@@ -1012,16 +1012,16 @@
         <v>42986</v>
       </c>
       <c r="B30" t="n">
-        <v>211.9285125732422</v>
+        <v>211.9285278320312</v>
       </c>
       <c r="C30" t="n">
-        <v>213.8796007898036</v>
+        <v>213.8796161890705</v>
       </c>
       <c r="D30" t="n">
-        <v>208.4300067941503</v>
+        <v>208.430021801048</v>
       </c>
       <c r="E30" t="n">
-        <v>209.5737537026497</v>
+        <v>209.5737687918968</v>
       </c>
       <c r="F30" t="n">
         <v>291538</v>
@@ -1052,16 +1052,16 @@
         <v>42990</v>
       </c>
       <c r="B32" t="n">
-        <v>211.9285125732422</v>
+        <v>211.9285278320312</v>
       </c>
       <c r="C32" t="n">
-        <v>215.0906127518968</v>
+        <v>215.0906282383561</v>
       </c>
       <c r="D32" t="n">
-        <v>211.9285125732422</v>
+        <v>211.9285278320312</v>
       </c>
       <c r="E32" t="n">
-        <v>212.3321832272732</v>
+        <v>212.3321985151265</v>
       </c>
       <c r="F32" t="n">
         <v>116385</v>
@@ -1072,16 +1072,16 @@
         <v>42991</v>
       </c>
       <c r="B33" t="n">
-        <v>209.8428802490234</v>
+        <v>209.8428649902344</v>
       </c>
       <c r="C33" t="n">
-        <v>212.8031452809086</v>
+        <v>212.803129806863</v>
       </c>
       <c r="D33" t="n">
-        <v>208.564576378013</v>
+        <v>208.5645612121762</v>
       </c>
       <c r="E33" t="n">
-        <v>211.9958039236887</v>
+        <v>211.9957885083492</v>
       </c>
       <c r="F33" t="n">
         <v>61349</v>
@@ -1112,16 +1112,16 @@
         <v>42993</v>
       </c>
       <c r="B35" t="n">
-        <v>213.543212890625</v>
+        <v>213.5432281494141</v>
       </c>
       <c r="C35" t="n">
-        <v>213.6777697780194</v>
+        <v>213.6777850464233</v>
       </c>
       <c r="D35" t="n">
-        <v>209.3046307714664</v>
+        <v>209.3046457273865</v>
       </c>
       <c r="E35" t="n">
-        <v>209.3046307714664</v>
+        <v>209.3046457273865</v>
       </c>
       <c r="F35" t="n">
         <v>102613</v>
@@ -1132,16 +1132,16 @@
         <v>42996</v>
       </c>
       <c r="B36" t="n">
-        <v>211.9285125732422</v>
+        <v>211.9285278320312</v>
       </c>
       <c r="C36" t="n">
-        <v>215.9652458910421</v>
+        <v>215.9652614404748</v>
       </c>
       <c r="D36" t="n">
-        <v>210.6502087800658</v>
+        <v>210.6502239468174</v>
       </c>
       <c r="E36" t="n">
-        <v>213.9468792321422</v>
+        <v>213.946894636253</v>
       </c>
       <c r="F36" t="n">
         <v>190750</v>
@@ -1152,16 +1152,16 @@
         <v>42997</v>
       </c>
       <c r="B37" t="n">
-        <v>211.6594085693359</v>
+        <v>211.6593933105469</v>
       </c>
       <c r="C37" t="n">
-        <v>215.2924580119801</v>
+        <v>215.29244249128</v>
       </c>
       <c r="D37" t="n">
-        <v>210.3138262717391</v>
+        <v>210.3138111099548</v>
       </c>
       <c r="E37" t="n">
-        <v>211.9285223511062</v>
+        <v>211.9285070729164</v>
       </c>
       <c r="F37" t="n">
         <v>22405</v>
@@ -1192,16 +1192,16 @@
         <v>42999</v>
       </c>
       <c r="B39" t="n">
-        <v>211.9285125732422</v>
+        <v>211.9285278320312</v>
       </c>
       <c r="C39" t="n">
-        <v>212.6685754389658</v>
+        <v>212.6685907510391</v>
       </c>
       <c r="D39" t="n">
-        <v>209.1700696598739</v>
+        <v>209.1700847200559</v>
       </c>
       <c r="E39" t="n">
-        <v>210.7174872224043</v>
+        <v>210.7175023939999</v>
       </c>
       <c r="F39" t="n">
         <v>89480</v>
@@ -1212,16 +1212,16 @@
         <v>43000</v>
       </c>
       <c r="B40" t="n">
-        <v>214.5523681640625</v>
+        <v>214.5523986816406</v>
       </c>
       <c r="C40" t="n">
-        <v>214.6196466010548</v>
+        <v>214.6196771282025</v>
       </c>
       <c r="D40" t="n">
-        <v>210.448356730044</v>
+        <v>210.4483866638742</v>
       </c>
       <c r="E40" t="n">
-        <v>211.7266604216416</v>
+        <v>211.7266905372957</v>
       </c>
       <c r="F40" t="n">
         <v>36999</v>
@@ -1232,16 +1232,16 @@
         <v>43003</v>
       </c>
       <c r="B41" t="n">
-        <v>210.9193267822266</v>
+        <v>210.9193115234375</v>
       </c>
       <c r="C41" t="n">
-        <v>215.8979717814236</v>
+        <v>215.8979561624585</v>
       </c>
       <c r="D41" t="n">
-        <v>209.9774285705851</v>
+        <v>209.9774133799369</v>
       </c>
       <c r="E41" t="n">
-        <v>214.7542248499711</v>
+        <v>214.7542093137495</v>
       </c>
       <c r="F41" t="n">
         <v>77912</v>
@@ -1252,16 +1252,16 @@
         <v>43004</v>
       </c>
       <c r="B42" t="n">
-        <v>209.3046264648438</v>
+        <v>209.3046417236328</v>
       </c>
       <c r="C42" t="n">
-        <v>212.4667400310389</v>
+        <v>212.4667555203533</v>
       </c>
       <c r="D42" t="n">
-        <v>207.959057618586</v>
+        <v>207.95907277928</v>
       </c>
       <c r="E42" t="n">
-        <v>211.4575633963456</v>
+        <v>211.4575788120887</v>
       </c>
       <c r="F42" t="n">
         <v>43625</v>
@@ -1272,16 +1272,16 @@
         <v>43005</v>
       </c>
       <c r="B43" t="n">
-        <v>206.5461730957031</v>
+        <v>206.5461883544922</v>
       </c>
       <c r="C43" t="n">
-        <v>210.9865765532026</v>
+        <v>210.9865921400306</v>
       </c>
       <c r="D43" t="n">
-        <v>205.9406671847922</v>
+        <v>205.940682398849</v>
       </c>
       <c r="E43" t="n">
-        <v>209.9101216004721</v>
+        <v>209.910137107776</v>
       </c>
       <c r="F43" t="n">
         <v>41486</v>
@@ -1312,16 +1312,16 @@
         <v>43007</v>
       </c>
       <c r="B45" t="n">
-        <v>203.5186462402344</v>
+        <v>203.5186767578125</v>
       </c>
       <c r="C45" t="n">
-        <v>206.7480247424462</v>
+        <v>206.748055744269</v>
       </c>
       <c r="D45" t="n">
-        <v>199.6837483905032</v>
+        <v>199.6837783330391</v>
       </c>
       <c r="E45" t="n">
-        <v>206.7480247424462</v>
+        <v>206.748055744269</v>
       </c>
       <c r="F45" t="n">
         <v>174513</v>
@@ -1332,16 +1332,16 @@
         <v>43010</v>
       </c>
       <c r="B46" t="n">
-        <v>207.3535614013672</v>
+        <v>207.3535461425781</v>
       </c>
       <c r="C46" t="n">
-        <v>209.1700929353872</v>
+        <v>209.1700775429227</v>
       </c>
       <c r="D46" t="n">
-        <v>203.5186763725986</v>
+        <v>203.5186613960121</v>
       </c>
       <c r="E46" t="n">
-        <v>204.2587393206731</v>
+        <v>204.2587242896267</v>
       </c>
       <c r="F46" t="n">
         <v>97827</v>
@@ -1372,16 +1372,16 @@
         <v>43012</v>
       </c>
       <c r="B48" t="n">
-        <v>206.8825988769531</v>
+        <v>206.8826293945312</v>
       </c>
       <c r="C48" t="n">
-        <v>208.564573402578</v>
+        <v>208.5646041682669</v>
       </c>
       <c r="D48" t="n">
-        <v>204.1914476692005</v>
+        <v>204.1914777898027</v>
       </c>
       <c r="E48" t="n">
-        <v>208.564573402578</v>
+        <v>208.5646041682669</v>
       </c>
       <c r="F48" t="n">
         <v>147256</v>
@@ -1392,16 +1392,16 @@
         <v>43013</v>
       </c>
       <c r="B49" t="n">
-        <v>204.1241455078125</v>
+        <v>204.1241607666016</v>
       </c>
       <c r="C49" t="n">
-        <v>207.8917647941771</v>
+        <v>207.8917803346051</v>
       </c>
       <c r="D49" t="n">
-        <v>202.9803986788739</v>
+        <v>202.980413852165</v>
       </c>
       <c r="E49" t="n">
-        <v>207.3535239041652</v>
+        <v>207.3535394043583</v>
       </c>
       <c r="F49" t="n">
         <v>185260</v>
@@ -1452,16 +1452,16 @@
         <v>43018</v>
       </c>
       <c r="B52" t="n">
-        <v>206.8825988769531</v>
+        <v>206.8826293945312</v>
       </c>
       <c r="C52" t="n">
-        <v>208.564573402578</v>
+        <v>208.5646041682669</v>
       </c>
       <c r="D52" t="n">
-        <v>204.1914476692005</v>
+        <v>204.1914777898027</v>
       </c>
       <c r="E52" t="n">
-        <v>207.5553967204503</v>
+        <v>207.5554273372739</v>
       </c>
       <c r="F52" t="n">
         <v>108639</v>
@@ -1492,16 +1492,16 @@
         <v>43021</v>
       </c>
       <c r="B54" t="n">
-        <v>211.0538635253906</v>
+        <v>211.0538787841797</v>
       </c>
       <c r="C54" t="n">
-        <v>213.0722300321513</v>
+        <v>213.0722454368643</v>
       </c>
       <c r="D54" t="n">
-        <v>210.2465222781839</v>
+        <v>210.2465374786037</v>
       </c>
       <c r="E54" t="n">
-        <v>210.2465222781839</v>
+        <v>210.2465374786037</v>
       </c>
       <c r="F54" t="n">
         <v>88189</v>
@@ -1532,16 +1532,16 @@
         <v>43025</v>
       </c>
       <c r="B56" t="n">
-        <v>213.2740631103516</v>
+        <v>213.2740936279297</v>
       </c>
       <c r="C56" t="n">
-        <v>215.1578727228487</v>
+        <v>215.1579035099829</v>
       </c>
       <c r="D56" t="n">
-        <v>212.1303296887869</v>
+        <v>212.1303600427072</v>
       </c>
       <c r="E56" t="n">
-        <v>214.1486961744093</v>
+        <v>214.1487268171395</v>
       </c>
       <c r="F56" t="n">
         <v>68039</v>
@@ -1552,16 +1552,16 @@
         <v>43026</v>
       </c>
       <c r="B57" t="n">
-        <v>215.6288604736328</v>
+        <v>215.6288452148438</v>
       </c>
       <c r="C57" t="n">
-        <v>215.6288604736328</v>
+        <v>215.6288452148438</v>
       </c>
       <c r="D57" t="n">
-        <v>211.9957976953891</v>
+        <v>211.9957826936906</v>
       </c>
       <c r="E57" t="n">
-        <v>214.6196704180117</v>
+        <v>214.6196552306371</v>
       </c>
       <c r="F57" t="n">
         <v>93014</v>
@@ -1572,16 +1572,16 @@
         <v>43027</v>
       </c>
       <c r="B58" t="n">
-        <v>219.5983123779297</v>
+        <v>219.5983276367188</v>
       </c>
       <c r="C58" t="n">
-        <v>220.8766028046159</v>
+        <v>220.8766181522269</v>
       </c>
       <c r="D58" t="n">
-        <v>212.6013006979307</v>
+        <v>212.6013154705325</v>
       </c>
       <c r="E58" t="n">
-        <v>213.0722498024993</v>
+        <v>213.0722646078249</v>
       </c>
       <c r="F58" t="n">
         <v>143656</v>
@@ -1632,16 +1632,16 @@
         <v>43032</v>
       </c>
       <c r="B61" t="n">
-        <v>219.5983123779297</v>
+        <v>219.5983276367188</v>
       </c>
       <c r="C61" t="n">
-        <v>223.8368810965369</v>
+        <v>223.836896649843</v>
       </c>
       <c r="D61" t="n">
-        <v>218.7236792235573</v>
+        <v>218.7236944215725</v>
       </c>
       <c r="E61" t="n">
-        <v>221.4148437414392</v>
+        <v>221.41485912645</v>
       </c>
       <c r="F61" t="n">
         <v>87785</v>
@@ -1652,16 +1652,16 @@
         <v>43033</v>
       </c>
       <c r="B62" t="n">
-        <v>218.9927825927734</v>
+        <v>218.9927978515625</v>
       </c>
       <c r="C62" t="n">
-        <v>221.1457060715419</v>
+        <v>221.1457214803405</v>
       </c>
       <c r="D62" t="n">
-        <v>217.108972875258</v>
+        <v>217.1089880027886</v>
       </c>
       <c r="E62" t="n">
-        <v>219.8001372652768</v>
+        <v>219.80015258032</v>
       </c>
       <c r="F62" t="n">
         <v>83611</v>
@@ -1672,16 +1672,16 @@
         <v>43034</v>
       </c>
       <c r="B63" t="n">
-        <v>221.8185272216797</v>
+        <v>221.8185119628906</v>
       </c>
       <c r="C63" t="n">
-        <v>223.3659315118316</v>
+        <v>223.3659161465973</v>
       </c>
       <c r="D63" t="n">
-        <v>218.320021179497</v>
+        <v>218.3200061613684</v>
       </c>
       <c r="E63" t="n">
-        <v>219.598325068803</v>
+        <v>219.5983099627405</v>
       </c>
       <c r="F63" t="n">
         <v>55545</v>
@@ -1692,16 +1692,16 @@
         <v>43035</v>
       </c>
       <c r="B64" t="n">
-        <v>223.029541015625</v>
+        <v>223.0294952392578</v>
       </c>
       <c r="C64" t="n">
-        <v>225.3843000816768</v>
+        <v>225.384253822</v>
       </c>
       <c r="D64" t="n">
-        <v>219.6656052307278</v>
+        <v>219.6655601448017</v>
       </c>
       <c r="E64" t="n">
-        <v>222.0203642967796</v>
+        <v>222.0203187275439</v>
       </c>
       <c r="F64" t="n">
         <v>55858</v>
@@ -1712,16 +1712,16 @@
         <v>43038</v>
       </c>
       <c r="B65" t="n">
-        <v>222.0203704833984</v>
+        <v>222.0203857421875</v>
       </c>
       <c r="C65" t="n">
-        <v>223.7696235668861</v>
+        <v>223.769638945896</v>
       </c>
       <c r="D65" t="n">
-        <v>220.6075096488995</v>
+        <v>220.6075248105869</v>
       </c>
       <c r="E65" t="n">
-        <v>222.8949903307692</v>
+        <v>222.8950056496682</v>
       </c>
       <c r="F65" t="n">
         <v>160324</v>
@@ -1732,16 +1732,16 @@
         <v>43039</v>
       </c>
       <c r="B66" t="n">
-        <v>220.7420501708984</v>
+        <v>220.7420349121094</v>
       </c>
       <c r="C66" t="n">
-        <v>223.0968091278583</v>
+        <v>223.0967937062966</v>
       </c>
       <c r="D66" t="n">
-        <v>219.9347088332248</v>
+        <v>219.9346936302432</v>
       </c>
       <c r="E66" t="n">
-        <v>223.0968091278583</v>
+        <v>223.0967937062966</v>
       </c>
       <c r="F66" t="n">
         <v>91632</v>
@@ -1752,16 +1752,16 @@
         <v>43040</v>
       </c>
       <c r="B67" t="n">
-        <v>223.7695922851562</v>
+        <v>223.7696075439453</v>
       </c>
       <c r="C67" t="n">
-        <v>227.6044767762788</v>
+        <v>227.6044922965676</v>
       </c>
       <c r="D67" t="n">
-        <v>222.4912885289525</v>
+        <v>222.4913037005743</v>
       </c>
       <c r="E67" t="n">
-        <v>225.3842748545786</v>
+        <v>225.3842902234725</v>
       </c>
       <c r="F67" t="n">
         <v>232015</v>
@@ -1772,16 +1772,16 @@
         <v>43042</v>
       </c>
       <c r="B68" t="n">
-        <v>225.2497406005859</v>
+        <v>225.2497253417969</v>
       </c>
       <c r="C68" t="n">
-        <v>227.0662720624047</v>
+        <v>227.0662566805609</v>
       </c>
       <c r="D68" t="n">
-        <v>223.5005009746637</v>
+        <v>223.500485834371</v>
       </c>
       <c r="E68" t="n">
-        <v>226.7298932153962</v>
+        <v>226.7298778563392</v>
       </c>
       <c r="F68" t="n">
         <v>201288</v>
@@ -1812,16 +1812,16 @@
         <v>43046</v>
       </c>
       <c r="B70" t="n">
-        <v>228.8155670166016</v>
+        <v>228.8155364990234</v>
       </c>
       <c r="C70" t="n">
-        <v>229.4210597277648</v>
+        <v>229.4210291294309</v>
       </c>
       <c r="D70" t="n">
-        <v>227.2008573060119</v>
+        <v>227.2008270037908</v>
       </c>
       <c r="E70" t="n">
-        <v>229.4210597277648</v>
+        <v>229.4210291294309</v>
       </c>
       <c r="F70" t="n">
         <v>136939</v>
@@ -1832,16 +1832,16 @@
         <v>43047</v>
       </c>
       <c r="B71" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C71" t="n">
-        <v>234.0994470241699</v>
+        <v>234.0994316756239</v>
       </c>
       <c r="D71" t="n">
-        <v>230.1293385349365</v>
+        <v>230.1293234466875</v>
       </c>
       <c r="E71" t="n">
-        <v>230.8138625450684</v>
+        <v>230.8138474119391</v>
       </c>
       <c r="F71" t="n">
         <v>198823</v>
@@ -1872,16 +1872,16 @@
         <v>43049</v>
       </c>
       <c r="B73" t="n">
-        <v>231.0876312255859</v>
+        <v>231.087646484375</v>
       </c>
       <c r="C73" t="n">
-        <v>231.6352285676182</v>
+        <v>231.6352438625653</v>
       </c>
       <c r="D73" t="n">
-        <v>228.9656779033866</v>
+        <v>228.9656930220625</v>
       </c>
       <c r="E73" t="n">
-        <v>230.7453692649914</v>
+        <v>230.7453845011808</v>
       </c>
       <c r="F73" t="n">
         <v>131358</v>
@@ -1892,16 +1892,16 @@
         <v>43052</v>
       </c>
       <c r="B74" t="n">
-        <v>232.6620025634766</v>
+        <v>232.6619873046875</v>
       </c>
       <c r="C74" t="n">
-        <v>232.7304386139235</v>
+        <v>232.7304233506462</v>
       </c>
       <c r="D74" t="n">
-        <v>228.7603303784792</v>
+        <v>228.7603153755755</v>
       </c>
       <c r="E74" t="n">
-        <v>231.0191831852906</v>
+        <v>231.0191680342434</v>
       </c>
       <c r="F74" t="n">
         <v>214187</v>
@@ -1912,16 +1912,16 @@
         <v>43053</v>
       </c>
       <c r="B75" t="n">
-        <v>230.5400238037109</v>
+        <v>230.5400390625</v>
       </c>
       <c r="C75" t="n">
-        <v>232.4566144170252</v>
+        <v>232.4566298026679</v>
       </c>
       <c r="D75" t="n">
-        <v>228.965667892379</v>
+        <v>228.9656830469659</v>
       </c>
       <c r="E75" t="n">
-        <v>232.4566144170252</v>
+        <v>232.4566298026679</v>
       </c>
       <c r="F75" t="n">
         <v>164145</v>
@@ -1932,16 +1932,16 @@
         <v>43055</v>
       </c>
       <c r="B76" t="n">
-        <v>229.9924163818359</v>
+        <v>229.9924011230469</v>
       </c>
       <c r="C76" t="n">
-        <v>232.7988937116663</v>
+        <v>232.7988782666822</v>
       </c>
       <c r="D76" t="n">
-        <v>229.1710203434879</v>
+        <v>229.1710051391942</v>
       </c>
       <c r="E76" t="n">
-        <v>230.4715776926971</v>
+        <v>230.4715624021183</v>
       </c>
       <c r="F76" t="n">
         <v>84511</v>
@@ -1952,16 +1952,16 @@
         <v>43056</v>
       </c>
       <c r="B77" t="n">
-        <v>230.6084747314453</v>
+        <v>230.6084594726562</v>
       </c>
       <c r="C77" t="n">
-        <v>232.3197300827539</v>
+        <v>232.3197147107354</v>
       </c>
       <c r="D77" t="n">
-        <v>226.2961183294964</v>
+        <v>226.2961033560453</v>
       </c>
       <c r="E77" t="n">
-        <v>229.9924140870064</v>
+        <v>229.9923988689805</v>
       </c>
       <c r="F77" t="n">
         <v>104830</v>
@@ -1972,16 +1972,16 @@
         <v>43060</v>
       </c>
       <c r="B78" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C78" t="n">
-        <v>235.4000045023071</v>
+        <v>235.3999890684911</v>
       </c>
       <c r="D78" t="n">
-        <v>228.9657076537476</v>
+        <v>228.9656926417911</v>
       </c>
       <c r="E78" t="n">
-        <v>231.019197953186</v>
+        <v>231.0191828065941</v>
       </c>
       <c r="F78" t="n">
         <v>104948</v>
@@ -1992,16 +1992,16 @@
         <v>43061</v>
       </c>
       <c r="B79" t="n">
-        <v>233.0042114257812</v>
+        <v>233.0042266845703</v>
       </c>
       <c r="C79" t="n">
-        <v>234.5785673350231</v>
+        <v>234.5785826969123</v>
       </c>
       <c r="D79" t="n">
-        <v>232.0459161203964</v>
+        <v>232.0459313164294</v>
       </c>
       <c r="E79" t="n">
-        <v>232.0459161203964</v>
+        <v>232.0459313164294</v>
       </c>
       <c r="F79" t="n">
         <v>34548</v>
@@ -2012,16 +2012,16 @@
         <v>43062</v>
       </c>
       <c r="B80" t="n">
-        <v>231.9774932861328</v>
+        <v>231.9774627685547</v>
       </c>
       <c r="C80" t="n">
-        <v>234.4417088876228</v>
+        <v>234.4416780458672</v>
       </c>
       <c r="D80" t="n">
-        <v>231.3614598184996</v>
+        <v>231.3614293819632</v>
       </c>
       <c r="E80" t="n">
-        <v>233.3465140619172</v>
+        <v>233.3464833642389</v>
       </c>
       <c r="F80" t="n">
         <v>12911</v>
@@ -2032,16 +2032,16 @@
         <v>43063</v>
       </c>
       <c r="B81" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C81" t="n">
-        <v>234.4417090292359</v>
+        <v>234.4416936582497</v>
       </c>
       <c r="D81" t="n">
-        <v>230.6769631917725</v>
+        <v>230.6769480676189</v>
       </c>
       <c r="E81" t="n">
-        <v>232.0459567247315</v>
+        <v>232.0459415108209</v>
       </c>
       <c r="F81" t="n">
         <v>49924</v>
@@ -2052,16 +2052,16 @@
         <v>43066</v>
       </c>
       <c r="B82" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C82" t="n">
-        <v>233.4834135561646</v>
+        <v>233.4833982480083</v>
       </c>
       <c r="D82" t="n">
-        <v>231.5667953663696</v>
+        <v>231.5667801838749</v>
       </c>
       <c r="E82" t="n">
-        <v>233.4834135561646</v>
+        <v>233.4833982480083</v>
       </c>
       <c r="F82" t="n">
         <v>74064</v>
@@ -2072,16 +2072,16 @@
         <v>43067</v>
       </c>
       <c r="B83" t="n">
-        <v>231.7721252441406</v>
+        <v>231.7721405029297</v>
       </c>
       <c r="C83" t="n">
-        <v>233.0726825383711</v>
+        <v>233.0726978827827</v>
       </c>
       <c r="D83" t="n">
-        <v>231.7721252441406</v>
+        <v>231.7721405029297</v>
       </c>
       <c r="E83" t="n">
-        <v>232.7304205817031</v>
+        <v>232.7304359035818</v>
       </c>
       <c r="F83" t="n">
         <v>48463</v>
@@ -2112,16 +2112,16 @@
         <v>43069</v>
       </c>
       <c r="B85" t="n">
-        <v>235.1262054443359</v>
+        <v>235.1261901855469</v>
       </c>
       <c r="C85" t="n">
-        <v>235.1262054443359</v>
+        <v>235.1261901855469</v>
       </c>
       <c r="D85" t="n">
-        <v>230.0609021363051</v>
+        <v>230.0608872062348</v>
       </c>
       <c r="E85" t="n">
-        <v>232.4566544372292</v>
+        <v>232.4566393516838</v>
       </c>
       <c r="F85" t="n">
         <v>138609</v>
@@ -2132,16 +2132,16 @@
         <v>43070</v>
       </c>
       <c r="B86" t="n">
-        <v>234.7154998779297</v>
+        <v>234.7154541015625</v>
       </c>
       <c r="C86" t="n">
-        <v>237.8642121419739</v>
+        <v>237.864165751516</v>
       </c>
       <c r="D86" t="n">
-        <v>233.6887411407585</v>
+        <v>233.6886955646392</v>
       </c>
       <c r="E86" t="n">
-        <v>234.7154998779297</v>
+        <v>234.7154541015625</v>
       </c>
       <c r="F86" t="n">
         <v>135061</v>
@@ -2152,16 +2152,16 @@
         <v>43073</v>
       </c>
       <c r="B87" t="n">
-        <v>232.6620025634766</v>
+        <v>232.6619873046875</v>
       </c>
       <c r="C87" t="n">
-        <v>237.5219429166355</v>
+        <v>237.5219273391146</v>
       </c>
       <c r="D87" t="n">
-        <v>232.6620025634766</v>
+        <v>232.6619873046875</v>
       </c>
       <c r="E87" t="n">
-        <v>235.4684527484664</v>
+        <v>235.4684373056205</v>
       </c>
       <c r="F87" t="n">
         <v>80546</v>
@@ -2172,16 +2172,16 @@
         <v>43074</v>
       </c>
       <c r="B88" t="n">
-        <v>230.1293334960938</v>
+        <v>230.1293029785156</v>
       </c>
       <c r="C88" t="n">
-        <v>234.2363412486972</v>
+        <v>234.2363101864865</v>
       </c>
       <c r="D88" t="n">
-        <v>230.1293334960938</v>
+        <v>230.1293029785156</v>
       </c>
       <c r="E88" t="n">
-        <v>232.730448395415</v>
+        <v>232.7304175329016</v>
       </c>
       <c r="F88" t="n">
         <v>50811</v>
@@ -2192,16 +2192,16 @@
         <v>43075</v>
       </c>
       <c r="B89" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C89" t="n">
-        <v>235.4000045023071</v>
+        <v>235.3999890684911</v>
       </c>
       <c r="D89" t="n">
-        <v>229.5133050669312</v>
+        <v>229.5132900190719</v>
       </c>
       <c r="E89" t="n">
-        <v>229.9240031268189</v>
+        <v>229.9239880520325</v>
       </c>
       <c r="F89" t="n">
         <v>49754</v>
@@ -2252,16 +2252,16 @@
         <v>43080</v>
       </c>
       <c r="B92" t="n">
-        <v>231.8405914306641</v>
+        <v>231.8405609130859</v>
       </c>
       <c r="C92" t="n">
-        <v>232.7304508387718</v>
+        <v>232.73042020406</v>
       </c>
       <c r="D92" t="n">
-        <v>227.2544359038677</v>
+        <v>227.2544059899732</v>
       </c>
       <c r="E92" t="n">
-        <v>229.6502018028937</v>
+        <v>229.6501715736403</v>
       </c>
       <c r="F92" t="n">
         <v>117298</v>
@@ -2272,16 +2272,16 @@
         <v>43081</v>
       </c>
       <c r="B93" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C93" t="n">
-        <v>232.935816142981</v>
+        <v>232.9358008707275</v>
       </c>
       <c r="D93" t="n">
-        <v>230.8822985998901</v>
+        <v>230.8822834622739</v>
       </c>
       <c r="E93" t="n">
-        <v>231.5667953663696</v>
+        <v>231.5667801838749</v>
       </c>
       <c r="F93" t="n">
         <v>108939</v>
@@ -2292,16 +2292,16 @@
         <v>43082</v>
       </c>
       <c r="B94" t="n">
-        <v>228.1442565917969</v>
+        <v>228.1442718505859</v>
       </c>
       <c r="C94" t="n">
-        <v>235.2630625393395</v>
+        <v>235.2630782742499</v>
       </c>
       <c r="D94" t="n">
-        <v>226.0907530424525</v>
+        <v>226.0907681638988</v>
       </c>
       <c r="E94" t="n">
-        <v>233.3464719403202</v>
+        <v>233.3464875470449</v>
       </c>
       <c r="F94" t="n">
         <v>51971</v>
@@ -2372,16 +2372,16 @@
         <v>43088</v>
       </c>
       <c r="B98" t="n">
-        <v>224.5164031982422</v>
+        <v>224.5163879394531</v>
       </c>
       <c r="C98" t="n">
-        <v>226.4330074707774</v>
+        <v>226.4329920817304</v>
       </c>
       <c r="D98" t="n">
-        <v>223.1473962544815</v>
+        <v>223.1473810887342</v>
       </c>
       <c r="E98" t="n">
-        <v>225.9538598080997</v>
+        <v>225.9538444516168</v>
       </c>
       <c r="F98" t="n">
         <v>28066</v>
@@ -2412,16 +2412,16 @@
         <v>43090</v>
       </c>
       <c r="B100" t="n">
-        <v>226.9121704101562</v>
+        <v>226.9121551513672</v>
       </c>
       <c r="C100" t="n">
-        <v>228.144278104674</v>
+        <v>228.1442627630314</v>
       </c>
       <c r="D100" t="n">
-        <v>224.5164183136509</v>
+        <v>224.516403215965</v>
       </c>
       <c r="E100" t="n">
-        <v>225.9538750202841</v>
+        <v>225.953859825936</v>
       </c>
       <c r="F100" t="n">
         <v>149421</v>
@@ -2432,16 +2432,16 @@
         <v>43091</v>
       </c>
       <c r="B101" t="n">
-        <v>230.5400238037109</v>
+        <v>230.5400390625</v>
       </c>
       <c r="C101" t="n">
-        <v>230.5400238037109</v>
+        <v>230.5400390625</v>
       </c>
       <c r="D101" t="n">
-        <v>225.2008954650403</v>
+        <v>225.2009103704476</v>
       </c>
       <c r="E101" t="n">
-        <v>226.9806003706559</v>
+        <v>226.9806153938569</v>
       </c>
       <c r="F101" t="n">
         <v>94553</v>
@@ -2452,16 +2452,16 @@
         <v>43095</v>
       </c>
       <c r="B102" t="n">
-        <v>232.7988891601562</v>
+        <v>232.7988739013672</v>
       </c>
       <c r="C102" t="n">
-        <v>233.6887212291445</v>
+        <v>233.6887059120314</v>
       </c>
       <c r="D102" t="n">
-        <v>226.5699148371684</v>
+        <v>226.5698999866571</v>
       </c>
       <c r="E102" t="n">
-        <v>230.6084725237372</v>
+        <v>230.6084574085188</v>
       </c>
       <c r="F102" t="n">
         <v>75564</v>
@@ -2492,16 +2492,16 @@
         <v>43097</v>
       </c>
       <c r="B104" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C104" t="n">
-        <v>233.0727154962769</v>
+        <v>233.0727002150477</v>
       </c>
       <c r="D104" t="n">
-        <v>228.144297912146</v>
+        <v>228.1442829540446</v>
       </c>
       <c r="E104" t="n">
-        <v>230.7453992465942</v>
+        <v>230.7453841179537</v>
       </c>
       <c r="F104" t="n">
         <v>86715</v>
@@ -2552,16 +2552,16 @@
         <v>43104</v>
       </c>
       <c r="B107" t="n">
-        <v>232.7304534912109</v>
+        <v>232.7304382324219</v>
       </c>
       <c r="C107" t="n">
-        <v>234.0994470241699</v>
+        <v>234.0994316756239</v>
       </c>
       <c r="D107" t="n">
-        <v>228.9657076537476</v>
+        <v>228.9656926417911</v>
       </c>
       <c r="E107" t="n">
-        <v>230.8138625450684</v>
+        <v>230.8138474119391</v>
       </c>
       <c r="F107" t="n">
         <v>136353</v>
@@ -2572,16 +2572,16 @@
         <v>43105</v>
       </c>
       <c r="B108" t="n">
-        <v>235.7422180175781</v>
+        <v>235.7422332763672</v>
       </c>
       <c r="C108" t="n">
-        <v>236.7689765779297</v>
+        <v>236.7689919031773</v>
       </c>
       <c r="D108" t="n">
-        <v>230.8138150689962</v>
+        <v>230.8138300087865</v>
       </c>
       <c r="E108" t="n">
-        <v>231.3614123695445</v>
+        <v>231.361427344779</v>
       </c>
       <c r="F108" t="n">
         <v>47198</v>
@@ -2632,16 +2632,16 @@
         <v>43110</v>
       </c>
       <c r="B111" t="n">
-        <v>239.1647491455078</v>
+        <v>239.1647644042969</v>
       </c>
       <c r="C111" t="n">
-        <v>241.4920378748115</v>
+        <v>241.4920532820823</v>
       </c>
       <c r="D111" t="n">
-        <v>238.0010911590314</v>
+        <v>238.0011063435787</v>
       </c>
       <c r="E111" t="n">
-        <v>241.3551385377936</v>
+        <v>241.3551539363303</v>
       </c>
       <c r="F111" t="n">
         <v>106434</v>
@@ -2652,16 +2652,16 @@
         <v>43111</v>
       </c>
       <c r="B112" t="n">
-        <v>246.4204406738281</v>
+        <v>246.4204254150391</v>
       </c>
       <c r="C112" t="n">
-        <v>246.4204406738281</v>
+        <v>246.4204254150391</v>
       </c>
       <c r="D112" t="n">
-        <v>238.3433253213977</v>
+        <v>238.3433105627579</v>
       </c>
       <c r="E112" t="n">
-        <v>239.5754465953212</v>
+        <v>239.5754317603862</v>
       </c>
       <c r="F112" t="n">
         <v>230476</v>
@@ -2672,16 +2672,16 @@
         <v>43112</v>
       </c>
       <c r="B113" t="n">
-        <v>253.1970672607422</v>
+        <v>253.1970062255859</v>
       </c>
       <c r="C113" t="n">
-        <v>255.2505576462442</v>
+        <v>255.2504961160778</v>
       </c>
       <c r="D113" t="n">
-        <v>244.2985271926063</v>
+        <v>244.2984683025135</v>
       </c>
       <c r="E113" t="n">
-        <v>244.4354265516398</v>
+        <v>244.4353676285463</v>
       </c>
       <c r="F113" t="n">
         <v>209648</v>
@@ -2792,16 +2792,16 @@
         <v>43122</v>
       </c>
       <c r="B119" t="n">
-        <v>261.1372680664062</v>
+        <v>261.1372375488281</v>
       </c>
       <c r="C119" t="n">
-        <v>265.3127118748384</v>
+        <v>265.3126808693007</v>
       </c>
       <c r="D119" t="n">
-        <v>256.0035015616586</v>
+        <v>256.0034716440336</v>
       </c>
       <c r="E119" t="n">
-        <v>256.6879983135613</v>
+        <v>256.6879683159431</v>
       </c>
       <c r="F119" t="n">
         <v>99157</v>
@@ -2932,16 +2932,16 @@
         <v>43132</v>
       </c>
       <c r="B126" t="n">
-        <v>259.0836791992188</v>
+        <v>259.0837097167969</v>
       </c>
       <c r="C126" t="n">
-        <v>261.0002968202418</v>
+        <v>261.0003275635792</v>
       </c>
       <c r="D126" t="n">
-        <v>256.6879276056732</v>
+        <v>256.6879578410547</v>
       </c>
       <c r="E126" t="n">
-        <v>260.1104376660653</v>
+        <v>260.1104683045857</v>
       </c>
       <c r="F126" t="n">
         <v>203518</v>
@@ -2952,16 +2952,16 @@
         <v>43133</v>
       </c>
       <c r="B127" t="n">
-        <v>260.0420532226562</v>
+        <v>260.0420227050781</v>
       </c>
       <c r="C127" t="n">
-        <v>262.3009061883292</v>
+        <v>262.3008754056605</v>
       </c>
       <c r="D127" t="n">
-        <v>257.1671667850331</v>
+        <v>257.1671366048411</v>
       </c>
       <c r="E127" t="n">
-        <v>257.6463009028107</v>
+        <v>257.6462706663893</v>
       </c>
       <c r="F127" t="n">
         <v>110412</v>
@@ -3052,16 +3052,16 @@
         <v>43140</v>
       </c>
       <c r="B132" t="n">
-        <v>258.0569458007812</v>
+        <v>258.0569763183594</v>
       </c>
       <c r="C132" t="n">
-        <v>270.2410675429375</v>
+        <v>270.2410995013987</v>
       </c>
       <c r="D132" t="n">
-        <v>256.5510532151254</v>
+        <v>256.5510835546181</v>
       </c>
       <c r="E132" t="n">
-        <v>266.2025238050371</v>
+        <v>266.2025552859037</v>
       </c>
       <c r="F132" t="n">
         <v>222103</v>
@@ -3072,16 +3072,16 @@
         <v>43145</v>
       </c>
       <c r="B133" t="n">
-        <v>265.1758117675781</v>
+        <v>265.1758728027344</v>
       </c>
       <c r="C133" t="n">
-        <v>270.3780143108417</v>
+        <v>270.3780765433819</v>
       </c>
       <c r="D133" t="n">
-        <v>258.3992530776061</v>
+        <v>258.399312553011</v>
       </c>
       <c r="E133" t="n">
-        <v>258.3992530776061</v>
+        <v>258.399312553011</v>
       </c>
       <c r="F133" t="n">
         <v>141282</v>
@@ -3092,16 +3092,16 @@
         <v>43146</v>
       </c>
       <c r="B134" t="n">
-        <v>262.2323913574219</v>
+        <v>262.2324523925781</v>
       </c>
       <c r="C134" t="n">
-        <v>267.6399550882621</v>
+        <v>267.6400173820405</v>
       </c>
       <c r="D134" t="n">
-        <v>262.2323913574219</v>
+        <v>262.2324523925781</v>
       </c>
       <c r="E134" t="n">
-        <v>267.5714918099162</v>
+        <v>267.5715540877596</v>
       </c>
       <c r="F134" t="n">
         <v>86167</v>
@@ -3112,16 +3112,16 @@
         <v>43147</v>
       </c>
       <c r="B135" t="n">
-        <v>264.9019775390625</v>
+        <v>264.9020080566406</v>
       </c>
       <c r="C135" t="n">
-        <v>265.7233735288359</v>
+        <v>265.7234041410416</v>
       </c>
       <c r="D135" t="n">
-        <v>261.1372322974435</v>
+        <v>261.1372623813106</v>
       </c>
       <c r="E135" t="n">
-        <v>264.9019775390625</v>
+        <v>264.9020080566406</v>
       </c>
       <c r="F135" t="n">
         <v>112655</v>
@@ -3132,16 +3132,16 @@
         <v>43150</v>
       </c>
       <c r="B136" t="n">
-        <v>262.780029296875</v>
+        <v>262.7800598144531</v>
       </c>
       <c r="C136" t="n">
-        <v>267.4346339048228</v>
+        <v>267.4346649629567</v>
       </c>
       <c r="D136" t="n">
-        <v>261.4794719997318</v>
+        <v>261.4795023662716</v>
       </c>
       <c r="E136" t="n">
-        <v>266.202539896626</v>
+        <v>266.2025708116724</v>
       </c>
       <c r="F136" t="n">
         <v>88593</v>
@@ -3232,16 +3232,16 @@
         <v>43157</v>
       </c>
       <c r="B141" t="n">
-        <v>266.3394165039062</v>
+        <v>266.3394470214844</v>
       </c>
       <c r="C141" t="n">
-        <v>269.6934635285073</v>
+        <v>269.6934944303972</v>
       </c>
       <c r="D141" t="n">
-        <v>265.9971545756772</v>
+        <v>265.9971850540384</v>
       </c>
       <c r="E141" t="n">
-        <v>268.9405036325911</v>
+        <v>268.9405344482058</v>
       </c>
       <c r="F141" t="n">
         <v>58114</v>
@@ -3252,16 +3252,16 @@
         <v>43158</v>
       </c>
       <c r="B142" t="n">
-        <v>267.6400451660156</v>
+        <v>267.6400146484375</v>
       </c>
       <c r="C142" t="n">
-        <v>268.3245419616291</v>
+        <v>268.3245113660014</v>
       </c>
       <c r="D142" t="n">
-        <v>262.3693789743113</v>
+        <v>262.3693490577193</v>
       </c>
       <c r="E142" t="n">
-        <v>266.4763869916459</v>
+        <v>266.4763566067535</v>
       </c>
       <c r="F142" t="n">
         <v>80520</v>
@@ -3272,16 +3272,16 @@
         <v>43159</v>
       </c>
       <c r="B143" t="n">
-        <v>264.9019775390625</v>
+        <v>264.9020080566406</v>
       </c>
       <c r="C143" t="n">
-        <v>268.73518606832</v>
+        <v>268.7352170274963</v>
       </c>
       <c r="D143" t="n">
-        <v>261.7532656679495</v>
+        <v>261.7532958227857</v>
       </c>
       <c r="E143" t="n">
-        <v>266.9554675134961</v>
+        <v>266.955498267643</v>
       </c>
       <c r="F143" t="n">
         <v>75330</v>
@@ -3292,16 +3292,16 @@
         <v>43160</v>
       </c>
       <c r="B144" t="n">
-        <v>263.5330200195312</v>
+        <v>263.5329895019531</v>
       </c>
       <c r="C144" t="n">
-        <v>267.4346651227554</v>
+        <v>267.4346341533601</v>
       </c>
       <c r="D144" t="n">
-        <v>262.5062612710216</v>
+        <v>262.5062308723439</v>
       </c>
       <c r="E144" t="n">
-        <v>264.9020135217763</v>
+        <v>264.9019828456663</v>
       </c>
       <c r="F144" t="n">
         <v>57645</v>
@@ -3332,16 +3332,16 @@
         <v>43164</v>
       </c>
       <c r="B146" t="n">
-        <v>263.5330200195312</v>
+        <v>263.5329895019531</v>
       </c>
       <c r="C146" t="n">
-        <v>267.2977657725309</v>
+        <v>267.2977348189888</v>
       </c>
       <c r="D146" t="n">
-        <v>262.9169593216951</v>
+        <v>262.9169288754579</v>
       </c>
       <c r="E146" t="n">
-        <v>266.6817050746948</v>
+        <v>266.6816741924935</v>
       </c>
       <c r="F146" t="n">
         <v>71404</v>
@@ -3372,16 +3372,16 @@
         <v>43166</v>
       </c>
       <c r="B148" t="n">
-        <v>272.6368408203125</v>
+        <v>272.6368713378906</v>
       </c>
       <c r="C148" t="n">
-        <v>273.1160021207269</v>
+        <v>273.1160326919399</v>
       </c>
       <c r="D148" t="n">
-        <v>266.6132427601048</v>
+        <v>266.6132726034321</v>
       </c>
       <c r="E148" t="n">
-        <v>266.6132427601048</v>
+        <v>266.6132726034321</v>
       </c>
       <c r="F148" t="n">
         <v>73125</v>
@@ -3392,16 +3392,16 @@
         <v>43167</v>
       </c>
       <c r="B149" t="n">
-        <v>277.2230529785156</v>
+        <v>277.2229919433594</v>
       </c>
       <c r="C149" t="n">
-        <v>279.2765705955771</v>
+        <v>279.2765091083056</v>
       </c>
       <c r="D149" t="n">
-        <v>273.1160449880462</v>
+        <v>273.1159848571144</v>
       </c>
       <c r="E149" t="n">
-        <v>273.8005417791822</v>
+        <v>273.8004814975473</v>
       </c>
       <c r="F149" t="n">
         <v>360517</v>
@@ -3412,16 +3412,16 @@
         <v>43168</v>
       </c>
       <c r="B150" t="n">
-        <v>289.2017517089844</v>
+        <v>289.2018127441406</v>
       </c>
       <c r="C150" t="n">
-        <v>291.5975308196897</v>
+        <v>291.5975923604679</v>
       </c>
       <c r="D150" t="n">
-        <v>277.9759523011636</v>
+        <v>277.9760109671489</v>
       </c>
       <c r="E150" t="n">
-        <v>278.0443883434895</v>
+        <v>278.0444470239179</v>
       </c>
       <c r="F150" t="n">
         <v>178074</v>
@@ -3432,16 +3432,16 @@
         <v>43171</v>
       </c>
       <c r="B151" t="n">
-        <v>295.4992065429688</v>
+        <v>295.4992370605469</v>
       </c>
       <c r="C151" t="n">
-        <v>296.5259652356011</v>
+        <v>296.5259958592174</v>
       </c>
       <c r="D151" t="n">
-        <v>286.8744934608874</v>
+        <v>286.8745230877512</v>
       </c>
       <c r="E151" t="n">
-        <v>287.4905541251969</v>
+        <v>287.4905838156842</v>
       </c>
       <c r="F151" t="n">
         <v>187725</v>
@@ -3452,16 +3452,16 @@
         <v>43172</v>
       </c>
       <c r="B152" t="n">
-        <v>298.4425354003906</v>
+        <v>298.4425659179688</v>
       </c>
       <c r="C152" t="n">
-        <v>298.4425354003906</v>
+        <v>298.4425659179688</v>
       </c>
       <c r="D152" t="n">
-        <v>293.2403334909926</v>
+        <v>293.2403634766137</v>
       </c>
       <c r="E152" t="n">
-        <v>296.5259447340618</v>
+        <v>296.5259750556568</v>
       </c>
       <c r="F152" t="n">
         <v>244066</v>
@@ -3472,16 +3472,16 @@
         <v>43173</v>
       </c>
       <c r="B153" t="n">
-        <v>292.9665222167969</v>
+        <v>292.966552734375</v>
       </c>
       <c r="C153" t="n">
-        <v>297.0735292829796</v>
+        <v>297.0735602283742</v>
       </c>
       <c r="D153" t="n">
-        <v>290.9814683474144</v>
+        <v>290.9814986582145</v>
       </c>
       <c r="E153" t="n">
-        <v>297.0735292829796</v>
+        <v>297.0735602283742</v>
       </c>
       <c r="F153" t="n">
         <v>157963</v>
@@ -3532,16 +3532,16 @@
         <v>43178</v>
       </c>
       <c r="B156" t="n">
-        <v>286.8059997558594</v>
+        <v>286.8060607910156</v>
       </c>
       <c r="C156" t="n">
-        <v>289.2017516221983</v>
+        <v>289.2018131671943</v>
       </c>
       <c r="D156" t="n">
-        <v>278.2497508742624</v>
+        <v>278.2498100885641</v>
       </c>
       <c r="E156" t="n">
-        <v>278.9342475155524</v>
+        <v>278.9343068755218</v>
       </c>
       <c r="F156" t="n">
         <v>266146</v>
@@ -3552,16 +3552,16 @@
         <v>43179</v>
       </c>
       <c r="B157" t="n">
-        <v>290.9130249023438</v>
+        <v>290.9130554199219</v>
       </c>
       <c r="C157" t="n">
-        <v>291.5975488297652</v>
+        <v>291.5975794191518</v>
       </c>
       <c r="D157" t="n">
-        <v>287.4905414834819</v>
+        <v>287.4905716420321</v>
       </c>
       <c r="E157" t="n">
-        <v>287.4905414834819</v>
+        <v>287.4905716420321</v>
       </c>
       <c r="F157" t="n">
         <v>107700</v>
@@ -3612,16 +3612,16 @@
         <v>43182</v>
       </c>
       <c r="B160" t="n">
-        <v>299.3314514160156</v>
+        <v>299.3314819335938</v>
       </c>
       <c r="C160" t="n">
-        <v>305.5245171004302</v>
+        <v>305.5245482494066</v>
       </c>
       <c r="D160" t="n">
-        <v>298.1213062825533</v>
+        <v>298.1213366767541</v>
       </c>
       <c r="E160" t="n">
-        <v>301.467004984715</v>
+        <v>301.4670357200181</v>
       </c>
       <c r="F160" t="n">
         <v>128358</v>
@@ -3632,16 +3632,16 @@
         <v>43185</v>
       </c>
       <c r="B161" t="n">
-        <v>301.8228759765625</v>
+        <v>301.8229064941406</v>
       </c>
       <c r="C161" t="n">
-        <v>303.9584292925603</v>
+        <v>303.9584600260661</v>
       </c>
       <c r="D161" t="n">
-        <v>300.8974676508297</v>
+        <v>300.8974980748389</v>
       </c>
       <c r="E161" t="n">
-        <v>301.6805076442964</v>
+        <v>301.6805381474795</v>
       </c>
       <c r="F161" t="n">
         <v>81498</v>
@@ -3652,16 +3652,16 @@
         <v>43186</v>
       </c>
       <c r="B162" t="n">
-        <v>298.8331604003906</v>
+        <v>298.8331909179688</v>
       </c>
       <c r="C162" t="n">
-        <v>303.4601744361335</v>
+        <v>303.4602054262336</v>
       </c>
       <c r="D162" t="n">
-        <v>298.8331604003906</v>
+        <v>298.8331909179688</v>
       </c>
       <c r="E162" t="n">
-        <v>302.2500292525688</v>
+        <v>302.250060119086</v>
       </c>
       <c r="F162" t="n">
         <v>78499</v>
@@ -3732,16 +3732,16 @@
         <v>43193</v>
       </c>
       <c r="B166" t="n">
-        <v>295.7010803222656</v>
+        <v>295.7011108398438</v>
       </c>
       <c r="C166" t="n">
-        <v>298.1925409008497</v>
+        <v>298.1925716755569</v>
       </c>
       <c r="D166" t="n">
-        <v>295.1316068565337</v>
+        <v>295.1316373153397</v>
       </c>
       <c r="E166" t="n">
-        <v>296.5552905208637</v>
+        <v>296.5553211265998</v>
       </c>
       <c r="F166" t="n">
         <v>70439</v>
@@ -3752,16 +3752,16 @@
         <v>43194</v>
       </c>
       <c r="B167" t="n">
-        <v>297.5518188476562</v>
+        <v>297.5518493652344</v>
       </c>
       <c r="C167" t="n">
-        <v>302.8906741855086</v>
+        <v>302.8907052506516</v>
       </c>
       <c r="D167" t="n">
-        <v>293.6366752657696</v>
+        <v>293.6367053818018</v>
       </c>
       <c r="E167" t="n">
-        <v>295.7010303965118</v>
+        <v>295.701060724269</v>
       </c>
       <c r="F167" t="n">
         <v>68913</v>
@@ -3812,16 +3812,16 @@
         <v>43199</v>
       </c>
       <c r="B170" t="n">
-        <v>305.0261840820312</v>
+        <v>305.0262451171875</v>
       </c>
       <c r="C170" t="n">
-        <v>306.3786974332219</v>
+        <v>306.3787587390135</v>
       </c>
       <c r="D170" t="n">
-        <v>301.3246073646769</v>
+        <v>301.3246676591547</v>
       </c>
       <c r="E170" t="n">
-        <v>303.6025007292026</v>
+        <v>303.6025614794826</v>
       </c>
       <c r="F170" t="n">
         <v>72199</v>
@@ -3872,16 +3872,16 @@
         <v>43202</v>
       </c>
       <c r="B173" t="n">
-        <v>301.8228759765625</v>
+        <v>301.8229064941406</v>
       </c>
       <c r="C173" t="n">
-        <v>308.8701509217435</v>
+        <v>308.8701821518778</v>
       </c>
       <c r="D173" t="n">
-        <v>300.4703626540315</v>
+        <v>300.4703930348558</v>
       </c>
       <c r="E173" t="n">
-        <v>308.5142442570815</v>
+        <v>308.5142754512298</v>
       </c>
       <c r="F173" t="n">
         <v>107060</v>
@@ -3892,16 +3892,16 @@
         <v>43203</v>
       </c>
       <c r="B174" t="n">
-        <v>301.8228759765625</v>
+        <v>301.8229064941406</v>
       </c>
       <c r="C174" t="n">
-        <v>305.3821126152211</v>
+        <v>305.3821434926768</v>
       </c>
       <c r="D174" t="n">
-        <v>298.9755093312407</v>
+        <v>298.9755395609191</v>
       </c>
       <c r="E174" t="n">
-        <v>301.8940743086987</v>
+        <v>301.8941048334758</v>
       </c>
       <c r="F174" t="n">
         <v>180213</v>
@@ -3972,16 +3972,16 @@
         <v>43209</v>
       </c>
       <c r="B178" t="n">
-        <v>335.9915466308594</v>
+        <v>335.9915771484375</v>
       </c>
       <c r="C178" t="n">
-        <v>338.8389419832259</v>
+        <v>338.8389727594285</v>
       </c>
       <c r="D178" t="n">
-        <v>324.9579285969529</v>
+        <v>324.957958112365</v>
       </c>
       <c r="E178" t="n">
-        <v>324.9579285969529</v>
+        <v>324.957958112365</v>
       </c>
       <c r="F178" t="n">
         <v>241809</v>
@@ -3992,16 +3992,16 @@
         <v>43210</v>
       </c>
       <c r="B179" t="n">
-        <v>336.3474731445312</v>
+        <v>336.3475036621094</v>
       </c>
       <c r="C179" t="n">
-        <v>340.2626168642371</v>
+        <v>340.2626477370452</v>
       </c>
       <c r="D179" t="n">
-        <v>331.934026042895</v>
+        <v>331.934056160031</v>
       </c>
       <c r="E179" t="n">
-        <v>335.9203681023093</v>
+        <v>335.9203985811352</v>
       </c>
       <c r="F179" t="n">
         <v>100696</v>
@@ -4032,16 +4032,16 @@
         <v>43214</v>
       </c>
       <c r="B181" t="n">
-        <v>330.1544189453125</v>
+        <v>330.1543579101562</v>
       </c>
       <c r="C181" t="n">
-        <v>332.4323125825596</v>
+        <v>332.4322511262926</v>
       </c>
       <c r="D181" t="n">
-        <v>325.9545100536225</v>
+        <v>325.9544497948972</v>
       </c>
       <c r="E181" t="n">
-        <v>328.1612336807109</v>
+        <v>328.1611730140318</v>
       </c>
       <c r="F181" t="n">
         <v>71391</v>
@@ -4052,16 +4052,16 @@
         <v>43215</v>
       </c>
       <c r="B182" t="n">
-        <v>335.92041015625</v>
+        <v>335.9203796386719</v>
       </c>
       <c r="C182" t="n">
-        <v>336.9881870614848</v>
+        <v>336.9881564469016</v>
       </c>
       <c r="D182" t="n">
-        <v>326.8799481340848</v>
+        <v>326.8799184378113</v>
       </c>
       <c r="E182" t="n">
-        <v>330.86629069255</v>
+        <v>330.8662606341267</v>
       </c>
       <c r="F182" t="n">
         <v>82020</v>
@@ -4072,16 +4072,16 @@
         <v>43216</v>
       </c>
       <c r="B183" t="n">
-        <v>343.4659423828125</v>
+        <v>343.4659729003906</v>
       </c>
       <c r="C183" t="n">
-        <v>343.4659423828125</v>
+        <v>343.4659729003906</v>
       </c>
       <c r="D183" t="n">
-        <v>334.6390199707884</v>
+        <v>334.6390497040783</v>
       </c>
       <c r="E183" t="n">
-        <v>334.6390199707884</v>
+        <v>334.6390497040783</v>
       </c>
       <c r="F183" t="n">
         <v>151181</v>
@@ -4112,16 +4112,16 @@
         <v>43220</v>
       </c>
       <c r="B185" t="n">
-        <v>336.7033996582031</v>
+        <v>336.703369140625</v>
       </c>
       <c r="C185" t="n">
-        <v>341.188045363418</v>
+        <v>341.1880144393678</v>
       </c>
       <c r="D185" t="n">
-        <v>334.8526110330102</v>
+        <v>334.8525806831809</v>
       </c>
       <c r="E185" t="n">
-        <v>340.4762035844976</v>
+        <v>340.4761727249662</v>
       </c>
       <c r="F185" t="n">
         <v>66083</v>
@@ -4172,16 +4172,16 @@
         <v>43224</v>
       </c>
       <c r="B188" t="n">
-        <v>358.0587768554688</v>
+        <v>358.0588073730469</v>
       </c>
       <c r="C188" t="n">
-        <v>358.0587768554688</v>
+        <v>358.0588073730469</v>
       </c>
       <c r="D188" t="n">
-        <v>328.5171603432981</v>
+        <v>328.5171883430254</v>
       </c>
       <c r="E188" t="n">
-        <v>345.2455404769352</v>
+        <v>345.245569902433</v>
       </c>
       <c r="F188" t="n">
         <v>336833</v>
@@ -4192,16 +4192,16 @@
         <v>43227</v>
       </c>
       <c r="B189" t="n">
-        <v>352.6487121582031</v>
+        <v>352.6487426757812</v>
       </c>
       <c r="C189" t="n">
-        <v>358.0587371405379</v>
+        <v>358.0587681262897</v>
       </c>
       <c r="D189" t="n">
-        <v>349.3030421689705</v>
+        <v>349.3030723970205</v>
       </c>
       <c r="E189" t="n">
-        <v>358.0587371405379</v>
+        <v>358.0587681262897</v>
       </c>
       <c r="F189" t="n">
         <v>165384</v>
@@ -4212,16 +4212,16 @@
         <v>43228</v>
       </c>
       <c r="B190" t="n">
-        <v>346.3132934570312</v>
+        <v>346.3133239746094</v>
       </c>
       <c r="C190" t="n">
-        <v>353.1470303887233</v>
+        <v>353.1470615084992</v>
       </c>
       <c r="D190" t="n">
-        <v>343.109991665554</v>
+        <v>343.110021900853</v>
       </c>
       <c r="E190" t="n">
-        <v>353.0758320532644</v>
+        <v>353.0758631667663</v>
       </c>
       <c r="F190" t="n">
         <v>143917</v>
@@ -4232,16 +4232,16 @@
         <v>43229</v>
       </c>
       <c r="B191" t="n">
-        <v>344.5337219238281</v>
+        <v>344.53369140625</v>
       </c>
       <c r="C191" t="n">
-        <v>350.6556179937721</v>
+        <v>350.6555869339381</v>
       </c>
       <c r="D191" t="n">
-        <v>341.6863547582836</v>
+        <v>341.6863244929152</v>
       </c>
       <c r="E191" t="n">
-        <v>347.3099190762399</v>
+        <v>347.309888312756</v>
       </c>
       <c r="F191" t="n">
         <v>105117</v>
@@ -4252,16 +4252,16 @@
         <v>43230</v>
       </c>
       <c r="B192" t="n">
-        <v>337.6288146972656</v>
+        <v>337.6287841796875</v>
       </c>
       <c r="C192" t="n">
-        <v>340.2626434964544</v>
+        <v>340.2626127408098</v>
       </c>
       <c r="D192" t="n">
-        <v>329.1578548654977</v>
+        <v>329.1578251135923</v>
       </c>
       <c r="E192" t="n">
-        <v>340.2626434964544</v>
+        <v>340.2626127408098</v>
       </c>
       <c r="F192" t="n">
         <v>218204</v>
@@ -4272,16 +4272,16 @@
         <v>43231</v>
       </c>
       <c r="B193" t="n">
-        <v>343.1100463867188</v>
+        <v>343.1099853515625</v>
       </c>
       <c r="C193" t="n">
-        <v>349.5878493382494</v>
+        <v>349.5877871507698</v>
       </c>
       <c r="D193" t="n">
-        <v>338.1271253981586</v>
+        <v>338.1270652494042</v>
       </c>
       <c r="E193" t="n">
-        <v>338.1271253981586</v>
+        <v>338.1270652494042</v>
       </c>
       <c r="F193" t="n">
         <v>94240</v>
@@ -4292,16 +4292,16 @@
         <v>43234</v>
       </c>
       <c r="B194" t="n">
-        <v>341.6863708496094</v>
+        <v>341.6863403320312</v>
       </c>
       <c r="C194" t="n">
-        <v>350.7268045239795</v>
+        <v>350.7267731989587</v>
       </c>
       <c r="D194" t="n">
-        <v>341.6863708496094</v>
+        <v>341.6863403320312</v>
       </c>
       <c r="E194" t="n">
-        <v>343.2524228644103</v>
+        <v>343.2523922069608</v>
       </c>
       <c r="F194" t="n">
         <v>112773</v>
@@ -4312,16 +4312,16 @@
         <v>43235</v>
       </c>
       <c r="B195" t="n">
-        <v>358.7706909179688</v>
+        <v>358.7706604003906</v>
       </c>
       <c r="C195" t="n">
-        <v>359.9808078642333</v>
+        <v>359.9807772437208</v>
       </c>
       <c r="D195" t="n">
-        <v>344.5337409749617</v>
+        <v>344.5337116684001</v>
       </c>
       <c r="E195" t="n">
-        <v>344.5337409749617</v>
+        <v>344.5337116684001</v>
       </c>
       <c r="F195" t="n">
         <v>409111</v>
@@ -4332,16 +4332,16 @@
         <v>43236</v>
       </c>
       <c r="B196" t="n">
-        <v>363.9671325683594</v>
+        <v>363.9671020507812</v>
       </c>
       <c r="C196" t="n">
-        <v>370.1601986896467</v>
+        <v>370.1601676527981</v>
       </c>
       <c r="D196" t="n">
-        <v>360.9061986805075</v>
+        <v>360.9061684195798</v>
       </c>
       <c r="E196" t="n">
-        <v>360.9061986805075</v>
+        <v>360.9061684195798</v>
       </c>
       <c r="F196" t="n">
         <v>163245</v>
@@ -4352,16 +4352,16 @@
         <v>43237</v>
       </c>
       <c r="B197" t="n">
-        <v>359.1265258789062</v>
+        <v>359.1265563964844</v>
       </c>
       <c r="C197" t="n">
-        <v>368.0957878174224</v>
+        <v>368.0958190971836</v>
       </c>
       <c r="D197" t="n">
-        <v>357.8452108396918</v>
+        <v>357.8452412483873</v>
       </c>
       <c r="E197" t="n">
-        <v>365.7466960795255</v>
+        <v>365.7467271596673</v>
       </c>
       <c r="F197" t="n">
         <v>115420</v>
@@ -4372,16 +4372,16 @@
         <v>43238</v>
       </c>
       <c r="B198" t="n">
-        <v>347.0963439941406</v>
+        <v>347.0963134765625</v>
       </c>
       <c r="C198" t="n">
-        <v>358.7706331341753</v>
+        <v>358.7706015901645</v>
       </c>
       <c r="D198" t="n">
-        <v>339.9067001635369</v>
+        <v>339.9066702780902</v>
       </c>
       <c r="E198" t="n">
-        <v>358.7706331341753</v>
+        <v>358.7706015901645</v>
       </c>
       <c r="F198" t="n">
         <v>310384</v>
@@ -4392,16 +4392,16 @@
         <v>43241</v>
       </c>
       <c r="B199" t="n">
-        <v>343.1100463867188</v>
+        <v>343.1099853515625</v>
       </c>
       <c r="C199" t="n">
-        <v>355.8520855813504</v>
+        <v>355.8520222795384</v>
       </c>
       <c r="D199" t="n">
-        <v>339.9779140991621</v>
+        <v>339.9778536211746</v>
       </c>
       <c r="E199" t="n">
-        <v>348.8048091833572</v>
+        <v>348.804747135171</v>
       </c>
       <c r="F199" t="n">
         <v>199215</v>
@@ -4432,16 +4432,16 @@
         <v>43243</v>
       </c>
       <c r="B201" t="n">
-        <v>343.394775390625</v>
+        <v>343.3947448730469</v>
       </c>
       <c r="C201" t="n">
-        <v>349.303104762877</v>
+        <v>349.3030737202242</v>
       </c>
       <c r="D201" t="n">
-        <v>333.5001036507331</v>
+        <v>333.500074012497</v>
       </c>
       <c r="E201" t="n">
-        <v>349.303104762877</v>
+        <v>349.3030737202242</v>
       </c>
       <c r="F201" t="n">
         <v>194780</v>
@@ -4452,16 +4452,16 @@
         <v>43244</v>
       </c>
       <c r="B202" t="n">
-        <v>345.1744384765625</v>
+        <v>345.1744079589844</v>
       </c>
       <c r="C202" t="n">
-        <v>346.9540573518779</v>
+        <v>346.9540266769599</v>
       </c>
       <c r="D202" t="n">
-        <v>336.8458176069644</v>
+        <v>336.8457878257366</v>
       </c>
       <c r="E202" t="n">
-        <v>336.8458176069644</v>
+        <v>336.8457878257366</v>
       </c>
       <c r="F202" t="n">
         <v>202723</v>
@@ -4472,16 +4472,16 @@
         <v>43245</v>
       </c>
       <c r="B203" t="n">
-        <v>340.9744262695312</v>
+        <v>340.9744873046875</v>
       </c>
       <c r="C203" t="n">
-        <v>354.0724263170686</v>
+        <v>354.072489696795</v>
       </c>
       <c r="D203" t="n">
-        <v>340.2625845999926</v>
+        <v>340.2626455077277</v>
       </c>
       <c r="E203" t="n">
-        <v>345.8150062864073</v>
+        <v>345.8150681880377</v>
       </c>
       <c r="F203" t="n">
         <v>304724</v>
@@ -4512,16 +4512,16 @@
         <v>43249</v>
       </c>
       <c r="B205" t="n">
-        <v>338.8389587402344</v>
+        <v>338.8389282226562</v>
       </c>
       <c r="C205" t="n">
-        <v>346.8116434555354</v>
+        <v>346.8116122198963</v>
       </c>
       <c r="D205" t="n">
-        <v>331.5069458022026</v>
+        <v>331.5069159449832</v>
       </c>
       <c r="E205" t="n">
-        <v>341.6863542334166</v>
+        <v>341.6863234593874</v>
       </c>
       <c r="F205" t="n">
         <v>340941</v>
@@ -4532,16 +4532,16 @@
         <v>43250</v>
       </c>
       <c r="B206" t="n">
-        <v>343.2524108886719</v>
+        <v>343.2523803710938</v>
       </c>
       <c r="C206" t="n">
-        <v>347.4522916751147</v>
+        <v>347.4522607841373</v>
       </c>
       <c r="D206" t="n">
-        <v>336.2051345699209</v>
+        <v>336.2051046788957</v>
       </c>
       <c r="E206" t="n">
-        <v>338.1271215961268</v>
+        <v>338.1270915342233</v>
       </c>
       <c r="F206" t="n">
         <v>2110271</v>
@@ -4572,16 +4572,16 @@
         <v>43255</v>
       </c>
       <c r="B208" t="n">
-        <v>362.6858215332031</v>
+        <v>362.685791015625</v>
       </c>
       <c r="C208" t="n">
-        <v>362.6858215332031</v>
+        <v>362.685791015625</v>
       </c>
       <c r="D208" t="n">
-        <v>352.2928745305449</v>
+        <v>352.2928448874634</v>
       </c>
       <c r="E208" t="n">
-        <v>353.4318214169705</v>
+        <v>353.4317916780544</v>
       </c>
       <c r="F208" t="n">
         <v>242827</v>
@@ -4612,16 +4612,16 @@
         <v>43257</v>
       </c>
       <c r="B210" t="n">
-        <v>364.038330078125</v>
+        <v>364.0383605957031</v>
       </c>
       <c r="C210" t="n">
-        <v>364.2518684503623</v>
+        <v>364.2518989858415</v>
       </c>
       <c r="D210" t="n">
-        <v>352.5776063623812</v>
+        <v>352.5776359191992</v>
       </c>
       <c r="E210" t="n">
-        <v>352.71997472121</v>
+        <v>352.7200042899627</v>
       </c>
       <c r="F210" t="n">
         <v>162971</v>
@@ -4652,16 +4652,16 @@
         <v>43259</v>
       </c>
       <c r="B212" t="n">
-        <v>365.7467346191406</v>
+        <v>365.7467651367188</v>
       </c>
       <c r="C212" t="n">
-        <v>366.6009447352938</v>
+        <v>366.6009753241464</v>
       </c>
       <c r="D212" t="n">
-        <v>356.7063017251708</v>
+        <v>356.7063314884233</v>
       </c>
       <c r="E212" t="n">
-        <v>362.3298658225175</v>
+        <v>362.3298960549952</v>
       </c>
       <c r="F212" t="n">
         <v>293742</v>
@@ -4672,16 +4672,16 @@
         <v>43262</v>
       </c>
       <c r="B213" t="n">
-        <v>357.702880859375</v>
+        <v>357.7028503417969</v>
       </c>
       <c r="C213" t="n">
-        <v>374.4312614938604</v>
+        <v>374.4312295490931</v>
       </c>
       <c r="D213" t="n">
-        <v>352.3640251254714</v>
+        <v>352.3639950633801</v>
       </c>
       <c r="E213" t="n">
-        <v>368.7364990435695</v>
+        <v>368.7364675846534</v>
       </c>
       <c r="F213" t="n">
         <v>371642</v>
@@ -4792,16 +4792,16 @@
         <v>43270</v>
       </c>
       <c r="B219" t="n">
-        <v>347.9505920410156</v>
+        <v>347.9505615234375</v>
       </c>
       <c r="C219" t="n">
-        <v>353.2894479926347</v>
+        <v>353.2894170068034</v>
       </c>
       <c r="D219" t="n">
-        <v>344.8896581616116</v>
+        <v>344.8896279124976</v>
       </c>
       <c r="E219" t="n">
-        <v>348.7336321802163</v>
+        <v>348.7336015939604</v>
       </c>
       <c r="F219" t="n">
         <v>184986</v>
@@ -4852,16 +4852,16 @@
         <v>43273</v>
       </c>
       <c r="B222" t="n">
-        <v>334.6390380859375</v>
+        <v>334.6390075683594</v>
       </c>
       <c r="C222" t="n">
-        <v>342.3981841613412</v>
+        <v>342.3981529361638</v>
       </c>
       <c r="D222" t="n">
-        <v>332.5035127890446</v>
+        <v>332.5034824662168</v>
       </c>
       <c r="E222" t="n">
-        <v>340.9744722980687</v>
+        <v>340.9744412027275</v>
       </c>
       <c r="F222" t="n">
         <v>100487</v>
@@ -4912,16 +4912,16 @@
         <v>43278</v>
       </c>
       <c r="B225" t="n">
-        <v>339.1948547363281</v>
+        <v>339.19482421875</v>
       </c>
       <c r="C225" t="n">
-        <v>343.6795003712829</v>
+        <v>343.6794694502183</v>
       </c>
       <c r="D225" t="n">
-        <v>334.6390390906019</v>
+        <v>334.6390089829134</v>
       </c>
       <c r="E225" t="n">
-        <v>342.2558168357468</v>
+        <v>342.2557860427719</v>
       </c>
       <c r="F225" t="n">
         <v>83103</v>
@@ -4952,16 +4952,16 @@
         <v>43280</v>
       </c>
       <c r="B227" t="n">
-        <v>344.1778259277344</v>
+        <v>344.1778564453125</v>
       </c>
       <c r="C227" t="n">
-        <v>344.1778259277344</v>
+        <v>344.1778564453125</v>
       </c>
       <c r="D227" t="n">
-        <v>333.7136804379924</v>
+        <v>333.7137100277351</v>
       </c>
       <c r="E227" t="n">
-        <v>336.2763109669012</v>
+        <v>336.2763407838674</v>
       </c>
       <c r="F227" t="n">
         <v>190059</v>
@@ -4992,16 +4992,16 @@
         <v>43284</v>
       </c>
       <c r="B229" t="n">
-        <v>340.2626342773438</v>
+        <v>340.2626037597656</v>
       </c>
       <c r="C229" t="n">
-        <v>346.02859514043</v>
+        <v>346.0285641057126</v>
       </c>
       <c r="D229" t="n">
-        <v>340.2626342773438</v>
+        <v>340.2626037597656</v>
       </c>
       <c r="E229" t="n">
-        <v>343.5371347672956</v>
+        <v>343.5371039560331</v>
       </c>
       <c r="F229" t="n">
         <v>56719</v>
@@ -5012,16 +5012,16 @@
         <v>43285</v>
       </c>
       <c r="B230" t="n">
-        <v>335.92041015625</v>
+        <v>335.9203796386719</v>
       </c>
       <c r="C230" t="n">
-        <v>342.8253183679457</v>
+        <v>342.8252872230729</v>
       </c>
       <c r="D230" t="n">
-        <v>331.6493308673239</v>
+        <v>331.6493007377633</v>
       </c>
       <c r="E230" t="n">
-        <v>340.6897645574762</v>
+        <v>340.6897336066134</v>
       </c>
       <c r="F230" t="n">
         <v>63018</v>
@@ -5032,16 +5032,16 @@
         <v>43286</v>
       </c>
       <c r="B231" t="n">
-        <v>342.7541198730469</v>
+        <v>342.7540893554688</v>
       </c>
       <c r="C231" t="n">
-        <v>344.3202002219263</v>
+        <v>344.3201695649101</v>
       </c>
       <c r="D231" t="n">
-        <v>336.3475151083983</v>
+        <v>336.347485161241</v>
       </c>
       <c r="E231" t="n">
-        <v>336.3475151083983</v>
+        <v>336.347485161241</v>
       </c>
       <c r="F231" t="n">
         <v>66122</v>
@@ -5052,16 +5052,16 @@
         <v>43287</v>
       </c>
       <c r="B232" t="n">
-        <v>342.0422058105469</v>
+        <v>342.042236328125</v>
       </c>
       <c r="C232" t="n">
-        <v>346.6692191993917</v>
+        <v>346.6692501297997</v>
       </c>
       <c r="D232" t="n">
-        <v>340.1914174542131</v>
+        <v>340.1914478066608</v>
       </c>
       <c r="E232" t="n">
-        <v>341.0456274648287</v>
+        <v>341.0456578934904</v>
       </c>
       <c r="F232" t="n">
         <v>56875</v>
@@ -5072,16 +5072,16 @@
         <v>43291</v>
       </c>
       <c r="B233" t="n">
-        <v>351.5809936523438</v>
+        <v>351.5809631347656</v>
       </c>
       <c r="C233" t="n">
-        <v>352.2216654223892</v>
+        <v>352.2216348492001</v>
       </c>
       <c r="D233" t="n">
-        <v>341.7575203930438</v>
+        <v>341.7574907281528</v>
       </c>
       <c r="E233" t="n">
-        <v>341.7575203930438</v>
+        <v>341.7574907281528</v>
       </c>
       <c r="F233" t="n">
         <v>97553</v>
@@ -5092,16 +5092,16 @@
         <v>43292</v>
       </c>
       <c r="B234" t="n">
-        <v>354.2860412597656</v>
+        <v>354.2859802246094</v>
       </c>
       <c r="C234" t="n">
-        <v>360.5503059702509</v>
+        <v>360.5502438559091</v>
       </c>
       <c r="D234" t="n">
-        <v>348.9471850857865</v>
+        <v>348.9471249703897</v>
       </c>
       <c r="E234" t="n">
-        <v>348.9471850857865</v>
+        <v>348.9471249703897</v>
       </c>
       <c r="F234" t="n">
         <v>77299</v>
@@ -5212,16 +5212,16 @@
         <v>43300</v>
       </c>
       <c r="B240" t="n">
-        <v>382.048095703125</v>
+        <v>382.0480346679688</v>
       </c>
       <c r="C240" t="n">
-        <v>382.1192657241226</v>
+        <v>382.1192046775964</v>
       </c>
       <c r="D240" t="n">
-        <v>367.5976065790601</v>
+        <v>367.5975478524819</v>
       </c>
       <c r="E240" t="n">
-        <v>374.858421985584</v>
+        <v>374.8583620990341</v>
       </c>
       <c r="F240" t="n">
         <v>96340</v>
@@ -5232,16 +5232,16 @@
         <v>43301</v>
       </c>
       <c r="B241" t="n">
-        <v>385.6072387695312</v>
+        <v>385.6072692871094</v>
       </c>
       <c r="C241" t="n">
-        <v>392.8680812599695</v>
+        <v>392.8681123521824</v>
       </c>
       <c r="D241" t="n">
-        <v>382.1903983806284</v>
+        <v>382.1904286277923</v>
       </c>
       <c r="E241" t="n">
-        <v>382.9022401283165</v>
+        <v>382.9022704318167</v>
       </c>
       <c r="F241" t="n">
         <v>143200</v>
@@ -5252,16 +5252,16 @@
         <v>43304</v>
       </c>
       <c r="B242" t="n">
-        <v>387.0309753417969</v>
+        <v>387.0309448242188</v>
       </c>
       <c r="C242" t="n">
-        <v>388.0987521976024</v>
+        <v>388.0987215958296</v>
       </c>
       <c r="D242" t="n">
-        <v>379.9836990911014</v>
+        <v>379.9836691292044</v>
       </c>
       <c r="E242" t="n">
-        <v>384.183579836986</v>
+        <v>384.1835495439264</v>
       </c>
       <c r="F242" t="n">
         <v>54684</v>
@@ -5292,16 +5292,16 @@
         <v>43306</v>
       </c>
       <c r="B244" t="n">
-        <v>392.5833435058594</v>
+        <v>392.5834045410156</v>
       </c>
       <c r="C244" t="n">
-        <v>392.5833435058594</v>
+        <v>392.5834045410156</v>
       </c>
       <c r="D244" t="n">
-        <v>382.4039357112513</v>
+        <v>382.4039951638093</v>
       </c>
       <c r="E244" t="n">
-        <v>386.4614761601839</v>
+        <v>386.46153624357</v>
       </c>
       <c r="F244" t="n">
         <v>87563</v>
@@ -5312,16 +5312,16 @@
         <v>43307</v>
       </c>
       <c r="B245" t="n">
-        <v>380.8379211425781</v>
+        <v>380.837890625</v>
       </c>
       <c r="C245" t="n">
-        <v>395.5019475367201</v>
+        <v>395.5019158440737</v>
       </c>
       <c r="D245" t="n">
-        <v>379.5566058747826</v>
+        <v>379.5565754598798</v>
       </c>
       <c r="E245" t="n">
-        <v>393.010487016667</v>
+        <v>393.0104555236681</v>
       </c>
       <c r="F245" t="n">
         <v>118211</v>
@@ -5352,16 +5352,16 @@
         <v>43311</v>
       </c>
       <c r="B247" t="n">
-        <v>373.8617858886719</v>
+        <v>373.8617553710938</v>
       </c>
       <c r="C247" t="n">
-        <v>377.2074563295386</v>
+        <v>377.2074255388602</v>
       </c>
       <c r="D247" t="n">
-        <v>371.227957208414</v>
+        <v>371.22792690583</v>
       </c>
       <c r="E247" t="n">
-        <v>371.227957208414</v>
+        <v>371.22792690583</v>
       </c>
       <c r="F247" t="n">
         <v>72473</v>
@@ -5492,16 +5492,16 @@
         <v>43320</v>
       </c>
       <c r="B254" t="n">
-        <v>417.925048828125</v>
+        <v>417.9250793457031</v>
       </c>
       <c r="C254" t="n">
-        <v>423.8333773803702</v>
+        <v>423.8334083293842</v>
       </c>
       <c r="D254" t="n">
-        <v>403.6169316311468</v>
+        <v>403.6169611039226</v>
       </c>
       <c r="E254" t="n">
-        <v>405.6101167043417</v>
+        <v>405.6101463226631</v>
       </c>
       <c r="F254" t="n">
         <v>155172</v>
@@ -5512,16 +5512,16 @@
         <v>43321</v>
       </c>
       <c r="B255" t="n">
-        <v>413.5828247070312</v>
+        <v>413.5828552246094</v>
       </c>
       <c r="C255" t="n">
-        <v>422.2673505408872</v>
+        <v>422.2673816992818</v>
       </c>
       <c r="D255" t="n">
-        <v>412.0167445575103</v>
+        <v>412.01677495953</v>
       </c>
       <c r="E255" t="n">
-        <v>413.9387314086429</v>
+        <v>413.9387619524828</v>
       </c>
       <c r="F255" t="n">
         <v>86363</v>
@@ -5532,16 +5532,16 @@
         <v>43322</v>
       </c>
       <c r="B256" t="n">
-        <v>411.447265625</v>
+        <v>411.4473266601562</v>
       </c>
       <c r="C256" t="n">
-        <v>419.5623179613181</v>
+        <v>419.5623802002823</v>
       </c>
       <c r="D256" t="n">
-        <v>410.0235821737193</v>
+        <v>410.0236429976827</v>
       </c>
       <c r="E256" t="n">
-        <v>413.5828191339301</v>
+        <v>413.5828804858799</v>
       </c>
       <c r="F256" t="n">
         <v>87106</v>
@@ -5612,16 +5612,16 @@
         <v>43328</v>
       </c>
       <c r="B260" t="n">
-        <v>423.5487365722656</v>
+        <v>423.5487060546875</v>
       </c>
       <c r="C260" t="n">
-        <v>426.253763951018</v>
+        <v>426.2537332385369</v>
       </c>
       <c r="D260" t="n">
-        <v>417.7116050341322</v>
+        <v>417.7115749371317</v>
       </c>
       <c r="E260" t="n">
-        <v>426.253763951018</v>
+        <v>426.2537332385369</v>
       </c>
       <c r="F260" t="n">
         <v>68717</v>
@@ -5652,16 +5652,16 @@
         <v>43332</v>
       </c>
       <c r="B262" t="n">
-        <v>426.0401916503906</v>
+        <v>426.0401611328125</v>
       </c>
       <c r="C262" t="n">
-        <v>428.5316522741929</v>
+        <v>428.5316215781496</v>
       </c>
       <c r="D262" t="n">
-        <v>413.4405201623625</v>
+        <v>413.4404905473083</v>
       </c>
       <c r="E262" t="n">
-        <v>419.9183234506511</v>
+        <v>419.918293371587</v>
       </c>
       <c r="F262" t="n">
         <v>76842</v>
@@ -5732,16 +5732,16 @@
         <v>43336</v>
       </c>
       <c r="B266" t="n">
-        <v>405.7525634765625</v>
+        <v>405.7525329589844</v>
       </c>
       <c r="C266" t="n">
-        <v>415.2201023253259</v>
+        <v>415.2200710956725</v>
       </c>
       <c r="D266" t="n">
-        <v>402.9051678210174</v>
+        <v>402.9051375175985</v>
       </c>
       <c r="E266" t="n">
-        <v>408.3863924168361</v>
+        <v>408.3863617011617</v>
       </c>
       <c r="F266" t="n">
         <v>110243</v>
@@ -5812,16 +5812,16 @@
         <v>43342</v>
       </c>
       <c r="B270" t="n">
-        <v>420.0606384277344</v>
+        <v>420.0606689453125</v>
       </c>
       <c r="C270" t="n">
-        <v>423.0503737970776</v>
+        <v>423.0504045318613</v>
       </c>
       <c r="D270" t="n">
-        <v>416.8573080339942</v>
+        <v>416.8573383188491</v>
       </c>
       <c r="E270" t="n">
-        <v>419.5623350335054</v>
+        <v>419.5623655148816</v>
       </c>
       <c r="F270" t="n">
         <v>65848</v>
@@ -5832,16 +5832,16 @@
         <v>43343</v>
       </c>
       <c r="B271" t="n">
-        <v>423.12158203125</v>
+        <v>423.1215515136719</v>
       </c>
       <c r="C271" t="n">
-        <v>425.6130423966255</v>
+        <v>425.6130116993512</v>
       </c>
       <c r="D271" t="n">
-        <v>416.928516123371</v>
+        <v>416.9284860524667</v>
       </c>
       <c r="E271" t="n">
-        <v>423.4774887508689</v>
+        <v>423.4774582076211</v>
       </c>
       <c r="F271" t="n">
         <v>65300</v>
@@ -5852,16 +5852,16 @@
         <v>43346</v>
       </c>
       <c r="B272" t="n">
-        <v>423.5487365722656</v>
+        <v>423.5487060546875</v>
       </c>
       <c r="C272" t="n">
-        <v>430.2400783356848</v>
+        <v>430.2400473359814</v>
       </c>
       <c r="D272" t="n">
-        <v>420.3454340614369</v>
+        <v>420.3454037746636</v>
       </c>
       <c r="E272" t="n">
-        <v>422.8368947178608</v>
+        <v>422.8368642515724</v>
       </c>
       <c r="F272" t="n">
         <v>33765</v>
@@ -5892,16 +5892,16 @@
         <v>43348</v>
       </c>
       <c r="B274" t="n">
-        <v>446.3989868164062</v>
+        <v>446.3989562988281</v>
       </c>
       <c r="C274" t="n">
-        <v>446.8972619159915</v>
+        <v>446.8972313643494</v>
       </c>
       <c r="D274" t="n">
-        <v>425.3283276399078</v>
+        <v>425.3282985628022</v>
       </c>
       <c r="E274" t="n">
-        <v>426.9655779642857</v>
+        <v>426.9655487752514</v>
       </c>
       <c r="F274" t="n">
         <v>107452</v>
@@ -5912,16 +5912,16 @@
         <v>43349</v>
       </c>
       <c r="B275" t="n">
-        <v>466.6865844726562</v>
+        <v>466.6865539550781</v>
       </c>
       <c r="C275" t="n">
-        <v>469.462781562717</v>
+        <v>469.4627508635978</v>
       </c>
       <c r="D275" t="n">
-        <v>448.5344917059376</v>
+        <v>448.5344623753615</v>
       </c>
       <c r="E275" t="n">
-        <v>448.5344917059376</v>
+        <v>448.5344623753615</v>
       </c>
       <c r="F275" t="n">
         <v>140070</v>
@@ -5952,16 +5952,16 @@
         <v>43354</v>
       </c>
       <c r="B277" t="n">
-        <v>454.3004150390625</v>
+        <v>454.3004455566406</v>
       </c>
       <c r="C277" t="n">
-        <v>461.6324272177329</v>
+        <v>461.6324582278381</v>
       </c>
       <c r="D277" t="n">
-        <v>452.236059895009</v>
+        <v>452.2360902739143</v>
       </c>
       <c r="E277" t="n">
-        <v>461.2053221877918</v>
+        <v>461.2053531692062</v>
       </c>
       <c r="F277" t="n">
         <v>57280</v>
@@ -5972,16 +5972,16 @@
         <v>43355</v>
       </c>
       <c r="B278" t="n">
-        <v>449.5310668945312</v>
+        <v>449.5310974121094</v>
       </c>
       <c r="C278" t="n">
-        <v>459.1409726842791</v>
+        <v>459.1410038542505</v>
       </c>
       <c r="D278" t="n">
-        <v>448.3920918020204</v>
+        <v>448.3921222422763</v>
       </c>
       <c r="E278" t="n">
-        <v>459.0698026777523</v>
+        <v>459.0698338428921</v>
       </c>
       <c r="F278" t="n">
         <v>50876</v>
@@ -5992,16 +5992,16 @@
         <v>43356</v>
       </c>
       <c r="B279" t="n">
-        <v>446.3989868164062</v>
+        <v>446.3989562988281</v>
       </c>
       <c r="C279" t="n">
-        <v>452.7344214055155</v>
+        <v>452.7343904548224</v>
       </c>
       <c r="D279" t="n">
-        <v>443.4804212376504</v>
+        <v>443.4803909195968</v>
       </c>
       <c r="E279" t="n">
-        <v>448.2497755171743</v>
+        <v>448.2497448730691</v>
       </c>
       <c r="F279" t="n">
         <v>76764</v>
@@ -6052,16 +6052,16 @@
         <v>43361</v>
       </c>
       <c r="B282" t="n">
-        <v>439.0669860839844</v>
+        <v>439.0669250488281</v>
       </c>
       <c r="C282" t="n">
-        <v>450.5988803627721</v>
+        <v>450.5988177245553</v>
       </c>
       <c r="D282" t="n">
-        <v>437.0738006333705</v>
+        <v>437.073739875289</v>
       </c>
       <c r="E282" t="n">
-        <v>450.4565119971577</v>
+        <v>450.4564493787317</v>
       </c>
       <c r="F282" t="n">
         <v>72004</v>
@@ -6072,16 +6072,16 @@
         <v>43362</v>
       </c>
       <c r="B283" t="n">
-        <v>443.622802734375</v>
+        <v>443.6228332519531</v>
       </c>
       <c r="C283" t="n">
-        <v>446.1854333190072</v>
+        <v>446.1854640128731</v>
       </c>
       <c r="D283" t="n">
-        <v>434.5111423263101</v>
+        <v>434.5111722170814</v>
       </c>
       <c r="E283" t="n">
-        <v>434.5111423263101</v>
+        <v>434.5111722170814</v>
       </c>
       <c r="F283" t="n">
         <v>53158</v>
@@ -6092,16 +6092,16 @@
         <v>43363</v>
       </c>
       <c r="B284" t="n">
-        <v>447.9649658203125</v>
+        <v>447.9650573730469</v>
       </c>
       <c r="C284" t="n">
-        <v>451.6665709508681</v>
+        <v>451.6666632601172</v>
       </c>
       <c r="D284" t="n">
-        <v>442.7684789704933</v>
+        <v>442.7685694611969</v>
       </c>
       <c r="E284" t="n">
-        <v>445.9718090826328</v>
+        <v>445.9719002280163</v>
       </c>
       <c r="F284" t="n">
         <v>54997</v>
@@ -6132,16 +6132,16 @@
         <v>43367</v>
       </c>
       <c r="B286" t="n">
-        <v>455.581787109375</v>
+        <v>455.5817565917969</v>
       </c>
       <c r="C286" t="n">
-        <v>472.5949337572724</v>
+        <v>472.5949021000526</v>
       </c>
       <c r="D286" t="n">
-        <v>452.0937480959283</v>
+        <v>452.0937178119998</v>
       </c>
       <c r="E286" t="n">
-        <v>465.618827398367</v>
+        <v>465.6187962084482</v>
       </c>
       <c r="F286" t="n">
         <v>114729</v>
@@ -6192,16 +6192,16 @@
         <v>43370</v>
       </c>
       <c r="B289" t="n">
-        <v>464.8358154296875</v>
+        <v>464.8357238769531</v>
       </c>
       <c r="C289" t="n">
-        <v>470.4593798581377</v>
+        <v>470.4592871978021</v>
       </c>
       <c r="D289" t="n">
-        <v>462.7002616815574</v>
+        <v>462.7001705494355</v>
       </c>
       <c r="E289" t="n">
-        <v>466.9001708312743</v>
+        <v>466.9000788719504</v>
       </c>
       <c r="F289" t="n">
         <v>111443</v>
@@ -6212,16 +6212,16 @@
         <v>43371</v>
       </c>
       <c r="B290" t="n">
-        <v>473.0220031738281</v>
+        <v>473.0220336914062</v>
       </c>
       <c r="C290" t="n">
-        <v>474.7304517104602</v>
+        <v>474.7304823382609</v>
       </c>
       <c r="D290" t="n">
-        <v>462.7002269408786</v>
+        <v>462.7002567925351</v>
       </c>
       <c r="E290" t="n">
-        <v>463.7680037347724</v>
+        <v>463.7680336553177</v>
       </c>
       <c r="F290" t="n">
         <v>82437</v>
@@ -6232,16 +6232,16 @@
         <v>43374</v>
       </c>
       <c r="B291" t="n">
-        <v>469.8187561035156</v>
+        <v>469.8187255859375</v>
       </c>
       <c r="C291" t="n">
-        <v>479.7846267927382</v>
+        <v>479.7845956278163</v>
       </c>
       <c r="D291" t="n">
-        <v>464.835834924911</v>
+        <v>464.8358047310038</v>
       </c>
       <c r="E291" t="n">
-        <v>476.9372027878022</v>
+        <v>476.9371718078378</v>
       </c>
       <c r="F291" t="n">
         <v>76882</v>
@@ -6252,16 +6252,16 @@
         <v>43375</v>
       </c>
       <c r="B292" t="n">
-        <v>478.7168579101562</v>
+        <v>478.716796875</v>
       </c>
       <c r="C292" t="n">
-        <v>484.0556859299913</v>
+        <v>484.0556242141483</v>
       </c>
       <c r="D292" t="n">
-        <v>474.3033817936307</v>
+        <v>474.3033213211812</v>
       </c>
       <c r="E292" t="n">
-        <v>476.2253972790296</v>
+        <v>476.2253365615281</v>
       </c>
       <c r="F292" t="n">
         <v>103031</v>
@@ -6272,16 +6272,16 @@
         <v>43376</v>
       </c>
       <c r="B293" t="n">
-        <v>462.3443603515625</v>
+        <v>462.3442993164062</v>
       </c>
       <c r="C293" t="n">
-        <v>486.9030304181649</v>
+        <v>486.9029661409614</v>
       </c>
       <c r="D293" t="n">
-        <v>459.1410296919073</v>
+        <v>459.1409690796302</v>
       </c>
       <c r="E293" t="n">
-        <v>484.8387033244498</v>
+        <v>484.838639319763</v>
       </c>
       <c r="F293" t="n">
         <v>143969</v>
@@ -6292,16 +6292,16 @@
         <v>43377</v>
       </c>
       <c r="B294" t="n">
-        <v>455.581787109375</v>
+        <v>455.5817565917969</v>
       </c>
       <c r="C294" t="n">
-        <v>472.8085004649586</v>
+        <v>472.8084687934327</v>
       </c>
       <c r="D294" t="n">
-        <v>446.4701553336692</v>
+        <v>446.4701254264423</v>
       </c>
       <c r="E294" t="n">
-        <v>463.4121036350006</v>
+        <v>463.4120725929013</v>
       </c>
       <c r="F294" t="n">
         <v>143591</v>
@@ -6312,16 +6312,16 @@
         <v>43378</v>
       </c>
       <c r="B295" t="n">
-        <v>455.1546325683594</v>
+        <v>455.1546630859375</v>
       </c>
       <c r="C295" t="n">
-        <v>463.6256199645633</v>
+        <v>463.6256510501111</v>
       </c>
       <c r="D295" t="n">
-        <v>441.4160163831015</v>
+        <v>441.4160459795217</v>
       </c>
       <c r="E295" t="n">
-        <v>456.3647776723898</v>
+        <v>456.3648082711067</v>
       </c>
       <c r="F295" t="n">
         <v>188272</v>
@@ -6372,16 +6372,16 @@
         <v>43383</v>
       </c>
       <c r="B298" t="n">
-        <v>438.7109985351562</v>
+        <v>438.7110290527344</v>
       </c>
       <c r="C298" t="n">
-        <v>442.7685106359028</v>
+        <v>442.7685414357292</v>
       </c>
       <c r="D298" t="n">
-        <v>431.0230510474159</v>
+        <v>431.0230810302057</v>
       </c>
       <c r="E298" t="n">
-        <v>433.3009729568244</v>
+        <v>433.3010030980707</v>
       </c>
       <c r="F298" t="n">
         <v>196176</v>
@@ -6392,16 +6392,16 @@
         <v>43384</v>
       </c>
       <c r="B299" t="n">
-        <v>450.0293579101562</v>
+        <v>450.0293884277344</v>
       </c>
       <c r="C299" t="n">
-        <v>450.5276613015677</v>
+        <v>450.527691852937</v>
       </c>
       <c r="D299" t="n">
-        <v>437.7855948041388</v>
+        <v>437.7856244914378</v>
       </c>
       <c r="E299" t="n">
-        <v>438.7822015869618</v>
+        <v>438.782231341843</v>
       </c>
       <c r="F299" t="n">
         <v>120559</v>
@@ -6432,16 +6432,16 @@
         <v>43389</v>
       </c>
       <c r="B301" t="n">
-        <v>473.8761901855469</v>
+        <v>473.876220703125</v>
       </c>
       <c r="C301" t="n">
-        <v>477.7913337963705</v>
+        <v>477.7913645660835</v>
       </c>
       <c r="D301" t="n">
-        <v>447.5378766556197</v>
+        <v>447.5379054770132</v>
       </c>
       <c r="E301" t="n">
-        <v>458.3579557536917</v>
+        <v>458.3579852718972</v>
       </c>
       <c r="F301" t="n">
         <v>117924</v>
@@ -6452,16 +6452,16 @@
         <v>43390</v>
       </c>
       <c r="B302" t="n">
-        <v>491.3164367675781</v>
+        <v>491.31640625</v>
       </c>
       <c r="C302" t="n">
-        <v>494.3774271396515</v>
+        <v>494.3773964319433</v>
       </c>
       <c r="D302" t="n">
-        <v>464.9069518694333</v>
+        <v>464.9069229922511</v>
       </c>
       <c r="E302" t="n">
-        <v>469.10686071584</v>
+        <v>469.1068315777851</v>
       </c>
       <c r="F302" t="n">
         <v>187503</v>
@@ -6472,16 +6472,16 @@
         <v>43391</v>
       </c>
       <c r="B303" t="n">
-        <v>493.8791809082031</v>
+        <v>493.8790588378906</v>
       </c>
       <c r="C303" t="n">
-        <v>498.2214586079846</v>
+        <v>498.2213354644072</v>
       </c>
       <c r="D303" t="n">
-        <v>489.4657331907928</v>
+        <v>489.4656122113361</v>
       </c>
       <c r="E303" t="n">
-        <v>492.3131005362102</v>
+        <v>492.3129788529801</v>
       </c>
       <c r="F303" t="n">
         <v>132636</v>
@@ -6492,16 +6492,16 @@
         <v>43392</v>
       </c>
       <c r="B304" t="n">
-        <v>491.174072265625</v>
+        <v>491.1741333007812</v>
       </c>
       <c r="C304" t="n">
-        <v>496.2993893027132</v>
+        <v>496.2994509747608</v>
       </c>
       <c r="D304" t="n">
-        <v>484.4115051100238</v>
+        <v>484.4115653048377</v>
       </c>
       <c r="E304" t="n">
-        <v>491.174072265625</v>
+        <v>491.1741333007812</v>
       </c>
       <c r="F304" t="n">
         <v>87498</v>
@@ -6512,16 +6512,16 @@
         <v>43395</v>
       </c>
       <c r="B305" t="n">
-        <v>489.1098022460938</v>
+        <v>489.1096496582031</v>
       </c>
       <c r="C305" t="n">
-        <v>497.1537146929717</v>
+        <v>497.1535595956167</v>
       </c>
       <c r="D305" t="n">
-        <v>487.1878149943316</v>
+        <v>487.1876630060445</v>
       </c>
       <c r="E305" t="n">
-        <v>496.7265812307887</v>
+        <v>496.7264262666868</v>
       </c>
       <c r="F305" t="n">
         <v>60501</v>
@@ -6572,16 +6572,16 @@
         <v>43398</v>
       </c>
       <c r="B308" t="n">
-        <v>497.2247924804688</v>
+        <v>497.2247619628906</v>
       </c>
       <c r="C308" t="n">
-        <v>503.5602265674268</v>
+        <v>503.5601956610062</v>
       </c>
       <c r="D308" t="n">
-        <v>489.6792415818524</v>
+        <v>489.6792115273886</v>
       </c>
       <c r="E308" t="n">
-        <v>496.7976590975188</v>
+        <v>496.7976286061563</v>
       </c>
       <c r="F308" t="n">
         <v>118198</v>
@@ -6592,16 +6592,16 @@
         <v>43399</v>
       </c>
       <c r="B309" t="n">
-        <v>491.885986328125</v>
+        <v>491.8860168457031</v>
       </c>
       <c r="C309" t="n">
-        <v>494.3062200555082</v>
+        <v>494.3062507232424</v>
       </c>
       <c r="D309" t="n">
-        <v>475.3711436536239</v>
+        <v>475.3711731465886</v>
       </c>
       <c r="E309" t="n">
-        <v>489.8216026618011</v>
+        <v>489.8216330513008</v>
       </c>
       <c r="F309" t="n">
         <v>181243</v>
@@ -6612,16 +6612,16 @@
         <v>43402</v>
       </c>
       <c r="B310" t="n">
-        <v>484.2692260742188</v>
+        <v>484.2691955566406</v>
       </c>
       <c r="C310" t="n">
-        <v>487.9708034764029</v>
+        <v>487.9707727255595</v>
       </c>
       <c r="D310" t="n">
-        <v>477.4354880523159</v>
+        <v>477.4354579653848</v>
       </c>
       <c r="E310" t="n">
-        <v>479.4998717938601</v>
+        <v>479.4998415768361</v>
       </c>
       <c r="F310" t="n">
         <v>124850</v>
@@ -6632,16 +6632,16 @@
         <v>43403</v>
       </c>
       <c r="B311" t="n">
-        <v>507.6889038085938</v>
+        <v>507.68896484375</v>
       </c>
       <c r="C311" t="n">
-        <v>511.4617073428208</v>
+        <v>511.4617688315493</v>
       </c>
       <c r="D311" t="n">
-        <v>479.7845389826546</v>
+        <v>479.7845966631043</v>
       </c>
       <c r="E311" t="n">
-        <v>491.5299696122788</v>
+        <v>491.5300287047826</v>
       </c>
       <c r="F311" t="n">
         <v>130875</v>
@@ -6652,16 +6652,16 @@
         <v>43404</v>
       </c>
       <c r="B312" t="n">
-        <v>515.803955078125</v>
+        <v>515.8040161132812</v>
       </c>
       <c r="C312" t="n">
-        <v>520.003892191256</v>
+        <v>520.0039537233914</v>
       </c>
       <c r="D312" t="n">
-        <v>508.9702743462901</v>
+        <v>508.9703345728159</v>
       </c>
       <c r="E312" t="n">
-        <v>508.9702743462901</v>
+        <v>508.9703345728159</v>
       </c>
       <c r="F312" t="n">
         <v>139717</v>
@@ -6672,16 +6672,16 @@
         <v>43405</v>
       </c>
       <c r="B313" t="n">
-        <v>494.0215148925781</v>
+        <v>494.0215454101562</v>
       </c>
       <c r="C313" t="n">
-        <v>500.1433829422568</v>
+        <v>500.1434138380059</v>
       </c>
       <c r="D313" t="n">
-        <v>485.9064897255199</v>
+        <v>485.9065197418022</v>
       </c>
       <c r="E313" t="n">
-        <v>491.174147582036</v>
+        <v>491.1741779237214</v>
       </c>
       <c r="F313" t="n">
         <v>268389</v>
@@ -6712,16 +6712,16 @@
         <v>43410</v>
       </c>
       <c r="B315" t="n">
-        <v>485.4792785644531</v>
+        <v>485.4793090820312</v>
       </c>
       <c r="C315" t="n">
-        <v>488.3267020831064</v>
+        <v>488.3267327796756</v>
       </c>
       <c r="D315" t="n">
-        <v>480.5675282421928</v>
+        <v>480.5675584510147</v>
       </c>
       <c r="E315" t="n">
-        <v>487.6148320374388</v>
+        <v>487.6148626892594</v>
       </c>
       <c r="F315" t="n">
         <v>70726</v>
@@ -6732,16 +6732,16 @@
         <v>43411</v>
       </c>
       <c r="B316" t="n">
-        <v>466.1882934570312</v>
+        <v>466.1882629394531</v>
       </c>
       <c r="C316" t="n">
-        <v>486.9030171658662</v>
+        <v>486.9029852922626</v>
       </c>
       <c r="D316" t="n">
-        <v>458.4291754008993</v>
+        <v>458.429145391248</v>
       </c>
       <c r="E316" t="n">
-        <v>486.9030171658662</v>
+        <v>486.9029852922626</v>
       </c>
       <c r="F316" t="n">
         <v>167692</v>
@@ -6752,16 +6752,16 @@
         <v>43412</v>
       </c>
       <c r="B317" t="n">
-        <v>482.6458129882812</v>
+        <v>482.645751953125</v>
       </c>
       <c r="C317" t="n">
-        <v>483.2922522215034</v>
+        <v>483.2921911045988</v>
       </c>
       <c r="D317" t="n">
-        <v>467.5631456252964</v>
+        <v>467.563086497487</v>
       </c>
       <c r="E317" t="n">
-        <v>468.1377201626522</v>
+        <v>468.1376609621825</v>
       </c>
       <c r="F317" t="n">
         <v>149747</v>
@@ -6812,16 +6812,16 @@
         <v>43417</v>
       </c>
       <c r="B320" t="n">
-        <v>509.9382629394531</v>
+        <v>509.9383239746094</v>
       </c>
       <c r="C320" t="n">
-        <v>514.8939533581685</v>
+        <v>514.8940149864776</v>
       </c>
       <c r="D320" t="n">
-        <v>495.1428276830607</v>
+        <v>495.1428869473325</v>
       </c>
       <c r="E320" t="n">
-        <v>497.2257029767771</v>
+        <v>497.225762490351</v>
       </c>
       <c r="F320" t="n">
         <v>127693</v>
@@ -6832,16 +6832,16 @@
         <v>43418</v>
       </c>
       <c r="B321" t="n">
-        <v>512.4521484375</v>
+        <v>512.4520874023438</v>
       </c>
       <c r="C321" t="n">
-        <v>512.8830507869616</v>
+        <v>512.8829897004831</v>
       </c>
       <c r="D321" t="n">
-        <v>503.8334725606678</v>
+        <v>503.8334125520312</v>
       </c>
       <c r="E321" t="n">
-        <v>509.938370355574</v>
+        <v>509.938309619819</v>
       </c>
       <c r="F321" t="n">
         <v>103291</v>
@@ -6872,16 +6872,16 @@
         <v>43423</v>
       </c>
       <c r="B323" t="n">
-        <v>523.5126342773438</v>
+        <v>523.5126953125</v>
       </c>
       <c r="C323" t="n">
-        <v>523.5844989643908</v>
+        <v>523.5845600079256</v>
       </c>
       <c r="D323" t="n">
-        <v>515.7558789749485</v>
+        <v>515.7559391057621</v>
       </c>
       <c r="E323" t="n">
-        <v>519.2751332914713</v>
+        <v>519.275193832587</v>
       </c>
       <c r="F323" t="n">
         <v>66070</v>
@@ -6932,16 +6932,16 @@
         <v>43427</v>
       </c>
       <c r="B326" t="n">
-        <v>531.700439453125</v>
+        <v>531.7005615234375</v>
       </c>
       <c r="C326" t="n">
-        <v>540.8218811494445</v>
+        <v>540.8220053139009</v>
       </c>
       <c r="D326" t="n">
-        <v>528.6120872077179</v>
+        <v>528.6122085689917</v>
       </c>
       <c r="E326" t="n">
-        <v>531.5567672416307</v>
+        <v>531.5568892789582</v>
       </c>
       <c r="F326" t="n">
         <v>87641</v>
@@ -6992,16 +6992,16 @@
         <v>43432</v>
       </c>
       <c r="B329" t="n">
-        <v>545.8494262695312</v>
+        <v>545.8494873046875</v>
       </c>
       <c r="C329" t="n">
-        <v>551.8825156058812</v>
+        <v>551.8825773156384</v>
       </c>
       <c r="D329" t="n">
-        <v>542.3301146280619</v>
+        <v>542.3301752696999</v>
       </c>
       <c r="E329" t="n">
-        <v>548.7222987289401</v>
+        <v>548.722360085332</v>
       </c>
       <c r="F329" t="n">
         <v>68365</v>
@@ -7152,16 +7152,16 @@
         <v>43444</v>
       </c>
       <c r="B337" t="n">
-        <v>540.1036987304688</v>
+        <v>540.1036376953125</v>
       </c>
       <c r="C337" t="n">
-        <v>547.5732253275535</v>
+        <v>547.5731634482931</v>
       </c>
       <c r="D337" t="n">
-        <v>539.8882189733723</v>
+        <v>539.8881579625667</v>
       </c>
       <c r="E337" t="n">
-        <v>545.8495016139799</v>
+        <v>545.8494399295113</v>
       </c>
       <c r="F337" t="n">
         <v>67100</v>
@@ -7172,16 +7172,16 @@
         <v>43445</v>
       </c>
       <c r="B338" t="n">
-        <v>541.5401000976562</v>
+        <v>541.5401611328125</v>
       </c>
       <c r="C338" t="n">
-        <v>544.9157397777561</v>
+        <v>544.9158011933694</v>
       </c>
       <c r="D338" t="n">
-        <v>530.5513192563691</v>
+        <v>530.5513790530169</v>
       </c>
       <c r="E338" t="n">
-        <v>544.9157397777561</v>
+        <v>544.9158011933694</v>
       </c>
       <c r="F338" t="n">
         <v>121498</v>
@@ -7192,16 +7192,16 @@
         <v>43446</v>
       </c>
       <c r="B339" t="n">
-        <v>543.335693359375</v>
+        <v>543.3356323242188</v>
       </c>
       <c r="C339" t="n">
-        <v>550.7333548450068</v>
+        <v>550.7332929788405</v>
       </c>
       <c r="D339" t="n">
-        <v>539.4572866336977</v>
+        <v>539.457226034219</v>
       </c>
       <c r="E339" t="n">
-        <v>541.5401050455487</v>
+        <v>541.5400442120983</v>
       </c>
       <c r="F339" t="n">
         <v>122528</v>
@@ -7212,16 +7212,16 @@
         <v>43447</v>
       </c>
       <c r="B340" t="n">
-        <v>545.8494262695312</v>
+        <v>545.8494873046875</v>
       </c>
       <c r="C340" t="n">
-        <v>547.2140549806483</v>
+        <v>547.214116168393</v>
       </c>
       <c r="D340" t="n">
-        <v>535.2915485167144</v>
+        <v>535.2916083713222</v>
       </c>
       <c r="E340" t="n">
-        <v>544.4129900398268</v>
+        <v>544.4130509143653</v>
       </c>
       <c r="F340" t="n">
         <v>85033</v>
@@ -7232,16 +7232,16 @@
         <v>43448</v>
       </c>
       <c r="B341" t="n">
-        <v>551.5234375</v>
+        <v>551.5233764648438</v>
       </c>
       <c r="C341" t="n">
-        <v>553.6063131905911</v>
+        <v>553.6062519249303</v>
       </c>
       <c r="D341" t="n">
-        <v>540.8937508056421</v>
+        <v>540.8936909468359</v>
       </c>
       <c r="E341" t="n">
-        <v>542.5456669838354</v>
+        <v>542.5456069422175</v>
       </c>
       <c r="F341" t="n">
         <v>76086</v>
@@ -7332,16 +7332,16 @@
         <v>43455</v>
       </c>
       <c r="B346" t="n">
-        <v>580.3240966796875</v>
+        <v>580.3241577148438</v>
       </c>
       <c r="C346" t="n">
-        <v>582.9814892844923</v>
+        <v>582.9815505991379</v>
       </c>
       <c r="D346" t="n">
-        <v>570.2689863816593</v>
+        <v>570.2690463592767</v>
       </c>
       <c r="E346" t="n">
-        <v>577.7385115900315</v>
+        <v>577.7385723532508</v>
       </c>
       <c r="F346" t="n">
         <v>378071</v>
@@ -7352,16 +7352,16 @@
         <v>43460</v>
       </c>
       <c r="B347" t="n">
-        <v>579.6058959960938</v>
+        <v>579.60595703125</v>
       </c>
       <c r="C347" t="n">
-        <v>586.5726548079504</v>
+        <v>586.5727165767382</v>
       </c>
       <c r="D347" t="n">
-        <v>573.5009989491645</v>
+        <v>573.501059341447</v>
       </c>
       <c r="E347" t="n">
-        <v>576.6612159254906</v>
+        <v>576.6612766505585</v>
       </c>
       <c r="F347" t="n">
         <v>118120</v>
@@ -7392,16 +7392,16 @@
         <v>43462</v>
       </c>
       <c r="B349" t="n">
-        <v>599.4288940429688</v>
+        <v>599.4288330078125</v>
       </c>
       <c r="C349" t="n">
-        <v>601.583519890837</v>
+        <v>601.5834586362921</v>
       </c>
       <c r="D349" t="n">
-        <v>579.7495739531772</v>
+        <v>579.7495149218122</v>
       </c>
       <c r="E349" t="n">
-        <v>583.5561158264204</v>
+        <v>583.556056407465</v>
       </c>
       <c r="F349" t="n">
         <v>152029</v>
@@ -7512,16 +7512,16 @@
         <v>43474</v>
       </c>
       <c r="B355" t="n">
-        <v>594.5449829101562</v>
+        <v>594.5450439453125</v>
       </c>
       <c r="C355" t="n">
-        <v>600.5780727945665</v>
+        <v>600.5781344490714</v>
       </c>
       <c r="D355" t="n">
-        <v>591.8157252399899</v>
+        <v>591.8157859949644</v>
       </c>
       <c r="E355" t="n">
-        <v>600.5062080978595</v>
+        <v>600.5062697449869</v>
       </c>
       <c r="F355" t="n">
         <v>147321</v>
@@ -7572,16 +7572,16 @@
         <v>43479</v>
       </c>
       <c r="B358" t="n">
-        <v>568.1143188476562</v>
+        <v>568.1143798828125</v>
       </c>
       <c r="C358" t="n">
-        <v>581.5450687782884</v>
+        <v>581.5451312563724</v>
       </c>
       <c r="D358" t="n">
-        <v>562.3685168777156</v>
+        <v>562.3685772955737</v>
       </c>
       <c r="E358" t="n">
-        <v>571.4181506925029</v>
+        <v>571.4182120826051</v>
       </c>
       <c r="F358" t="n">
         <v>172283</v>
@@ -7652,16 +7652,16 @@
         <v>43483</v>
       </c>
       <c r="B362" t="n">
-        <v>619.1799926757812</v>
+        <v>619.1800537109375</v>
       </c>
       <c r="C362" t="n">
-        <v>619.8981822009272</v>
+        <v>619.8982433068784</v>
       </c>
       <c r="D362" t="n">
-        <v>597.4177981065877</v>
+        <v>597.4178569965536</v>
       </c>
       <c r="E362" t="n">
-        <v>603.2354076839059</v>
+        <v>603.2354671473379</v>
       </c>
       <c r="F362" t="n">
         <v>144739</v>
@@ -7672,16 +7672,16 @@
         <v>43486</v>
       </c>
       <c r="B363" t="n">
-        <v>618.0308837890625</v>
+        <v>618.0308227539062</v>
       </c>
       <c r="C363" t="n">
-        <v>621.76567572531</v>
+        <v>621.7656143213152</v>
       </c>
       <c r="D363" t="n">
-        <v>613.8652466758325</v>
+        <v>613.865186052064</v>
       </c>
       <c r="E363" t="n">
-        <v>619.3955127075068</v>
+        <v>619.3954515375832</v>
       </c>
       <c r="F363" t="n">
         <v>36712</v>
@@ -7692,16 +7692,16 @@
         <v>43487</v>
       </c>
       <c r="B364" t="n">
-        <v>621.9091796875</v>
+        <v>621.9092407226562</v>
       </c>
       <c r="C364" t="n">
-        <v>624.4948220034996</v>
+        <v>624.4948832924149</v>
       </c>
       <c r="D364" t="n">
-        <v>614.2242317709398</v>
+        <v>614.224292051883</v>
       </c>
       <c r="E364" t="n">
-        <v>618.3181177949477</v>
+        <v>618.3181784776715</v>
       </c>
       <c r="F364" t="n">
         <v>56158</v>
@@ -7712,16 +7712,16 @@
         <v>43488</v>
       </c>
       <c r="B365" t="n">
-        <v>621.3345947265625</v>
+        <v>621.3346557617188</v>
       </c>
       <c r="C365" t="n">
-        <v>624.2075242323521</v>
+        <v>624.2075855497229</v>
       </c>
       <c r="D365" t="n">
-        <v>616.0197523224966</v>
+        <v>616.0198128355635</v>
       </c>
       <c r="E365" t="n">
-        <v>621.3345947265625</v>
+        <v>621.3346557617188</v>
       </c>
       <c r="F365" t="n">
         <v>67413</v>
@@ -7732,16 +7732,16 @@
         <v>43489</v>
       </c>
       <c r="B366" t="n">
-        <v>631.5333862304688</v>
+        <v>631.533447265625</v>
       </c>
       <c r="C366" t="n">
-        <v>631.5333862304688</v>
+        <v>631.533447265625</v>
       </c>
       <c r="D366" t="n">
-        <v>616.9534874630561</v>
+        <v>616.953547089124</v>
       </c>
       <c r="E366" t="n">
-        <v>619.7545523215402</v>
+        <v>619.7546122183197</v>
       </c>
       <c r="F366" t="n">
         <v>78173</v>
@@ -7752,16 +7752,16 @@
         <v>43493</v>
       </c>
       <c r="B367" t="n">
-        <v>633.3290405273438</v>
+        <v>633.3291015625</v>
       </c>
       <c r="C367" t="n">
-        <v>651.5000602481508</v>
+        <v>651.5001230344836</v>
       </c>
       <c r="D367" t="n">
-        <v>610.4895026590767</v>
+        <v>610.4895614931421</v>
       </c>
       <c r="E367" t="n">
-        <v>611.2795569376502</v>
+        <v>611.2796158478546</v>
       </c>
       <c r="F367" t="n">
         <v>160193</v>
@@ -7792,16 +7792,16 @@
         <v>43495</v>
       </c>
       <c r="B369" t="n">
-        <v>616.2352905273438</v>
+        <v>616.2353515625</v>
       </c>
       <c r="C369" t="n">
-        <v>636.9200876399608</v>
+        <v>636.9201507238472</v>
       </c>
       <c r="D369" t="n">
-        <v>612.3568839222787</v>
+        <v>612.3569445732975</v>
       </c>
       <c r="E369" t="n">
-        <v>624.5666782588467</v>
+        <v>624.5667401191871</v>
       </c>
       <c r="F369" t="n">
         <v>160897</v>
@@ -7832,16 +7832,16 @@
         <v>43497</v>
       </c>
       <c r="B371" t="n">
-        <v>623.4893188476562</v>
+        <v>623.4893798828125</v>
       </c>
       <c r="C371" t="n">
-        <v>630.5997498101098</v>
+        <v>630.5998115413265</v>
       </c>
       <c r="D371" t="n">
-        <v>616.9535195616811</v>
+        <v>616.9535799570293</v>
       </c>
       <c r="E371" t="n">
-        <v>616.9535195616811</v>
+        <v>616.9535799570293</v>
       </c>
       <c r="F371" t="n">
         <v>187216</v>
@@ -7852,16 +7852,16 @@
         <v>43500</v>
       </c>
       <c r="B372" t="n">
-        <v>628.4451293945312</v>
+        <v>628.4451904296875</v>
       </c>
       <c r="C372" t="n">
-        <v>634.5500269953985</v>
+        <v>634.5500886234679</v>
       </c>
       <c r="D372" t="n">
-        <v>617.743578125374</v>
+        <v>617.743638121186</v>
       </c>
       <c r="E372" t="n">
-        <v>628.3014571682105</v>
+        <v>628.3015181894132</v>
       </c>
       <c r="F372" t="n">
         <v>140148</v>
@@ -7892,16 +7892,16 @@
         <v>43502</v>
       </c>
       <c r="B374" t="n">
-        <v>617.6716918945312</v>
+        <v>617.6717529296875</v>
       </c>
       <c r="C374" t="n">
-        <v>626.7213258516895</v>
+        <v>626.7213877810843</v>
       </c>
       <c r="D374" t="n">
-        <v>612.8596162573104</v>
+        <v>612.859676816962</v>
       </c>
       <c r="E374" t="n">
-        <v>621.2628110357917</v>
+        <v>621.2628724258041</v>
       </c>
       <c r="F374" t="n">
         <v>112512</v>
@@ -7912,16 +7912,16 @@
         <v>43503</v>
       </c>
       <c r="B375" t="n">
-        <v>616.2352905273438</v>
+        <v>616.2353515625</v>
       </c>
       <c r="C375" t="n">
-        <v>622.5556674340411</v>
+        <v>622.5557290952005</v>
       </c>
       <c r="D375" t="n">
-        <v>603.3791141471297</v>
+        <v>603.3791739089432</v>
       </c>
       <c r="E375" t="n">
-        <v>621.1192311306086</v>
+        <v>621.1192926494958</v>
       </c>
       <c r="F375" t="n">
         <v>104504</v>
@@ -7932,16 +7932,16 @@
         <v>43504</v>
       </c>
       <c r="B376" t="n">
-        <v>640.7266235351562</v>
+        <v>640.7266845703125</v>
       </c>
       <c r="C376" t="n">
-        <v>640.7266235351562</v>
+        <v>640.7266845703125</v>
       </c>
       <c r="D376" t="n">
-        <v>609.8430459564737</v>
+        <v>609.8431040496826</v>
       </c>
       <c r="E376" t="n">
-        <v>625.5721505639639</v>
+        <v>625.5722101555159</v>
       </c>
       <c r="F376" t="n">
         <v>269863</v>
@@ -7992,16 +7992,16 @@
         <v>43509</v>
       </c>
       <c r="B379" t="n">
-        <v>651.1409301757812</v>
+        <v>651.140869140625</v>
       </c>
       <c r="C379" t="n">
-        <v>669.4556211237972</v>
+        <v>669.4555583719005</v>
       </c>
       <c r="D379" t="n">
-        <v>650.2790684199256</v>
+        <v>650.2790074655566</v>
       </c>
       <c r="E379" t="n">
-        <v>667.2291306282719</v>
+        <v>667.2290680850768</v>
       </c>
       <c r="F379" t="n">
         <v>182730</v>
@@ -8012,16 +8012,16 @@
         <v>43510</v>
       </c>
       <c r="B380" t="n">
-        <v>660.76513671875</v>
+        <v>660.7650146484375</v>
       </c>
       <c r="C380" t="n">
-        <v>667.8755682610803</v>
+        <v>667.8754448771806</v>
       </c>
       <c r="D380" t="n">
-        <v>646.5443308056866</v>
+        <v>646.5442113625379</v>
       </c>
       <c r="E380" t="n">
-        <v>654.7321039254365</v>
+        <v>654.7319829696715</v>
       </c>
       <c r="F380" t="n">
         <v>132140</v>
@@ -8032,16 +8032,16 @@
         <v>43511</v>
       </c>
       <c r="B381" t="n">
-        <v>654.6602172851562</v>
+        <v>654.66015625</v>
       </c>
       <c r="C381" t="n">
-        <v>660.0469249917048</v>
+        <v>660.0468634543359</v>
       </c>
       <c r="D381" t="n">
-        <v>640.3676043250778</v>
+        <v>640.3675446224476</v>
       </c>
       <c r="E381" t="n">
-        <v>653.5828757438466</v>
+        <v>653.5828148091327</v>
       </c>
       <c r="F381" t="n">
         <v>315705</v>
@@ -8052,16 +8052,16 @@
         <v>43514</v>
       </c>
       <c r="B382" t="n">
-        <v>658.6104736328125</v>
+        <v>658.6104125976562</v>
       </c>
       <c r="C382" t="n">
-        <v>664.7153713098178</v>
+        <v>664.7153097089048</v>
       </c>
       <c r="D382" t="n">
-        <v>650.7818522480502</v>
+        <v>650.7817919383928</v>
       </c>
       <c r="E382" t="n">
-        <v>660.7651568533082</v>
+        <v>660.7650956184718</v>
       </c>
       <c r="F382" t="n">
         <v>91084</v>
@@ -8092,16 +8092,16 @@
         <v>43516</v>
       </c>
       <c r="B384" t="n">
-        <v>666.15185546875</v>
+        <v>666.1517333984375</v>
       </c>
       <c r="C384" t="n">
-        <v>666.5109502765465</v>
+        <v>666.510828140431</v>
       </c>
       <c r="D384" t="n">
-        <v>648.6272170115859</v>
+        <v>648.6270981526104</v>
       </c>
       <c r="E384" t="n">
-        <v>662.8480231565471</v>
+        <v>662.8479016916519</v>
       </c>
       <c r="F384" t="n">
         <v>179613</v>
@@ -8112,16 +8112,16 @@
         <v>43517</v>
       </c>
       <c r="B385" t="n">
-        <v>681.3063354492188</v>
+        <v>681.3062133789062</v>
       </c>
       <c r="C385" t="n">
-        <v>681.3063354492188</v>
+        <v>681.3062133789062</v>
       </c>
       <c r="D385" t="n">
-        <v>663.6380818217434</v>
+        <v>663.637962917069</v>
       </c>
       <c r="E385" t="n">
-        <v>663.6380818217434</v>
+        <v>663.637962917069</v>
       </c>
       <c r="F385" t="n">
         <v>232784</v>
@@ -8192,16 +8192,16 @@
         <v>43523</v>
       </c>
       <c r="B389" t="n">
-        <v>646.400634765625</v>
+        <v>646.4006958007812</v>
       </c>
       <c r="C389" t="n">
-        <v>669.3119207819476</v>
+        <v>669.3119839804588</v>
       </c>
       <c r="D389" t="n">
-        <v>646.400634765625</v>
+        <v>646.4006958007812</v>
       </c>
       <c r="E389" t="n">
-        <v>667.15723789707</v>
+        <v>667.1573008921292</v>
       </c>
       <c r="F389" t="n">
         <v>481207</v>
@@ -8332,16 +8332,16 @@
         <v>43536</v>
       </c>
       <c r="B396" t="n">
-        <v>647.47802734375</v>
+        <v>647.4779663085938</v>
       </c>
       <c r="C396" t="n">
-        <v>659.32872802132</v>
+        <v>659.3286658690457</v>
       </c>
       <c r="D396" t="n">
-        <v>639.5775983397697</v>
+        <v>639.5775380493552</v>
       </c>
       <c r="E396" t="n">
-        <v>655.1630337604796</v>
+        <v>655.1629720008887</v>
       </c>
       <c r="F396" t="n">
         <v>122580</v>
@@ -8412,16 +8412,16 @@
         <v>43542</v>
       </c>
       <c r="B400" t="n">
-        <v>644.8923950195312</v>
+        <v>644.8924560546875</v>
       </c>
       <c r="C400" t="n">
-        <v>644.8923950195312</v>
+        <v>644.8924560546875</v>
       </c>
       <c r="D400" t="n">
-        <v>634.8372834989018</v>
+        <v>634.8373435824027</v>
       </c>
       <c r="E400" t="n">
-        <v>636.4173920538334</v>
+        <v>636.4174522868821</v>
       </c>
       <c r="F400" t="n">
         <v>127432</v>
@@ -8472,16 +8472,16 @@
         <v>43545</v>
       </c>
       <c r="B403" t="n">
-        <v>650.7819213867188</v>
+        <v>650.7817993164062</v>
       </c>
       <c r="C403" t="n">
-        <v>654.6603287270111</v>
+        <v>654.660205929207</v>
       </c>
       <c r="D403" t="n">
-        <v>646.4008041236223</v>
+        <v>646.4006828750971</v>
       </c>
       <c r="E403" t="n">
-        <v>653.5829870023072</v>
+        <v>653.5828644065853</v>
       </c>
       <c r="F403" t="n">
         <v>181165</v>
@@ -8492,16 +8492,16 @@
         <v>43546</v>
       </c>
       <c r="B404" t="n">
-        <v>657.0747680664062</v>
+        <v>657.0748291015625</v>
       </c>
       <c r="C404" t="n">
-        <v>663.2680393651752</v>
+        <v>663.2681009756196</v>
       </c>
       <c r="D404" t="n">
-        <v>635.5458053085566</v>
+        <v>635.5458643439046</v>
       </c>
       <c r="E404" t="n">
-        <v>647.7848611182527</v>
+        <v>647.7849212904769</v>
       </c>
       <c r="F404" t="n">
         <v>199032</v>
@@ -8512,16 +8512,16 @@
         <v>43549</v>
       </c>
       <c r="B405" t="n">
-        <v>666.5120849609375</v>
+        <v>666.5120239257812</v>
       </c>
       <c r="C405" t="n">
-        <v>671.0832949165999</v>
+        <v>671.0832334628399</v>
       </c>
       <c r="D405" t="n">
-        <v>654.8628592408074</v>
+        <v>654.8627992724171</v>
       </c>
       <c r="E405" t="n">
-        <v>656.1900055371226</v>
+        <v>656.1899454472001</v>
       </c>
       <c r="F405" t="n">
         <v>187007</v>
@@ -8532,16 +8532,16 @@
         <v>43550</v>
       </c>
       <c r="B406" t="n">
-        <v>667.3969116210938</v>
+        <v>667.3967895507812</v>
       </c>
       <c r="C406" t="n">
-        <v>670.346060764781</v>
+        <v>670.345938155054</v>
       </c>
       <c r="D406" t="n">
-        <v>658.4756914442885</v>
+        <v>658.4755710057128</v>
       </c>
       <c r="E406" t="n">
-        <v>667.2494248191418</v>
+        <v>667.2493027758054</v>
       </c>
       <c r="F406" t="n">
         <v>144960</v>
@@ -8552,16 +8552,16 @@
         <v>43551</v>
       </c>
       <c r="B407" t="n">
-        <v>658.2544555664062</v>
+        <v>658.2545166015625</v>
       </c>
       <c r="C407" t="n">
-        <v>670.0511102030978</v>
+        <v>670.0511723320722</v>
       </c>
       <c r="D407" t="n">
-        <v>654.8629048868319</v>
+        <v>654.8629656075142</v>
       </c>
       <c r="E407" t="n">
-        <v>669.3138523011663</v>
+        <v>669.3139143617802</v>
       </c>
       <c r="F407" t="n">
         <v>249165</v>
@@ -8592,16 +8592,16 @@
         <v>43553</v>
       </c>
       <c r="B409" t="n">
-        <v>672.7791137695312</v>
+        <v>672.7789916992188</v>
       </c>
       <c r="C409" t="n">
-        <v>672.7791137695312</v>
+        <v>672.7789916992188</v>
       </c>
       <c r="D409" t="n">
-        <v>659.2866838585011</v>
+        <v>659.2865642362806</v>
       </c>
       <c r="E409" t="n">
-        <v>659.3603979104303</v>
+        <v>659.360278274835</v>
       </c>
       <c r="F409" t="n">
         <v>206635</v>
@@ -8612,16 +8612,16 @@
         <v>43556</v>
       </c>
       <c r="B410" t="n">
-        <v>678.3087768554688</v>
+        <v>678.3087158203125</v>
       </c>
       <c r="C410" t="n">
-        <v>681.1842117509711</v>
+        <v>681.1841504570795</v>
       </c>
       <c r="D410" t="n">
-        <v>665.406176851351</v>
+        <v>665.4061169771885</v>
       </c>
       <c r="E410" t="n">
-        <v>673.1477368538217</v>
+        <v>673.1476762830629</v>
       </c>
       <c r="F410" t="n">
         <v>165645</v>
@@ -8692,16 +8692,16 @@
         <v>43560</v>
       </c>
       <c r="B414" t="n">
-        <v>701.017333984375</v>
+        <v>701.0173950195312</v>
       </c>
       <c r="C414" t="n">
-        <v>702.2707074966779</v>
+        <v>702.2707686409611</v>
       </c>
       <c r="D414" t="n">
-        <v>682.4375799852958</v>
+        <v>682.4376394027771</v>
       </c>
       <c r="E414" t="n">
-        <v>689.8105103494357</v>
+        <v>689.8105704088525</v>
       </c>
       <c r="F414" t="n">
         <v>143643</v>
@@ -8712,16 +8712,16 @@
         <v>43563</v>
       </c>
       <c r="B415" t="n">
-        <v>712.0029907226562</v>
+        <v>712.0029296875</v>
       </c>
       <c r="C415" t="n">
-        <v>712.0029907226562</v>
+        <v>712.0029296875</v>
       </c>
       <c r="D415" t="n">
-        <v>694.6766680998304</v>
+        <v>694.6766085499415</v>
       </c>
       <c r="E415" t="n">
-        <v>701.8283979821206</v>
+        <v>701.8283378191627</v>
       </c>
       <c r="F415" t="n">
         <v>133157</v>
@@ -8732,16 +8732,16 @@
         <v>43564</v>
       </c>
       <c r="B416" t="n">
-        <v>701.9021606445312</v>
+        <v>701.902099609375</v>
       </c>
       <c r="C416" t="n">
-        <v>710.8970944839187</v>
+        <v>710.8970326665921</v>
       </c>
       <c r="D416" t="n">
-        <v>698.5106099329405</v>
+        <v>698.5105491927027</v>
       </c>
       <c r="E416" t="n">
-        <v>707.8005173633237</v>
+        <v>707.8004558152653</v>
       </c>
       <c r="F416" t="n">
         <v>71169</v>
@@ -8772,16 +8772,16 @@
         <v>43566</v>
       </c>
       <c r="B418" t="n">
-        <v>696.7410278320312</v>
+        <v>696.7410888671875</v>
       </c>
       <c r="C418" t="n">
-        <v>701.8283532226163</v>
+        <v>701.828414703427</v>
       </c>
       <c r="D418" t="n">
-        <v>682.2163681606097</v>
+        <v>682.2164279233924</v>
       </c>
       <c r="E418" t="n">
-        <v>688.6307810864605</v>
+        <v>688.6308414111518</v>
       </c>
       <c r="F418" t="n">
         <v>167666</v>
@@ -8792,16 +8792,16 @@
         <v>43567</v>
       </c>
       <c r="B419" t="n">
-        <v>704.114013671875</v>
+        <v>704.1139526367188</v>
       </c>
       <c r="C419" t="n">
-        <v>704.114013671875</v>
+        <v>704.1139526367188</v>
       </c>
       <c r="D419" t="n">
-        <v>684.5020270613682</v>
+        <v>684.5019677262501</v>
       </c>
       <c r="E419" t="n">
-        <v>692.5385017087726</v>
+        <v>692.5384416770238</v>
       </c>
       <c r="F419" t="n">
         <v>134670</v>
@@ -8892,16 +8892,16 @@
         <v>43577</v>
       </c>
       <c r="B424" t="n">
-        <v>697.9207153320312</v>
+        <v>697.920654296875</v>
       </c>
       <c r="C424" t="n">
-        <v>703.3766698473084</v>
+        <v>703.3766083350134</v>
       </c>
       <c r="D424" t="n">
-        <v>686.2714897715088</v>
+        <v>686.2714297551105</v>
       </c>
       <c r="E424" t="n">
-        <v>686.3452038176474</v>
+        <v>686.3451437948027</v>
       </c>
       <c r="F424" t="n">
         <v>77260</v>
@@ -8912,16 +8912,16 @@
         <v>43578</v>
       </c>
       <c r="B425" t="n">
-        <v>721.36669921875</v>
+        <v>721.3666381835938</v>
       </c>
       <c r="C425" t="n">
-        <v>722.9150465494968</v>
+        <v>722.9149853833342</v>
       </c>
       <c r="D425" t="n">
-        <v>697.9208166033296</v>
+        <v>697.9207575519399</v>
       </c>
       <c r="E425" t="n">
-        <v>697.9208166033296</v>
+        <v>697.9207575519399</v>
       </c>
       <c r="F425" t="n">
         <v>178282</v>
@@ -8952,16 +8952,16 @@
         <v>43580</v>
       </c>
       <c r="B427" t="n">
-        <v>722.5462646484375</v>
+        <v>722.5463256835938</v>
       </c>
       <c r="C427" t="n">
-        <v>724.7581555812845</v>
+        <v>724.7582168032844</v>
       </c>
       <c r="D427" t="n">
-        <v>711.5606414104789</v>
+        <v>711.5607015176541</v>
       </c>
       <c r="E427" t="n">
-        <v>717.3115108842588</v>
+        <v>717.3115714772234</v>
       </c>
       <c r="F427" t="n">
         <v>179547</v>
@@ -8972,16 +8972,16 @@
         <v>43581</v>
       </c>
       <c r="B428" t="n">
-        <v>697.9207153320312</v>
+        <v>697.920654296875</v>
       </c>
       <c r="C428" t="n">
-        <v>723.7259135380083</v>
+        <v>723.7258502461139</v>
       </c>
       <c r="D428" t="n">
-        <v>697.9207153320312</v>
+        <v>697.920654296875</v>
       </c>
       <c r="E428" t="n">
-        <v>722.546254041681</v>
+        <v>722.5461908529511</v>
       </c>
       <c r="F428" t="n">
         <v>338189</v>
@@ -8992,16 +8992,16 @@
         <v>43584</v>
       </c>
       <c r="B429" t="n">
-        <v>699.6902465820312</v>
+        <v>699.690185546875</v>
       </c>
       <c r="C429" t="n">
-        <v>708.7589528663908</v>
+        <v>708.7588910401561</v>
       </c>
       <c r="D429" t="n">
-        <v>673.5163591949721</v>
+        <v>673.516300443008</v>
       </c>
       <c r="E429" t="n">
-        <v>697.9207572313101</v>
+        <v>697.9206963505094</v>
       </c>
       <c r="F429" t="n">
         <v>175687</v>
@@ -9012,16 +9012,16 @@
         <v>43585</v>
       </c>
       <c r="B430" t="n">
-        <v>692.3173217773438</v>
+        <v>692.3172607421875</v>
       </c>
       <c r="C430" t="n">
-        <v>705.4411226132963</v>
+        <v>705.441060421137</v>
       </c>
       <c r="D430" t="n">
-        <v>691.9486928317025</v>
+        <v>691.9486318290448</v>
       </c>
       <c r="E430" t="n">
-        <v>703.2292902499178</v>
+        <v>703.229228252755</v>
       </c>
       <c r="F430" t="n">
         <v>138113</v>
@@ -9032,16 +9032,16 @@
         <v>43587</v>
       </c>
       <c r="B431" t="n">
-        <v>711.4869995117188</v>
+        <v>711.4869384765625</v>
       </c>
       <c r="C431" t="n">
-        <v>712.1505433830484</v>
+        <v>712.1504822909699</v>
       </c>
       <c r="D431" t="n">
-        <v>690.6215790073074</v>
+        <v>690.6215197620984</v>
       </c>
       <c r="E431" t="n">
-        <v>690.6215790073074</v>
+        <v>690.6215197620984</v>
       </c>
       <c r="F431" t="n">
         <v>276240</v>
@@ -9072,16 +9072,16 @@
         <v>43591</v>
       </c>
       <c r="B433" t="n">
-        <v>726.2327880859375</v>
+        <v>726.2327270507812</v>
       </c>
       <c r="C433" t="n">
-        <v>744.2227144876096</v>
+        <v>744.2226519405167</v>
       </c>
       <c r="D433" t="n">
-        <v>719.3022585439375</v>
+        <v>719.3021980912473</v>
       </c>
       <c r="E433" t="n">
-        <v>729.9192537058282</v>
+        <v>729.9191923608485</v>
       </c>
       <c r="F433" t="n">
         <v>141178</v>
@@ -9152,16 +9152,16 @@
         <v>43595</v>
       </c>
       <c r="B437" t="n">
-        <v>745.2548828125</v>
+        <v>745.2549438476562</v>
       </c>
       <c r="C437" t="n">
-        <v>746.0659133966576</v>
+        <v>746.065974498236</v>
       </c>
       <c r="D437" t="n">
-        <v>727.6335868597536</v>
+        <v>727.6336464517544</v>
       </c>
       <c r="E437" t="n">
-        <v>735.0065174745151</v>
+        <v>735.006577670347</v>
       </c>
       <c r="F437" t="n">
         <v>130275</v>
@@ -9172,16 +9172,16 @@
         <v>43598</v>
       </c>
       <c r="B438" t="n">
-        <v>721.4403076171875</v>
+        <v>721.4402465820312</v>
       </c>
       <c r="C438" t="n">
-        <v>742.2319529356944</v>
+        <v>742.2318901415273</v>
       </c>
       <c r="D438" t="n">
-        <v>721.3665935711483</v>
+        <v>721.3665325422285</v>
       </c>
       <c r="E438" t="n">
-        <v>733.4582207712275</v>
+        <v>733.4581587193341</v>
       </c>
       <c r="F438" t="n">
         <v>104165</v>
@@ -9212,16 +9212,16 @@
         <v>43600</v>
       </c>
       <c r="B440" t="n">
-        <v>715.1732788085938</v>
+        <v>715.17333984375</v>
       </c>
       <c r="C440" t="n">
-        <v>726.2326739298459</v>
+        <v>726.2327359088459</v>
       </c>
       <c r="D440" t="n">
-        <v>712.2241302520692</v>
+        <v>712.2241910355358</v>
       </c>
       <c r="E440" t="n">
-        <v>720.9242065281018</v>
+        <v>720.9242680540605</v>
       </c>
       <c r="F440" t="n">
         <v>136379</v>
@@ -9272,16 +9272,16 @@
         <v>43605</v>
       </c>
       <c r="B443" t="n">
-        <v>768.3321533203125</v>
+        <v>768.3322143554688</v>
       </c>
       <c r="C443" t="n">
-        <v>769.8067277437154</v>
+        <v>769.8067888960097</v>
       </c>
       <c r="D443" t="n">
-        <v>730.6565273718671</v>
+        <v>730.6565854141281</v>
       </c>
       <c r="E443" t="n">
-        <v>733.9005911033537</v>
+        <v>733.9006494033182</v>
       </c>
       <c r="F443" t="n">
         <v>149825</v>
@@ -9292,16 +9292,16 @@
         <v>43606</v>
       </c>
       <c r="B444" t="n">
-        <v>766.0465087890625</v>
+        <v>766.0465698242188</v>
       </c>
       <c r="C444" t="n">
-        <v>770.2490310066679</v>
+        <v>770.2490923766624</v>
       </c>
       <c r="D444" t="n">
-        <v>750.2684165484537</v>
+        <v>750.2684763264823</v>
       </c>
       <c r="E444" t="n">
-        <v>755.7244296679894</v>
+        <v>755.7244898807286</v>
       </c>
       <c r="F444" t="n">
         <v>224959</v>
@@ -9312,16 +9312,16 @@
         <v>43607</v>
       </c>
       <c r="B445" t="n">
-        <v>761.0330200195312</v>
+        <v>761.032958984375</v>
       </c>
       <c r="C445" t="n">
-        <v>769.7330981059772</v>
+        <v>769.7330363730712</v>
       </c>
       <c r="D445" t="n">
-        <v>746.9507593698219</v>
+        <v>746.9506994640686</v>
       </c>
       <c r="E445" t="n">
-        <v>766.0466322984372</v>
+        <v>766.0465708611872</v>
       </c>
       <c r="F445" t="n">
         <v>111769</v>
@@ -9432,16 +9432,16 @@
         <v>43615</v>
       </c>
       <c r="B451" t="n">
-        <v>768.9957275390625</v>
+        <v>768.9956665039062</v>
       </c>
       <c r="C451" t="n">
-        <v>768.9957275390625</v>
+        <v>768.9956665039062</v>
       </c>
       <c r="D451" t="n">
-        <v>752.3329478615876</v>
+        <v>752.3328881489555</v>
       </c>
       <c r="E451" t="n">
-        <v>759.4109053737338</v>
+        <v>759.4108450993244</v>
       </c>
       <c r="F451" t="n">
         <v>116385</v>
@@ -9532,16 +9532,16 @@
         <v>43622</v>
       </c>
       <c r="B456" t="n">
-        <v>699.3216552734375</v>
+        <v>699.3215942382812</v>
       </c>
       <c r="C456" t="n">
-        <v>733.458305265325</v>
+        <v>733.4582412508018</v>
       </c>
       <c r="D456" t="n">
-        <v>699.3216552734375</v>
+        <v>699.3215942382812</v>
       </c>
       <c r="E456" t="n">
-        <v>725.6429721780975</v>
+        <v>725.6429088456783</v>
       </c>
       <c r="F456" t="n">
         <v>226537</v>
@@ -9552,16 +9552,16 @@
         <v>43623</v>
       </c>
       <c r="B457" t="n">
-        <v>726.5277709960938</v>
+        <v>726.5276489257812</v>
       </c>
       <c r="C457" t="n">
-        <v>728.1498324537512</v>
+        <v>728.149710110902</v>
       </c>
       <c r="D457" t="n">
-        <v>700.4276530012258</v>
+        <v>700.4275353162235</v>
       </c>
       <c r="E457" t="n">
-        <v>704.4827479558314</v>
+        <v>704.4826295894969</v>
       </c>
       <c r="F457" t="n">
         <v>188533</v>
@@ -9612,16 +9612,16 @@
         <v>43628</v>
       </c>
       <c r="B460" t="n">
-        <v>713.55126953125</v>
+        <v>713.5513305664062</v>
       </c>
       <c r="C460" t="n">
-        <v>717.9749923231602</v>
+        <v>717.9750537367092</v>
       </c>
       <c r="D460" t="n">
-        <v>705.9571387099003</v>
+        <v>705.9571990954761</v>
       </c>
       <c r="E460" t="n">
-        <v>714.5097281304498</v>
+        <v>714.5097892475899</v>
       </c>
       <c r="F460" t="n">
         <v>341893</v>
@@ -9632,16 +9632,16 @@
         <v>43629</v>
       </c>
       <c r="B461" t="n">
-        <v>707.8004760742188</v>
+        <v>707.8004150390625</v>
       </c>
       <c r="C461" t="n">
-        <v>728.8870370225827</v>
+        <v>728.886974169087</v>
       </c>
       <c r="D461" t="n">
-        <v>702.2707486324451</v>
+        <v>702.2706880741292</v>
       </c>
       <c r="E461" t="n">
-        <v>717.3115251087285</v>
+        <v>717.3114632534141</v>
       </c>
       <c r="F461" t="n">
         <v>234349</v>
@@ -9672,16 +9672,16 @@
         <v>43633</v>
       </c>
       <c r="B463" t="n">
-        <v>710.7496337890625</v>
+        <v>710.7495727539062</v>
       </c>
       <c r="C463" t="n">
-        <v>718.1225646771105</v>
+        <v>718.1225030088086</v>
       </c>
       <c r="D463" t="n">
-        <v>686.4927228597309</v>
+        <v>686.4926639076209</v>
       </c>
       <c r="E463" t="n">
-        <v>693.0546231335594</v>
+        <v>693.0545636179505</v>
       </c>
       <c r="F463" t="n">
         <v>382414</v>
@@ -9712,16 +9712,16 @@
         <v>43635</v>
       </c>
       <c r="B465" t="n">
-        <v>724.8319091796875</v>
+        <v>724.8319702148438</v>
       </c>
       <c r="C465" t="n">
-        <v>728.9607763922664</v>
+        <v>728.9608377750978</v>
       </c>
       <c r="D465" t="n">
-        <v>714.0674861855476</v>
+        <v>714.0675463142754</v>
       </c>
       <c r="E465" t="n">
-        <v>720.4081857621364</v>
+        <v>720.4082464247889</v>
       </c>
       <c r="F465" t="n">
         <v>115851</v>
@@ -9732,16 +9732,16 @@
         <v>43637</v>
       </c>
       <c r="B466" t="n">
-        <v>733.4581909179688</v>
+        <v>733.458251953125</v>
       </c>
       <c r="C466" t="n">
-        <v>733.4581909179688</v>
+        <v>733.458251953125</v>
       </c>
       <c r="D466" t="n">
-        <v>723.3572541987642</v>
+        <v>723.3573143933651</v>
       </c>
       <c r="E466" t="n">
-        <v>728.4445795798858</v>
+        <v>728.4446401978315</v>
       </c>
       <c r="F466" t="n">
         <v>181934</v>
@@ -9752,16 +9752,16 @@
         <v>43640</v>
       </c>
       <c r="B467" t="n">
-        <v>745.0337524414062</v>
+        <v>745.03369140625</v>
       </c>
       <c r="C467" t="n">
-        <v>752.0380547946963</v>
+        <v>752.037993185729</v>
       </c>
       <c r="D467" t="n">
-        <v>733.8269273656755</v>
+        <v>733.8268672486123</v>
       </c>
       <c r="E467" t="n">
-        <v>734.0481282167337</v>
+        <v>734.0480680815492</v>
       </c>
       <c r="F467" t="n">
         <v>155459</v>
@@ -9792,16 +9792,16 @@
         <v>43642</v>
       </c>
       <c r="B469" t="n">
-        <v>737.2921752929688</v>
+        <v>737.2921142578125</v>
       </c>
       <c r="C469" t="n">
-        <v>751.0058060911912</v>
+        <v>751.0057439207814</v>
       </c>
       <c r="D469" t="n">
-        <v>732.6472509747404</v>
+        <v>732.6471903241043</v>
       </c>
       <c r="E469" t="n">
-        <v>733.6057097213413</v>
+        <v>733.6056489913612</v>
       </c>
       <c r="F469" t="n">
         <v>130066</v>
@@ -9832,16 +9832,16 @@
         <v>43644</v>
       </c>
       <c r="B471" t="n">
-        <v>726.2327880859375</v>
+        <v>726.2327270507812</v>
       </c>
       <c r="C471" t="n">
-        <v>740.2413339657089</v>
+        <v>740.2412717532253</v>
       </c>
       <c r="D471" t="n">
-        <v>724.6844995227684</v>
+        <v>724.6844386177359</v>
       </c>
       <c r="E471" t="n">
-        <v>737.2921849456095</v>
+        <v>737.2921229809828</v>
       </c>
       <c r="F471" t="n">
         <v>201679</v>
@@ -9852,16 +9852,16 @@
         <v>43647</v>
       </c>
       <c r="B472" t="n">
-        <v>746.50830078125</v>
+        <v>746.5082397460938</v>
       </c>
       <c r="C472" t="n">
-        <v>747.8354471515152</v>
+        <v>747.8353860078503</v>
       </c>
       <c r="D472" t="n">
-        <v>732.5734693068254</v>
+        <v>732.5734094109929</v>
       </c>
       <c r="E472" t="n">
-        <v>735.0802752553124</v>
+        <v>735.0802151545213</v>
       </c>
       <c r="F472" t="n">
         <v>147425</v>
@@ -9872,16 +9872,16 @@
         <v>43648</v>
       </c>
       <c r="B473" t="n">
-        <v>715.1732788085938</v>
+        <v>715.17333984375</v>
       </c>
       <c r="C473" t="n">
-        <v>746.1395734101949</v>
+        <v>746.139637088113</v>
       </c>
       <c r="D473" t="n">
-        <v>711.8555013548845</v>
+        <v>711.8555621068912</v>
       </c>
       <c r="E473" t="n">
-        <v>746.1395734101949</v>
+        <v>746.139637088113</v>
       </c>
       <c r="F473" t="n">
         <v>313670</v>
@@ -9892,16 +9892,16 @@
         <v>43649</v>
       </c>
       <c r="B474" t="n">
-        <v>709.5700073242188</v>
+        <v>709.5699462890625</v>
       </c>
       <c r="C474" t="n">
-        <v>721.44037613449</v>
+        <v>721.440314078279</v>
       </c>
       <c r="D474" t="n">
-        <v>705.3674259579516</v>
+        <v>705.3673652842892</v>
       </c>
       <c r="E474" t="n">
-        <v>712.9615580384484</v>
+        <v>712.9614967115608</v>
       </c>
       <c r="F474" t="n">
         <v>330638</v>
@@ -9912,16 +9912,16 @@
         <v>43650</v>
       </c>
       <c r="B475" t="n">
-        <v>708.0953979492188</v>
+        <v>708.0953369140625</v>
       </c>
       <c r="C475" t="n">
-        <v>725.4954936713608</v>
+        <v>725.4954311363819</v>
       </c>
       <c r="D475" t="n">
-        <v>708.0953979492188</v>
+        <v>708.0953369140625</v>
       </c>
       <c r="E475" t="n">
-        <v>718.1225628025588</v>
+        <v>718.1225009030987</v>
       </c>
       <c r="F475" t="n">
         <v>244483</v>
@@ -10012,16 +10012,16 @@
         <v>43658</v>
       </c>
       <c r="B480" t="n">
-        <v>693.2758178710938</v>
+        <v>693.2757568359375</v>
       </c>
       <c r="C480" t="n">
-        <v>719.6708468333378</v>
+        <v>719.6707834743954</v>
       </c>
       <c r="D480" t="n">
-        <v>693.2758178710938</v>
+        <v>693.2757568359375</v>
       </c>
       <c r="E480" t="n">
-        <v>713.3301474536453</v>
+        <v>713.3300846529303</v>
       </c>
       <c r="F480" t="n">
         <v>217604</v>
@@ -10052,16 +10052,16 @@
         <v>43662</v>
       </c>
       <c r="B482" t="n">
-        <v>683.6910400390625</v>
+        <v>683.6909790039062</v>
       </c>
       <c r="C482" t="n">
-        <v>700.132678006064</v>
+        <v>700.1326155031132</v>
       </c>
       <c r="D482" t="n">
-        <v>678.308799018167</v>
+        <v>678.3087384634996</v>
       </c>
       <c r="E482" t="n">
-        <v>683.9122408896819</v>
+        <v>683.9121798347784</v>
       </c>
       <c r="F482" t="n">
         <v>150151</v>
@@ -10112,16 +10112,16 @@
         <v>43665</v>
       </c>
       <c r="B485" t="n">
-        <v>653.2407836914062</v>
+        <v>653.2408447265625</v>
       </c>
       <c r="C485" t="n">
-        <v>670.0510487535236</v>
+        <v>670.0511113593367</v>
       </c>
       <c r="D485" t="n">
-        <v>647.268713523699</v>
+        <v>647.2687740008586</v>
       </c>
       <c r="E485" t="n">
-        <v>652.1348969399286</v>
+        <v>652.134957871757</v>
       </c>
       <c r="F485" t="n">
         <v>752622</v>
@@ -10172,16 +10172,16 @@
         <v>43670</v>
       </c>
       <c r="B488" t="n">
-        <v>704.114013671875</v>
+        <v>704.1139526367188</v>
       </c>
       <c r="C488" t="n">
-        <v>708.5377369545855</v>
+        <v>708.5376755359649</v>
       </c>
       <c r="D488" t="n">
-        <v>688.6308354585647</v>
+        <v>688.6307757655464</v>
       </c>
       <c r="E488" t="n">
-        <v>699.6902316996351</v>
+        <v>699.6901710479483</v>
       </c>
       <c r="F488" t="n">
         <v>484337</v>
@@ -10192,16 +10192,16 @@
         <v>43671</v>
       </c>
       <c r="B489" t="n">
-        <v>704.114013671875</v>
+        <v>704.1139526367188</v>
       </c>
       <c r="C489" t="n">
-        <v>707.0631625270154</v>
+        <v>707.0631012362162</v>
       </c>
       <c r="D489" t="n">
-        <v>689.5156388046362</v>
+        <v>689.5155790349201</v>
       </c>
       <c r="E489" t="n">
-        <v>707.0631625270154</v>
+        <v>707.0631012362162</v>
       </c>
       <c r="F489" t="n">
         <v>429130</v>
@@ -10232,16 +10232,16 @@
         <v>43675</v>
       </c>
       <c r="B491" t="n">
-        <v>698.3630981445312</v>
+        <v>698.3631591796875</v>
       </c>
       <c r="C491" t="n">
-        <v>703.0080219583713</v>
+        <v>703.0080833994821</v>
       </c>
       <c r="D491" t="n">
-        <v>697.1096659463585</v>
+        <v>697.109726871968</v>
       </c>
       <c r="E491" t="n">
-        <v>700.4275022074017</v>
+        <v>700.4275634229816</v>
       </c>
       <c r="F491" t="n">
         <v>471177</v>
@@ -10292,16 +10292,16 @@
         <v>43678</v>
       </c>
       <c r="B494" t="n">
-        <v>677.055419921875</v>
+        <v>677.0553588867188</v>
       </c>
       <c r="C494" t="n">
-        <v>711.4869841552428</v>
+        <v>711.4869200161518</v>
       </c>
       <c r="D494" t="n">
-        <v>672.1155806418019</v>
+        <v>672.115520051962</v>
       </c>
       <c r="E494" t="n">
-        <v>707.800518536081</v>
+        <v>707.8004547293172</v>
       </c>
       <c r="F494" t="n">
         <v>781314</v>
@@ -10312,16 +10312,16 @@
         <v>43679</v>
       </c>
       <c r="B495" t="n">
-        <v>674.622314453125</v>
+        <v>674.6223754882812</v>
       </c>
       <c r="C495" t="n">
-        <v>684.1334225572709</v>
+        <v>684.1334844529263</v>
       </c>
       <c r="D495" t="n">
-        <v>657.369705000169</v>
+        <v>657.3697644744285</v>
       </c>
       <c r="E495" t="n">
-        <v>679.7096404270576</v>
+        <v>679.7097019224799</v>
       </c>
       <c r="F495" t="n">
         <v>683082</v>
@@ -10332,16 +10332,16 @@
         <v>43682</v>
       </c>
       <c r="B496" t="n">
-        <v>675.5808715820312</v>
+        <v>675.580810546875</v>
       </c>
       <c r="C496" t="n">
-        <v>678.3825926038681</v>
+        <v>678.3825313155912</v>
       </c>
       <c r="D496" t="n">
-        <v>662.0883822436379</v>
+        <v>662.0883224274567</v>
       </c>
       <c r="E496" t="n">
-        <v>667.9130251447273</v>
+        <v>667.9129648023204</v>
       </c>
       <c r="F496" t="n">
         <v>339376</v>
@@ -10352,16 +10352,16 @@
         <v>43683</v>
       </c>
       <c r="B497" t="n">
-        <v>715.1732788085938</v>
+        <v>715.17333984375</v>
       </c>
       <c r="C497" t="n">
-        <v>717.2377414876844</v>
+        <v>717.2378026990284</v>
       </c>
       <c r="D497" t="n">
-        <v>683.7646412682756</v>
+        <v>683.7646996229191</v>
       </c>
       <c r="E497" t="n">
-        <v>692.3172307717201</v>
+        <v>692.3172898562688</v>
       </c>
       <c r="F497" t="n">
         <v>933500</v>
@@ -10412,16 +10412,16 @@
         <v>43686</v>
       </c>
       <c r="B500" t="n">
-        <v>735.0802001953125</v>
+        <v>735.0802612304688</v>
       </c>
       <c r="C500" t="n">
-        <v>741.6420999462755</v>
+        <v>741.6421615262792</v>
       </c>
       <c r="D500" t="n">
-        <v>708.9800879684439</v>
+        <v>708.9801468364564</v>
       </c>
       <c r="E500" t="n">
-        <v>712.5927803854685</v>
+        <v>712.5928395534499</v>
       </c>
       <c r="F500" t="n">
         <v>340941</v>
@@ -10472,16 +10472,16 @@
         <v>43691</v>
       </c>
       <c r="B503" t="n">
-        <v>741.1998291015625</v>
+        <v>741.1997680664062</v>
       </c>
       <c r="C503" t="n">
-        <v>755.355802661426</v>
+        <v>755.3557404605759</v>
       </c>
       <c r="D503" t="n">
-        <v>731.0251772542147</v>
+        <v>731.0251170569046</v>
       </c>
       <c r="E503" t="n">
-        <v>734.7116427631291</v>
+        <v>734.7115822622519</v>
       </c>
       <c r="F503" t="n">
         <v>464383</v>
@@ -10592,16 +10592,16 @@
         <v>43699</v>
       </c>
       <c r="B509" t="n">
-        <v>743.1905517578125</v>
+        <v>743.1904907226562</v>
       </c>
       <c r="C509" t="n">
-        <v>754.5448049839988</v>
+        <v>754.5447430163649</v>
       </c>
       <c r="D509" t="n">
-        <v>735.9650485262451</v>
+        <v>735.9649880844896</v>
       </c>
       <c r="E509" t="n">
-        <v>750.7109112058572</v>
+        <v>750.710849553085</v>
       </c>
       <c r="F509" t="n">
         <v>188833</v>
@@ -10632,16 +10632,16 @@
         <v>43703</v>
       </c>
       <c r="B511" t="n">
-        <v>726.2327880859375</v>
+        <v>726.2327270507812</v>
       </c>
       <c r="C511" t="n">
-        <v>745.9922038996692</v>
+        <v>745.9921412038623</v>
       </c>
       <c r="D511" t="n">
-        <v>723.7259820740866</v>
+        <v>723.7259212496111</v>
       </c>
       <c r="E511" t="n">
-        <v>742.3057969693112</v>
+        <v>742.3057345833229</v>
       </c>
       <c r="F511" t="n">
         <v>116946</v>
@@ -10692,16 +10692,16 @@
         <v>43706</v>
       </c>
       <c r="B514" t="n">
-        <v>766.7838134765625</v>
+        <v>766.7838745117188</v>
       </c>
       <c r="C514" t="n">
-        <v>771.4287963165239</v>
+        <v>771.4288577214157</v>
       </c>
       <c r="D514" t="n">
-        <v>734.3429997835032</v>
+        <v>734.3430582364061</v>
       </c>
       <c r="E514" t="n">
-        <v>734.3429997835032</v>
+        <v>734.3430582364061</v>
       </c>
       <c r="F514" t="n">
         <v>327430</v>
@@ -10892,16 +10892,16 @@
         <v>43720</v>
       </c>
       <c r="B524" t="n">
-        <v>774.15673828125</v>
+        <v>774.1566772460938</v>
       </c>
       <c r="C524" t="n">
-        <v>788.1652833616874</v>
+        <v>788.165221222086</v>
       </c>
       <c r="D524" t="n">
-        <v>766.7838074621714</v>
+        <v>766.7837470083031</v>
       </c>
       <c r="E524" t="n">
-        <v>778.9491491826039</v>
+        <v>778.9490877696101</v>
       </c>
       <c r="F524" t="n">
         <v>295451</v>
@@ -10912,16 +10912,16 @@
         <v>43721</v>
       </c>
       <c r="B525" t="n">
-        <v>759.4110107421875</v>
+        <v>759.4109497070312</v>
       </c>
       <c r="C525" t="n">
-        <v>779.6866034197437</v>
+        <v>779.6865407550036</v>
       </c>
       <c r="D525" t="n">
-        <v>759.4110107421875</v>
+        <v>759.4109497070312</v>
       </c>
       <c r="E525" t="n">
-        <v>779.3179157310152</v>
+        <v>779.3178530959071</v>
       </c>
       <c r="F525" t="n">
         <v>153881</v>
@@ -10992,16 +10992,16 @@
         <v>43727</v>
       </c>
       <c r="B529" t="n">
-        <v>826.7994995117188</v>
+        <v>826.7994384765625</v>
       </c>
       <c r="C529" t="n">
-        <v>831.9605398012469</v>
+        <v>831.9604783850976</v>
       </c>
       <c r="D529" t="n">
-        <v>819.131653132825</v>
+        <v>819.1315926637169</v>
       </c>
       <c r="E529" t="n">
-        <v>822.1545162995156</v>
+        <v>822.1544556072568</v>
       </c>
       <c r="F529" t="n">
         <v>114064</v>
@@ -11012,16 +11012,16 @@
         <v>43728</v>
       </c>
       <c r="B530" t="n">
-        <v>819.942626953125</v>
+        <v>819.9426879882812</v>
       </c>
       <c r="C530" t="n">
-        <v>843.3147934356261</v>
+        <v>843.3148562105673</v>
       </c>
       <c r="D530" t="n">
-        <v>818.7629087008795</v>
+        <v>818.7629696482194</v>
       </c>
       <c r="E530" t="n">
-        <v>833.1401416729129</v>
+        <v>833.1402036904701</v>
       </c>
       <c r="F530" t="n">
         <v>328551</v>
@@ -11052,16 +11052,16 @@
         <v>43732</v>
       </c>
       <c r="B532" t="n">
-        <v>813.9705200195312</v>
+        <v>813.9705810546875</v>
       </c>
       <c r="C532" t="n">
-        <v>830.5595845854463</v>
+        <v>830.559646864525</v>
       </c>
       <c r="D532" t="n">
-        <v>808.8831943655513</v>
+        <v>808.8832550192371</v>
       </c>
       <c r="E532" t="n">
-        <v>828.7900953204605</v>
+        <v>828.790157466855</v>
       </c>
       <c r="F532" t="n">
         <v>236567</v>
@@ -11072,16 +11072,16 @@
         <v>43733</v>
       </c>
       <c r="B533" t="n">
-        <v>813.0120239257812</v>
+        <v>813.0120849609375</v>
       </c>
       <c r="C533" t="n">
-        <v>814.7077991881504</v>
+        <v>814.7078603506134</v>
       </c>
       <c r="D533" t="n">
-        <v>802.3213153195873</v>
+        <v>802.3213755521612</v>
       </c>
       <c r="E533" t="n">
-        <v>814.7077991881504</v>
+        <v>814.7078603506134</v>
       </c>
       <c r="F533" t="n">
         <v>211226</v>
@@ -11092,16 +11092,16 @@
         <v>43734</v>
       </c>
       <c r="B534" t="n">
-        <v>818.8366088867188</v>
+        <v>818.836669921875</v>
       </c>
       <c r="C534" t="n">
-        <v>827.0205110502928</v>
+        <v>827.020572695468</v>
       </c>
       <c r="D534" t="n">
-        <v>804.0170342365382</v>
+        <v>804.01709416706</v>
       </c>
       <c r="E534" t="n">
-        <v>826.1357664566505</v>
+        <v>826.1358280358776</v>
       </c>
       <c r="F534" t="n">
         <v>152164</v>
@@ -11112,16 +11112,16 @@
         <v>43735</v>
       </c>
       <c r="B535" t="n">
-        <v>829.0112915039062</v>
+        <v>829.01123046875</v>
       </c>
       <c r="C535" t="n">
-        <v>829.0112915039062</v>
+        <v>829.01123046875</v>
       </c>
       <c r="D535" t="n">
-        <v>811.0951381660786</v>
+        <v>811.0950784499818</v>
       </c>
       <c r="E535" t="n">
-        <v>818.173095687427</v>
+        <v>818.1730354502224</v>
       </c>
       <c r="F535" t="n">
         <v>111112</v>
@@ -11152,16 +11152,16 @@
         <v>43739</v>
       </c>
       <c r="B537" t="n">
-        <v>823.9239501953125</v>
+        <v>823.924072265625</v>
       </c>
       <c r="C537" t="n">
-        <v>840.5130143524692</v>
+        <v>840.513138880572</v>
       </c>
       <c r="D537" t="n">
-        <v>818.8366246666855</v>
+        <v>818.8367459832738</v>
       </c>
       <c r="E537" t="n">
-        <v>840.5130143524692</v>
+        <v>840.513138880572</v>
       </c>
       <c r="F537" t="n">
         <v>140869</v>
@@ -11172,16 +11172,16 @@
         <v>43740</v>
       </c>
       <c r="B538" t="n">
-        <v>810.4315185546875</v>
+        <v>810.4314575195312</v>
       </c>
       <c r="C538" t="n">
-        <v>827.2417846927439</v>
+        <v>827.2417223915742</v>
       </c>
       <c r="D538" t="n">
-        <v>805.3441926762648</v>
+        <v>805.3441320242448</v>
       </c>
       <c r="E538" t="n">
-        <v>820.6061703115331</v>
+        <v>820.6061085101043</v>
       </c>
       <c r="F538" t="n">
         <v>168666</v>
@@ -11252,16 +11252,16 @@
         <v>43746</v>
       </c>
       <c r="B542" t="n">
-        <v>784.7737426757812</v>
+        <v>784.773681640625</v>
       </c>
       <c r="C542" t="n">
-        <v>793.4001058821761</v>
+        <v>793.4000441761112</v>
       </c>
       <c r="D542" t="n">
-        <v>770.8389701590906</v>
+        <v>770.8389102077002</v>
       </c>
       <c r="E542" t="n">
-        <v>782.5619103539522</v>
+        <v>782.5618494908194</v>
       </c>
       <c r="F542" t="n">
         <v>161376</v>
@@ -11272,16 +11272,16 @@
         <v>43747</v>
       </c>
       <c r="B543" t="n">
-        <v>795.1695556640625</v>
+        <v>795.1696166992188</v>
       </c>
       <c r="C543" t="n">
-        <v>795.1695556640625</v>
+        <v>795.1696166992188</v>
       </c>
       <c r="D543" t="n">
-        <v>777.4745458323913</v>
+        <v>777.4746055093244</v>
       </c>
       <c r="E543" t="n">
-        <v>789.6398284107107</v>
+        <v>789.6398890214194</v>
       </c>
       <c r="F543" t="n">
         <v>80085</v>
@@ -11292,16 +11292,16 @@
         <v>43748</v>
       </c>
       <c r="B544" t="n">
-        <v>792.5153198242188</v>
+        <v>792.515380859375</v>
       </c>
       <c r="C544" t="n">
-        <v>808.8832432381029</v>
+        <v>808.8833055338263</v>
       </c>
       <c r="D544" t="n">
-        <v>783.8890151190678</v>
+        <v>783.8890754898738</v>
       </c>
       <c r="E544" t="n">
-        <v>798.9297921592629</v>
+        <v>798.9298536884264</v>
       </c>
       <c r="F544" t="n">
         <v>229776</v>
@@ -11352,16 +11352,16 @@
         <v>43753</v>
       </c>
       <c r="B547" t="n">
-        <v>817.9519653320312</v>
+        <v>817.951904296875</v>
       </c>
       <c r="C547" t="n">
-        <v>824.3663791006722</v>
+        <v>824.3663175868757</v>
       </c>
       <c r="D547" t="n">
-        <v>804.0171335541686</v>
+        <v>804.0170735588223</v>
       </c>
       <c r="E547" t="n">
-        <v>807.556112365897</v>
+        <v>807.5560521064739</v>
       </c>
       <c r="F547" t="n">
         <v>148942</v>
@@ -11372,16 +11372,16 @@
         <v>43754</v>
       </c>
       <c r="B548" t="n">
-        <v>813.9705200195312</v>
+        <v>813.9705810546875</v>
       </c>
       <c r="C548" t="n">
-        <v>817.951900210513</v>
+        <v>817.951961544211</v>
       </c>
       <c r="D548" t="n">
-        <v>806.4501026090501</v>
+        <v>806.4501630802918</v>
       </c>
       <c r="E548" t="n">
-        <v>816.1823522559995</v>
+        <v>816.1824134570088</v>
       </c>
       <c r="F548" t="n">
         <v>165832</v>
@@ -11412,16 +11412,16 @@
         <v>43756</v>
       </c>
       <c r="B550" t="n">
-        <v>824.1451416015625</v>
+        <v>824.1452026367188</v>
       </c>
       <c r="C550" t="n">
-        <v>832.1079022633679</v>
+        <v>832.1079638882363</v>
       </c>
       <c r="D550" t="n">
-        <v>821.712108449083</v>
+        <v>821.7121693040519</v>
       </c>
       <c r="E550" t="n">
-        <v>823.7027986145343</v>
+        <v>823.7028596169313</v>
       </c>
       <c r="F550" t="n">
         <v>77690</v>
@@ -11432,16 +11432,16 @@
         <v>43759</v>
       </c>
       <c r="B551" t="n">
-        <v>854.8901977539062</v>
+        <v>854.8902587890625</v>
       </c>
       <c r="C551" t="n">
-        <v>854.8901977539062</v>
+        <v>854.8902587890625</v>
       </c>
       <c r="D551" t="n">
-        <v>812.8645641458583</v>
+        <v>812.8646221805811</v>
       </c>
       <c r="E551" t="n">
-        <v>824.145102082814</v>
+        <v>824.1451609229144</v>
       </c>
       <c r="F551" t="n">
         <v>154924</v>
@@ -11492,16 +11492,16 @@
         <v>43762</v>
       </c>
       <c r="B554" t="n">
-        <v>860.4199829101562</v>
+        <v>860.419921875</v>
       </c>
       <c r="C554" t="n">
-        <v>875.2395600295914</v>
+        <v>875.2394979431867</v>
       </c>
       <c r="D554" t="n">
-        <v>855.7750583472094</v>
+        <v>855.7749976415478</v>
       </c>
       <c r="E554" t="n">
-        <v>863.7378197062811</v>
+        <v>863.7377584357694</v>
       </c>
       <c r="F554" t="n">
         <v>162584</v>
@@ -11512,16 +11512,16 @@
         <v>43763</v>
       </c>
       <c r="B555" t="n">
-        <v>855.9961547851562</v>
+        <v>855.9962158203125</v>
       </c>
       <c r="C555" t="n">
-        <v>871.2580730686105</v>
+        <v>871.2581351919885</v>
       </c>
       <c r="D555" t="n">
-        <v>852.4571762526242</v>
+        <v>852.4572370354404</v>
       </c>
       <c r="E555" t="n">
-        <v>865.9496052698125</v>
+        <v>865.9496670146802</v>
       </c>
       <c r="F555" t="n">
         <v>281561</v>
@@ -11572,16 +11572,16 @@
         <v>43768</v>
       </c>
       <c r="B558" t="n">
-        <v>826.1358032226562</v>
+        <v>826.1358642578125</v>
       </c>
       <c r="C558" t="n">
-        <v>842.7248677983947</v>
+        <v>842.7249300591559</v>
       </c>
       <c r="D558" t="n">
-        <v>815.0764659651826</v>
+        <v>815.0765261832718</v>
       </c>
       <c r="E558" t="n">
-        <v>833.877362778699</v>
+        <v>833.8774243858039</v>
       </c>
       <c r="F558" t="n">
         <v>414767</v>
@@ -11592,16 +11592,16 @@
         <v>43769</v>
       </c>
       <c r="B559" t="n">
-        <v>835.8681030273438</v>
+        <v>835.8680419921875</v>
       </c>
       <c r="C559" t="n">
-        <v>840.2918851473819</v>
+        <v>840.2918237892007</v>
       </c>
       <c r="D559" t="n">
-        <v>820.3849829862731</v>
+        <v>820.3849230816957</v>
       </c>
       <c r="E559" t="n">
-        <v>827.6842000085235</v>
+        <v>827.6841395709565</v>
       </c>
       <c r="F559" t="n">
         <v>215786</v>
@@ -11612,16 +11612,16 @@
         <v>43770</v>
       </c>
       <c r="B560" t="n">
-        <v>848.2545776367188</v>
+        <v>848.254638671875</v>
       </c>
       <c r="C560" t="n">
-        <v>858.8715717036641</v>
+        <v>858.8716335027536</v>
       </c>
       <c r="D560" t="n">
-        <v>836.3104373028327</v>
+        <v>836.3104974785625</v>
       </c>
       <c r="E560" t="n">
-        <v>840.513018240206</v>
+        <v>840.5130787183275</v>
       </c>
       <c r="F560" t="n">
         <v>349209</v>
@@ -11652,16 +11652,16 @@
         <v>43774</v>
       </c>
       <c r="B562" t="n">
-        <v>855.9961547851562</v>
+        <v>855.9962158203125</v>
       </c>
       <c r="C562" t="n">
-        <v>869.4885838023446</v>
+        <v>869.4886457995524</v>
       </c>
       <c r="D562" t="n">
-        <v>848.2545952280965</v>
+        <v>848.2546557112557</v>
       </c>
       <c r="E562" t="n">
-        <v>858.2080457127528</v>
+        <v>858.2081069056236</v>
       </c>
       <c r="F562" t="n">
         <v>167131</v>
@@ -11712,16 +11712,16 @@
         <v>43777</v>
       </c>
       <c r="B565" t="n">
-        <v>776.3685913085938</v>
+        <v>776.36865234375</v>
       </c>
       <c r="C565" t="n">
-        <v>807.7772304582729</v>
+        <v>807.7772939626574</v>
       </c>
       <c r="D565" t="n">
-        <v>771.9448095576114</v>
+        <v>771.9448702449868</v>
       </c>
       <c r="E565" t="n">
-        <v>807.1136866714362</v>
+        <v>807.1137501236553</v>
       </c>
       <c r="F565" t="n">
         <v>568905</v>
@@ -11732,16 +11732,16 @@
         <v>43780</v>
       </c>
       <c r="B566" t="n">
-        <v>806.2290649414062</v>
+        <v>806.22900390625</v>
       </c>
       <c r="C566" t="n">
-        <v>809.5468430707991</v>
+        <v>809.5467817844722</v>
       </c>
       <c r="D566" t="n">
-        <v>765.309312266098</v>
+        <v>765.3092543287505</v>
       </c>
       <c r="E566" t="n">
-        <v>774.1568184270383</v>
+        <v>774.1567598198949</v>
       </c>
       <c r="F566" t="n">
         <v>251817</v>
@@ -11752,16 +11752,16 @@
         <v>43781</v>
       </c>
       <c r="B567" t="n">
-        <v>808.8832397460938</v>
+        <v>808.8831787109375</v>
       </c>
       <c r="C567" t="n">
-        <v>813.528163999656</v>
+        <v>813.5281026140121</v>
       </c>
       <c r="D567" t="n">
-        <v>792.5153164028711</v>
+        <v>792.5152566027742</v>
       </c>
       <c r="E567" t="n">
-        <v>808.4408380602634</v>
+        <v>808.4407770584892</v>
       </c>
       <c r="F567" t="n">
         <v>229237</v>
@@ -11772,16 +11772,16 @@
         <v>43782</v>
       </c>
       <c r="B568" t="n">
-        <v>807.55615234375</v>
+        <v>807.5560913085938</v>
       </c>
       <c r="C568" t="n">
-        <v>810.210445273479</v>
+        <v>810.210384037711</v>
       </c>
       <c r="D568" t="n">
-        <v>793.1789768474492</v>
+        <v>793.178916898921</v>
       </c>
       <c r="E568" t="n">
-        <v>807.3349514846833</v>
+        <v>807.3348904662455</v>
       </c>
       <c r="F568" t="n">
         <v>158441</v>
@@ -11812,16 +11812,16 @@
         <v>43787</v>
       </c>
       <c r="B570" t="n">
-        <v>805.7865600585938</v>
+        <v>805.78662109375</v>
       </c>
       <c r="C570" t="n">
-        <v>832.7714768048862</v>
+        <v>832.7715398840436</v>
       </c>
       <c r="D570" t="n">
-        <v>805.565359227745</v>
+        <v>805.5654202461462</v>
       </c>
       <c r="E570" t="n">
-        <v>829.6748412415876</v>
+        <v>829.6749040861871</v>
       </c>
       <c r="F570" t="n">
         <v>210918</v>
@@ -11832,16 +11832,16 @@
         <v>43788</v>
       </c>
       <c r="B571" t="n">
-        <v>818.7593994140625</v>
+        <v>818.7594604492188</v>
       </c>
       <c r="C571" t="n">
-        <v>818.9818426132675</v>
+        <v>818.981903665006</v>
       </c>
       <c r="D571" t="n">
-        <v>804.5200829239741</v>
+        <v>804.5201428976476</v>
       </c>
       <c r="E571" t="n">
-        <v>813.1971387375502</v>
+        <v>813.1971993580627</v>
       </c>
       <c r="F571" t="n">
         <v>132996</v>
@@ -11852,16 +11852,16 @@
         <v>43790</v>
       </c>
       <c r="B572" t="n">
-        <v>835.0010375976562</v>
+        <v>835.0010986328125</v>
       </c>
       <c r="C572" t="n">
-        <v>841.8981934326687</v>
+        <v>841.8982549719789</v>
       </c>
       <c r="D572" t="n">
-        <v>804.9650668502497</v>
+        <v>804.9651256898997</v>
       </c>
       <c r="E572" t="n">
-        <v>814.5320723209652</v>
+        <v>814.5321318599239</v>
       </c>
       <c r="F572" t="n">
         <v>256564</v>
@@ -11872,16 +11872,16 @@
         <v>43791</v>
       </c>
       <c r="B573" t="n">
-        <v>837.2259521484375</v>
+        <v>837.2260131835938</v>
       </c>
       <c r="C573" t="n">
-        <v>839.0058519275486</v>
+        <v>839.0059130924625</v>
       </c>
       <c r="D573" t="n">
-        <v>820.316786177245</v>
+        <v>820.3168459796951</v>
       </c>
       <c r="E573" t="n">
-        <v>835.0010479071394</v>
+        <v>835.0011087800964</v>
       </c>
       <c r="F573" t="n">
         <v>175470</v>
@@ -11912,16 +11912,16 @@
         <v>43795</v>
       </c>
       <c r="B575" t="n">
-        <v>821.4293212890625</v>
+        <v>821.4292602539062</v>
       </c>
       <c r="C575" t="n">
-        <v>829.8838756114353</v>
+        <v>829.8838139480753</v>
       </c>
       <c r="D575" t="n">
-        <v>807.8575103086214</v>
+        <v>807.8574502818997</v>
       </c>
       <c r="E575" t="n">
-        <v>823.6542257551486</v>
+        <v>823.654164554674</v>
       </c>
       <c r="F575" t="n">
         <v>294042</v>
@@ -12012,16 +12012,16 @@
         <v>43802</v>
       </c>
       <c r="B580" t="n">
-        <v>828.10400390625</v>
+        <v>828.1039428710938</v>
       </c>
       <c r="C580" t="n">
-        <v>835.4461652809086</v>
+        <v>835.4461037046005</v>
       </c>
       <c r="D580" t="n">
-        <v>820.9843447927564</v>
+        <v>820.9842842823524</v>
       </c>
       <c r="E580" t="n">
-        <v>828.9939539160833</v>
+        <v>828.9938928153337</v>
       </c>
       <c r="F580" t="n">
         <v>140261</v>
@@ -12032,16 +12032,16 @@
         <v>43803</v>
       </c>
       <c r="B581" t="n">
-        <v>820.9841918945312</v>
+        <v>820.9842529296875</v>
       </c>
       <c r="C581" t="n">
-        <v>831.6637080932562</v>
+        <v>831.6637699223692</v>
       </c>
       <c r="D581" t="n">
-        <v>815.4219906102576</v>
+        <v>815.4220512318982</v>
       </c>
       <c r="E581" t="n">
-        <v>831.6637080932562</v>
+        <v>831.6637699223692</v>
       </c>
       <c r="F581" t="n">
         <v>148560</v>
@@ -12072,16 +12072,16 @@
         <v>43805</v>
       </c>
       <c r="B583" t="n">
-        <v>824.7666015625</v>
+        <v>824.7666625976562</v>
       </c>
       <c r="C583" t="n">
-        <v>833.221155101445</v>
+        <v>833.2212167622632</v>
       </c>
       <c r="D583" t="n">
-        <v>820.9842407067104</v>
+        <v>820.9843014619607</v>
       </c>
       <c r="E583" t="n">
-        <v>823.2091449666292</v>
+        <v>823.209205886529</v>
       </c>
       <c r="F583" t="n">
         <v>143460</v>
@@ -12132,16 +12132,16 @@
         <v>43810</v>
       </c>
       <c r="B586" t="n">
-        <v>817.4244995117188</v>
+        <v>817.4244384765625</v>
       </c>
       <c r="C586" t="n">
-        <v>824.0991537334627</v>
+        <v>824.0990921999258</v>
       </c>
       <c r="D586" t="n">
-        <v>812.5297452111301</v>
+        <v>812.5296845414535</v>
       </c>
       <c r="E586" t="n">
-        <v>821.6518061005801</v>
+        <v>821.6517447497808</v>
       </c>
       <c r="F586" t="n">
         <v>143517</v>
@@ -12152,16 +12152,16 @@
         <v>43811</v>
       </c>
       <c r="B587" t="n">
-        <v>835.2235717773438</v>
+        <v>835.2236328125</v>
       </c>
       <c r="C587" t="n">
-        <v>836.5585261636726</v>
+        <v>836.5585872963826</v>
       </c>
       <c r="D587" t="n">
-        <v>819.4268575175364</v>
+        <v>819.4269173983253</v>
       </c>
       <c r="E587" t="n">
-        <v>820.7618119038652</v>
+        <v>820.7618718822077</v>
       </c>
       <c r="F587" t="n">
         <v>149190</v>
@@ -12192,16 +12192,16 @@
         <v>43815</v>
       </c>
       <c r="B589" t="n">
-        <v>817.4244995117188</v>
+        <v>817.4244384765625</v>
       </c>
       <c r="C589" t="n">
-        <v>822.5417560611577</v>
+        <v>822.5416946439079</v>
       </c>
       <c r="D589" t="n">
-        <v>815.6445995905635</v>
+        <v>815.6445386883082</v>
       </c>
       <c r="E589" t="n">
-        <v>817.2019972628685</v>
+        <v>817.201936244326</v>
       </c>
       <c r="F589" t="n">
         <v>114381</v>
@@ -12212,16 +12212,16 @@
         <v>43816</v>
       </c>
       <c r="B590" t="n">
-        <v>828.10400390625</v>
+        <v>828.1039428710938</v>
       </c>
       <c r="C590" t="n">
-        <v>829.8839039259168</v>
+        <v>829.8838427595736</v>
       </c>
       <c r="D590" t="n">
-        <v>819.2044447730896</v>
+        <v>819.2043843938726</v>
       </c>
       <c r="E590" t="n">
-        <v>819.6494492954196</v>
+        <v>819.6493888834036</v>
       </c>
       <c r="F590" t="n">
         <v>131975</v>
@@ -12252,16 +12252,16 @@
         <v>43818</v>
       </c>
       <c r="B592" t="n">
-        <v>851.020263671875</v>
+        <v>851.0203247070312</v>
       </c>
       <c r="C592" t="n">
-        <v>855.4700721528143</v>
+        <v>855.4701335071107</v>
       </c>
       <c r="D592" t="n">
-        <v>831.6637502703173</v>
+        <v>831.6638099172249</v>
       </c>
       <c r="E592" t="n">
-        <v>851.2427659028857</v>
+        <v>851.2428269539998</v>
       </c>
       <c r="F592" t="n">
         <v>220621</v>
@@ -12312,16 +12312,16 @@
         <v>43825</v>
       </c>
       <c r="B595" t="n">
-        <v>889.288330078125</v>
+        <v>889.2883911132812</v>
       </c>
       <c r="C595" t="n">
-        <v>889.288330078125</v>
+        <v>889.2883911132812</v>
       </c>
       <c r="D595" t="n">
-        <v>855.915003172138</v>
+        <v>855.9150619167591</v>
       </c>
       <c r="E595" t="n">
-        <v>867.484410572119</v>
+        <v>867.4844701107916</v>
       </c>
       <c r="F595" t="n">
         <v>118811</v>
@@ -12432,16 +12432,16 @@
         <v>43837</v>
       </c>
       <c r="B601" t="n">
-        <v>878.1639404296875</v>
+        <v>878.1640014648438</v>
       </c>
       <c r="C601" t="n">
-        <v>879.7213379744908</v>
+        <v>879.7213991178911</v>
       </c>
       <c r="D601" t="n">
-        <v>864.592071813634</v>
+        <v>864.5921319055027</v>
       </c>
       <c r="E601" t="n">
-        <v>872.8241820685562</v>
+        <v>872.8242427325824</v>
       </c>
       <c r="F601" t="n">
         <v>133796</v>
@@ -12472,16 +12472,16 @@
         <v>43839</v>
       </c>
       <c r="B603" t="n">
-        <v>915.5420532226562</v>
+        <v>915.5421752929688</v>
       </c>
       <c r="C603" t="n">
-        <v>921.1042546664174</v>
+        <v>921.1043774783449</v>
       </c>
       <c r="D603" t="n">
-        <v>877.9414203336983</v>
+        <v>877.9415373906736</v>
       </c>
       <c r="E603" t="n">
-        <v>880.1663245251297</v>
+        <v>880.1664418787541</v>
       </c>
       <c r="F603" t="n">
         <v>555906</v>
@@ -12532,16 +12532,16 @@
         <v>43844</v>
       </c>
       <c r="B606" t="n">
-        <v>917.5444946289062</v>
+        <v>917.5445556640625</v>
       </c>
       <c r="C606" t="n">
-        <v>929.5589069372982</v>
+        <v>929.5589687716543</v>
       </c>
       <c r="D606" t="n">
-        <v>911.0922840033685</v>
+        <v>911.0923446093229</v>
       </c>
       <c r="E606" t="n">
-        <v>919.991842116827</v>
+        <v>919.991903314781</v>
       </c>
       <c r="F606" t="n">
         <v>179395</v>
@@ -12552,16 +12552,16 @@
         <v>43845</v>
       </c>
       <c r="B607" t="n">
-        <v>939.1259765625</v>
+        <v>939.1259155273438</v>
       </c>
       <c r="C607" t="n">
-        <v>945.3556853758477</v>
+        <v>945.3556239358136</v>
       </c>
       <c r="D607" t="n">
-        <v>909.3124460005382</v>
+        <v>909.3123869030065</v>
       </c>
       <c r="E607" t="n">
-        <v>912.204798156416</v>
+        <v>912.2047388709061</v>
       </c>
       <c r="F607" t="n">
         <v>262820</v>
@@ -12592,16 +12592,16 @@
         <v>43847</v>
       </c>
       <c r="B609" t="n">
-        <v>961.3748779296875</v>
+        <v>961.3748168945312</v>
       </c>
       <c r="C609" t="n">
-        <v>961.3748779296875</v>
+        <v>961.3748168945312</v>
       </c>
       <c r="D609" t="n">
-        <v>927.779046115251</v>
+        <v>927.7789872130055</v>
       </c>
       <c r="E609" t="n">
-        <v>927.779046115251</v>
+        <v>927.7789872130055</v>
       </c>
       <c r="F609" t="n">
         <v>135692</v>
@@ -12612,16 +12612,16 @@
         <v>43850</v>
       </c>
       <c r="B610" t="n">
-        <v>975.6140747070312</v>
+        <v>975.6141357421875</v>
       </c>
       <c r="C610" t="n">
-        <v>983.178737318101</v>
+        <v>983.1787988265082</v>
       </c>
       <c r="D610" t="n">
-        <v>952.6977027124357</v>
+        <v>952.6977623139263</v>
       </c>
       <c r="E610" t="n">
-        <v>957.3700134246553</v>
+        <v>957.3700733184493</v>
       </c>
       <c r="F610" t="n">
         <v>110330</v>
@@ -12652,16 +12652,16 @@
         <v>43852</v>
       </c>
       <c r="B612" t="n">
-        <v>998.9754028320312</v>
+        <v>998.9754638671875</v>
       </c>
       <c r="C612" t="n">
-        <v>998.9754028320312</v>
+        <v>998.9754638671875</v>
       </c>
       <c r="D612" t="n">
-        <v>960.4848188104922</v>
+        <v>960.4848774939602</v>
       </c>
       <c r="E612" t="n">
-        <v>961.1523255107145</v>
+        <v>961.1523842349657</v>
       </c>
       <c r="F612" t="n">
         <v>125437</v>
@@ -12672,16 +12672,16 @@
         <v>43853</v>
       </c>
       <c r="B613" t="n">
-        <v>976.2816772460938</v>
+        <v>976.2816162109375</v>
       </c>
       <c r="C613" t="n">
-        <v>996.3056993076882</v>
+        <v>996.3056370206705</v>
       </c>
       <c r="D613" t="n">
-        <v>974.7242205108452</v>
+        <v>974.7241595730579</v>
       </c>
       <c r="E613" t="n">
-        <v>984.95873379451</v>
+        <v>984.9586722168816</v>
       </c>
       <c r="F613" t="n">
         <v>197093</v>
@@ -12692,16 +12692,16 @@
         <v>43854</v>
       </c>
       <c r="B614" t="n">
-        <v>952.69775390625</v>
+        <v>952.6976928710938</v>
       </c>
       <c r="C614" t="n">
-        <v>982.7337856638734</v>
+        <v>982.7337227044407</v>
       </c>
       <c r="D614" t="n">
-        <v>952.69775390625</v>
+        <v>952.6976928710938</v>
       </c>
       <c r="E614" t="n">
-        <v>975.8366293752512</v>
+        <v>975.8365668576889</v>
       </c>
       <c r="F614" t="n">
         <v>152264</v>
@@ -12772,16 +12772,16 @@
         <v>43860</v>
       </c>
       <c r="B618" t="n">
-        <v>982.7337646484375</v>
+        <v>982.7337036132812</v>
       </c>
       <c r="C618" t="n">
-        <v>993.4132817348734</v>
+        <v>993.4132200364389</v>
       </c>
       <c r="D618" t="n">
-        <v>961.8197939868294</v>
+        <v>961.819734250588</v>
       </c>
       <c r="E618" t="n">
-        <v>977.6165083434412</v>
+        <v>977.616447626105</v>
       </c>
       <c r="F618" t="n">
         <v>201453</v>
@@ -12812,16 +12812,16 @@
         <v>43864</v>
       </c>
       <c r="B620" t="n">
-        <v>907.0875244140625</v>
+        <v>907.0875854492188</v>
       </c>
       <c r="C620" t="n">
-        <v>956.2576282040886</v>
+        <v>956.2576925477513</v>
       </c>
       <c r="D620" t="n">
-        <v>840.1183625584863</v>
+        <v>840.1184190874917</v>
       </c>
       <c r="E620" t="n">
-        <v>845.4581213025272</v>
+        <v>845.4581781908287</v>
       </c>
       <c r="F620" t="n">
         <v>1962510</v>
@@ -12892,16 +12892,16 @@
         <v>43868</v>
       </c>
       <c r="B624" t="n">
-        <v>879.4989013671875</v>
+        <v>879.4989624023438</v>
       </c>
       <c r="C624" t="n">
-        <v>948.6929678200464</v>
+        <v>948.6930336571082</v>
       </c>
       <c r="D624" t="n">
-        <v>873.7141971479834</v>
+        <v>873.7142577816948</v>
       </c>
       <c r="E624" t="n">
-        <v>939.5709660315907</v>
+        <v>939.5710312356071</v>
       </c>
       <c r="F624" t="n">
         <v>370246</v>
@@ -12952,16 +12952,16 @@
         <v>43873</v>
       </c>
       <c r="B627" t="n">
-        <v>749.787841796875</v>
+        <v>749.7877807617188</v>
       </c>
       <c r="C627" t="n">
-        <v>783.1612314901223</v>
+        <v>783.1611677382641</v>
       </c>
       <c r="D627" t="n">
-        <v>747.7854395959766</v>
+        <v>747.7853787238224</v>
       </c>
       <c r="E627" t="n">
-        <v>781.1588292892239</v>
+        <v>781.1587657003678</v>
       </c>
       <c r="F627" t="n">
         <v>527262</v>
@@ -13032,16 +13032,16 @@
         <v>43879</v>
       </c>
       <c r="B631" t="n">
-        <v>807.6349487304688</v>
+        <v>807.635009765625</v>
       </c>
       <c r="C631" t="n">
-        <v>838.5609296259686</v>
+        <v>838.5609929982849</v>
       </c>
       <c r="D631" t="n">
-        <v>778.7113699003957</v>
+        <v>778.7114287497189</v>
       </c>
       <c r="E631" t="n">
-        <v>805.1875421905826</v>
+        <v>805.1876030407818</v>
       </c>
       <c r="F631" t="n">
         <v>685347</v>
@@ -13112,16 +13112,16 @@
         <v>43887</v>
       </c>
       <c r="B635" t="n">
-        <v>711.9647216796875</v>
+        <v>711.9646606445312</v>
       </c>
       <c r="C635" t="n">
-        <v>716.4144713038074</v>
+        <v>716.4144098871841</v>
       </c>
       <c r="D635" t="n">
-        <v>661.2372217557945</v>
+        <v>661.2371650693943</v>
       </c>
       <c r="E635" t="n">
-        <v>670.5817254838569</v>
+        <v>670.5816679963731</v>
       </c>
       <c r="F635" t="n">
         <v>736458</v>
@@ -13132,16 +13132,16 @@
         <v>43888</v>
       </c>
       <c r="B636" t="n">
-        <v>759.3547973632812</v>
+        <v>759.3548583984375</v>
       </c>
       <c r="C636" t="n">
-        <v>784.0510679196184</v>
+        <v>784.051130939803</v>
       </c>
       <c r="D636" t="n">
-        <v>713.0770511921929</v>
+        <v>713.0771085076525</v>
       </c>
       <c r="E636" t="n">
-        <v>713.0770511921929</v>
+        <v>713.0771085076525</v>
       </c>
       <c r="F636" t="n">
         <v>1264812</v>
@@ -13212,16 +13212,16 @@
         <v>43894</v>
       </c>
       <c r="B640" t="n">
-        <v>423.8414306640625</v>
+        <v>423.8414916992188</v>
       </c>
       <c r="C640" t="n">
-        <v>489.4756889538189</v>
+        <v>489.4757594406165</v>
       </c>
       <c r="D640" t="n">
-        <v>362.8794828328039</v>
+        <v>362.8795350891534</v>
       </c>
       <c r="E640" t="n">
-        <v>469.4516699454437</v>
+        <v>469.4517375486885</v>
       </c>
       <c r="F640" t="n">
         <v>6553269</v>
@@ -13272,16 +13272,16 @@
         <v>43899</v>
       </c>
       <c r="B643" t="n">
-        <v>306.1448364257812</v>
+        <v>306.1448059082031</v>
       </c>
       <c r="C643" t="n">
-        <v>347.0828315630422</v>
+        <v>347.0827969646228</v>
       </c>
       <c r="D643" t="n">
-        <v>302.8075091700803</v>
+        <v>302.8074789851785</v>
       </c>
       <c r="E643" t="n">
-        <v>333.7334930228257</v>
+        <v>333.7334597551147</v>
       </c>
       <c r="F643" t="n">
         <v>800099</v>
@@ -13292,16 +13292,16 @@
         <v>43900</v>
       </c>
       <c r="B644" t="n">
-        <v>304.8098754882812</v>
+        <v>304.8099060058594</v>
       </c>
       <c r="C644" t="n">
-        <v>342.1880071868422</v>
+        <v>342.1880414467205</v>
       </c>
       <c r="D644" t="n">
-        <v>289.9031114483475</v>
+        <v>289.9031404734598</v>
       </c>
       <c r="E644" t="n">
-        <v>337.0707805360925</v>
+        <v>337.0708142836338</v>
       </c>
       <c r="F644" t="n">
         <v>1215566</v>
@@ -13352,16 +13352,16 @@
         <v>43903</v>
       </c>
       <c r="B647" t="n">
-        <v>222.4889678955078</v>
+        <v>222.4889831542969</v>
       </c>
       <c r="C647" t="n">
-        <v>244.7378632091881</v>
+        <v>244.737879993856</v>
       </c>
       <c r="D647" t="n">
-        <v>200.4625600590938</v>
+        <v>200.4625738072628</v>
       </c>
       <c r="E647" t="n">
-        <v>244.7378632091881</v>
+        <v>244.737879993856</v>
       </c>
       <c r="F647" t="n">
         <v>1357909</v>
@@ -13372,16 +13372,16 @@
         <v>43906</v>
       </c>
       <c r="B648" t="n">
-        <v>194.6778564453125</v>
+        <v>194.6778411865234</v>
       </c>
       <c r="C648" t="n">
-        <v>208.2496821614688</v>
+        <v>208.2496658389243</v>
       </c>
       <c r="D648" t="n">
-        <v>191.5630167637396</v>
+        <v>191.5630017490907</v>
       </c>
       <c r="E648" t="n">
-        <v>196.9027461489235</v>
+        <v>196.9027307157482</v>
       </c>
       <c r="F648" t="n">
         <v>1146722</v>
@@ -13392,16 +13392,16 @@
         <v>43907</v>
       </c>
       <c r="B649" t="n">
-        <v>196.9027252197266</v>
+        <v>196.9027404785156</v>
       </c>
       <c r="C649" t="n">
-        <v>208.9171371974128</v>
+        <v>208.9171533872473</v>
       </c>
       <c r="D649" t="n">
-        <v>189.1156194641488</v>
+        <v>189.1156341194835</v>
       </c>
       <c r="E649" t="n">
-        <v>202.464956266886</v>
+        <v>202.4649719567149</v>
       </c>
       <c r="F649" t="n">
         <v>1082943</v>
@@ -13412,16 +13412,16 @@
         <v>43908</v>
       </c>
       <c r="B650" t="n">
-        <v>160.1920471191406</v>
+        <v>160.1920776367188</v>
       </c>
       <c r="C650" t="n">
-        <v>185.3332922147648</v>
+        <v>185.333327521906</v>
       </c>
       <c r="D650" t="n">
-        <v>150.1800377172615</v>
+        <v>150.1800663274898</v>
       </c>
       <c r="E650" t="n">
-        <v>185.1108047568012</v>
+        <v>185.1108400215572</v>
       </c>
       <c r="F650" t="n">
         <v>1085342</v>
@@ -13552,16 +13552,16 @@
         <v>43917</v>
       </c>
       <c r="B657" t="n">
-        <v>231.3885498046875</v>
+        <v>231.3885345458984</v>
       </c>
       <c r="C657" t="n">
-        <v>241.1780588454579</v>
+        <v>241.1780429411052</v>
       </c>
       <c r="D657" t="n">
-        <v>206.2472851849431</v>
+        <v>206.2472715840807</v>
       </c>
       <c r="E657" t="n">
-        <v>212.2544919647103</v>
+        <v>212.254477967706</v>
       </c>
       <c r="F657" t="n">
         <v>1391484</v>
@@ -13572,16 +13572,16 @@
         <v>43920</v>
       </c>
       <c r="B658" t="n">
-        <v>238.9531555175781</v>
+        <v>238.9531402587891</v>
       </c>
       <c r="C658" t="n">
-        <v>262.981981272284</v>
+        <v>262.9819644790905</v>
       </c>
       <c r="D658" t="n">
-        <v>235.6158284463394</v>
+        <v>235.6158134006614</v>
       </c>
       <c r="E658" t="n">
-        <v>240.288095201297</v>
+        <v>240.2880798572629</v>
       </c>
       <c r="F658" t="n">
         <v>1073465</v>
@@ -13592,16 +13592,16 @@
         <v>43921</v>
       </c>
       <c r="B659" t="n">
-        <v>215.3693084716797</v>
+        <v>215.3693237304688</v>
       </c>
       <c r="C659" t="n">
-        <v>244.5153744643405</v>
+        <v>244.5153917881112</v>
       </c>
       <c r="D659" t="n">
-        <v>208.4721524360645</v>
+        <v>208.4721672061941</v>
       </c>
       <c r="E659" t="n">
-        <v>244.5153744643405</v>
+        <v>244.5153917881112</v>
       </c>
       <c r="F659" t="n">
         <v>1005243</v>
@@ -13612,16 +13612,16 @@
         <v>43922</v>
       </c>
       <c r="B660" t="n">
-        <v>207.1372375488281</v>
+        <v>207.1372222900391</v>
       </c>
       <c r="C660" t="n">
-        <v>208.0271874961128</v>
+        <v>208.0271721717654</v>
       </c>
       <c r="D660" t="n">
-        <v>195.3453121950729</v>
+        <v>195.3452978049374</v>
       </c>
       <c r="E660" t="n">
-        <v>201.3525186153611</v>
+        <v>201.352503782704</v>
       </c>
       <c r="F660" t="n">
         <v>767742</v>
@@ -13652,16 +13652,16 @@
         <v>43924</v>
       </c>
       <c r="B662" t="n">
-        <v>191.1180114746094</v>
+        <v>191.1180267333984</v>
       </c>
       <c r="C662" t="n">
-        <v>202.4649456881939</v>
+        <v>202.4649618529179</v>
       </c>
       <c r="D662" t="n">
-        <v>183.1084039079832</v>
+        <v>183.1084185272883</v>
       </c>
       <c r="E662" t="n">
-        <v>200.4625437965374</v>
+        <v>200.4625598013904</v>
       </c>
       <c r="F662" t="n">
         <v>765433</v>
@@ -13672,16 +13672,16 @@
         <v>43927</v>
       </c>
       <c r="B663" t="n">
-        <v>226.4937744140625</v>
+        <v>226.4937896728516</v>
       </c>
       <c r="C663" t="n">
-        <v>226.4937744140625</v>
+        <v>226.4937896728516</v>
       </c>
       <c r="D663" t="n">
-        <v>200.9075371516884</v>
+        <v>200.9075506867436</v>
       </c>
       <c r="E663" t="n">
-        <v>205.8022912210472</v>
+        <v>205.8023050858598</v>
       </c>
       <c r="F663" t="n">
         <v>959201</v>
@@ -13712,16 +13712,16 @@
         <v>43929</v>
       </c>
       <c r="B665" t="n">
-        <v>225.6038208007812</v>
+        <v>225.6038055419922</v>
       </c>
       <c r="C665" t="n">
-        <v>226.938760502758</v>
+        <v>226.9387451536799</v>
       </c>
       <c r="D665" t="n">
-        <v>214.7018599705395</v>
+        <v>214.7018454491082</v>
       </c>
       <c r="E665" t="n">
-        <v>216.9267496346969</v>
+        <v>216.9267349627844</v>
       </c>
       <c r="F665" t="n">
         <v>1185635</v>
@@ -13752,16 +13752,16 @@
         <v>43934</v>
       </c>
       <c r="B667" t="n">
-        <v>231.1660461425781</v>
+        <v>231.1660614013672</v>
       </c>
       <c r="C667" t="n">
-        <v>234.0583982008221</v>
+        <v>234.0584136505294</v>
       </c>
       <c r="D667" t="n">
-        <v>221.5990105121156</v>
+        <v>221.5990251394046</v>
       </c>
       <c r="E667" t="n">
-        <v>224.713864813645</v>
+        <v>224.713879646539</v>
       </c>
       <c r="F667" t="n">
         <v>570405</v>
@@ -13812,16 +13812,16 @@
         <v>43937</v>
       </c>
       <c r="B670" t="n">
-        <v>262.7594909667969</v>
+        <v>262.7594604492188</v>
       </c>
       <c r="C670" t="n">
-        <v>275.6638543805785</v>
+        <v>275.6638223642537</v>
       </c>
       <c r="D670" t="n">
-        <v>259.4221637438982</v>
+        <v>259.422133613926</v>
       </c>
       <c r="E670" t="n">
-        <v>273.8839543996759</v>
+        <v>273.8839225900734</v>
       </c>
       <c r="F670" t="n">
         <v>858661</v>
@@ -13872,16 +13872,16 @@
         <v>43943</v>
       </c>
       <c r="B673" t="n">
-        <v>246.0728149414062</v>
+        <v>246.0727996826172</v>
       </c>
       <c r="C673" t="n">
-        <v>270.1016274556211</v>
+        <v>270.1016107068236</v>
       </c>
       <c r="D673" t="n">
-        <v>245.1828649351676</v>
+        <v>245.1828497315637</v>
       </c>
       <c r="E673" t="n">
-        <v>266.9867729163728</v>
+        <v>266.9867563607251</v>
       </c>
       <c r="F673" t="n">
         <v>1710454</v>
@@ -13892,16 +13892,16 @@
         <v>43944</v>
       </c>
       <c r="B674" t="n">
-        <v>225.1588287353516</v>
+        <v>225.1588439941406</v>
       </c>
       <c r="C674" t="n">
-        <v>243.6254071190605</v>
+        <v>243.6254236293111</v>
       </c>
       <c r="D674" t="n">
-        <v>216.0367832803288</v>
+        <v>216.036797920926</v>
       </c>
       <c r="E674" t="n">
-        <v>237.8407032863998</v>
+        <v>237.8407194046269</v>
       </c>
       <c r="F674" t="n">
         <v>2199225</v>
@@ -13912,16 +13912,16 @@
         <v>43945</v>
       </c>
       <c r="B675" t="n">
-        <v>201.7974853515625</v>
+        <v>201.7975006103516</v>
       </c>
       <c r="C675" t="n">
-        <v>219.5966016403344</v>
+        <v>219.5966182449923</v>
       </c>
       <c r="D675" t="n">
-        <v>183.7758815850515</v>
+        <v>183.7758954811484</v>
       </c>
       <c r="E675" t="n">
-        <v>218.2616767738995</v>
+        <v>218.261693277618</v>
       </c>
       <c r="F675" t="n">
         <v>2006627</v>
@@ -13932,16 +13932,16 @@
         <v>43948</v>
       </c>
       <c r="B676" t="n">
-        <v>210.4745483398438</v>
+        <v>210.4745635986328</v>
       </c>
       <c r="C676" t="n">
-        <v>216.9267292350107</v>
+        <v>216.926744961564</v>
       </c>
       <c r="D676" t="n">
-        <v>204.9123320818714</v>
+        <v>204.9123469374161</v>
       </c>
       <c r="E676" t="n">
-        <v>210.0295734005987</v>
+        <v>210.0295886271283</v>
       </c>
       <c r="F676" t="n">
         <v>1136627</v>
@@ -13972,16 +13972,16 @@
         <v>43950</v>
       </c>
       <c r="B678" t="n">
-        <v>228.0511932373047</v>
+        <v>228.0512084960938</v>
       </c>
       <c r="C678" t="n">
-        <v>230.276082855431</v>
+        <v>230.2760982630863</v>
       </c>
       <c r="D678" t="n">
-        <v>202.6874574941464</v>
+        <v>202.6874710558608</v>
       </c>
       <c r="E678" t="n">
-        <v>204.4673721403886</v>
+        <v>204.4673858211962</v>
       </c>
       <c r="F678" t="n">
         <v>2221988</v>
@@ -14032,16 +14032,16 @@
         <v>43956</v>
       </c>
       <c r="B681" t="n">
-        <v>200.4625549316406</v>
+        <v>200.4625701904297</v>
       </c>
       <c r="C681" t="n">
-        <v>219.5965955567701</v>
+        <v>219.5966122720022</v>
       </c>
       <c r="D681" t="n">
-        <v>199.7950777582095</v>
+        <v>199.7950929661916</v>
       </c>
       <c r="E681" t="n">
-        <v>216.0367812528576</v>
+        <v>216.0367976971241</v>
       </c>
       <c r="F681" t="n">
         <v>1156334</v>
@@ -14112,16 +14112,16 @@
         <v>43962</v>
       </c>
       <c r="B685" t="n">
-        <v>171.3165130615234</v>
+        <v>171.3164978027344</v>
       </c>
       <c r="C685" t="n">
-        <v>177.7686795848986</v>
+        <v>177.7686637514292</v>
       </c>
       <c r="D685" t="n">
-        <v>169.5365984391037</v>
+        <v>169.5365833388478</v>
       </c>
       <c r="E685" t="n">
-        <v>175.76629223822</v>
+        <v>175.7662765830988</v>
       </c>
       <c r="F685" t="n">
         <v>2483473</v>
@@ -14132,16 +14132,16 @@
         <v>43963</v>
       </c>
       <c r="B686" t="n">
-        <v>178.8811187744141</v>
+        <v>178.8811340332031</v>
       </c>
       <c r="C686" t="n">
-        <v>190.6730283091375</v>
+        <v>190.6730445737916</v>
       </c>
       <c r="D686" t="n">
-        <v>170.2040485338067</v>
+        <v>170.2040630524306</v>
       </c>
       <c r="E686" t="n">
-        <v>174.4313399207028</v>
+        <v>174.43135479992</v>
       </c>
       <c r="F686" t="n">
         <v>2218366</v>
@@ -14152,16 +14152,16 @@
         <v>43964</v>
       </c>
       <c r="B687" t="n">
-        <v>164.8643341064453</v>
+        <v>164.8643493652344</v>
       </c>
       <c r="C687" t="n">
-        <v>183.7758884949831</v>
+        <v>183.7759055041047</v>
       </c>
       <c r="D687" t="n">
-        <v>163.529394431112</v>
+        <v>163.5294095663476</v>
       </c>
       <c r="E687" t="n">
-        <v>180.4385614447081</v>
+        <v>180.4385781449481</v>
       </c>
       <c r="F687" t="n">
         <v>1360979</v>
@@ -14212,16 +14212,16 @@
         <v>43969</v>
       </c>
       <c r="B690" t="n">
-        <v>163.5293884277344</v>
+        <v>163.5294036865234</v>
       </c>
       <c r="C690" t="n">
-        <v>163.5293884277344</v>
+        <v>163.5294036865234</v>
       </c>
       <c r="D690" t="n">
-        <v>149.2901012875477</v>
+        <v>149.290115217681</v>
       </c>
       <c r="E690" t="n">
-        <v>153.0724031711787</v>
+        <v>153.0724174542353</v>
       </c>
       <c r="F690" t="n">
         <v>1711636</v>
@@ -14252,16 +14252,16 @@
         <v>43971</v>
       </c>
       <c r="B692" t="n">
-        <v>169.3141326904297</v>
+        <v>169.3141174316406</v>
       </c>
       <c r="C692" t="n">
-        <v>170.6490577595753</v>
+        <v>170.6490423804813</v>
       </c>
       <c r="D692" t="n">
-        <v>159.0796333667769</v>
+        <v>159.079619030333</v>
       </c>
       <c r="E692" t="n">
-        <v>160.6370607061541</v>
+        <v>160.6370462293529</v>
       </c>
       <c r="F692" t="n">
         <v>1274832</v>
@@ -14292,16 +14292,16 @@
         <v>43973</v>
       </c>
       <c r="B694" t="n">
-        <v>159.5245971679688</v>
+        <v>159.5246124267578</v>
       </c>
       <c r="C694" t="n">
-        <v>163.9743766028462</v>
+        <v>163.974392287264</v>
       </c>
       <c r="D694" t="n">
-        <v>156.6322449629103</v>
+        <v>156.6322599450411</v>
       </c>
       <c r="E694" t="n">
-        <v>158.857134680349</v>
+        <v>158.8571498752942</v>
       </c>
       <c r="F694" t="n">
         <v>1395700</v>
@@ -14332,16 +14332,16 @@
         <v>43977</v>
       </c>
       <c r="B696" t="n">
-        <v>164.4193420410156</v>
+        <v>164.4193572998047</v>
       </c>
       <c r="C696" t="n">
-        <v>186.2232629567407</v>
+        <v>186.2232802390231</v>
       </c>
       <c r="D696" t="n">
-        <v>163.9743670751244</v>
+        <v>163.9743822926179</v>
       </c>
       <c r="E696" t="n">
-        <v>180.883533848635</v>
+        <v>180.8835506353685</v>
       </c>
       <c r="F696" t="n">
         <v>1999101</v>
@@ -14352,16 +14352,16 @@
         <v>43978</v>
       </c>
       <c r="B697" t="n">
-        <v>171.3165130615234</v>
+        <v>171.3164978027344</v>
       </c>
       <c r="C697" t="n">
-        <v>171.9839755104163</v>
+        <v>171.9839601921778</v>
       </c>
       <c r="D697" t="n">
-        <v>160.8595275686749</v>
+        <v>160.8595132412668</v>
       </c>
       <c r="E697" t="n">
-        <v>165.7542817113001</v>
+        <v>165.7542669479268</v>
       </c>
       <c r="F697" t="n">
         <v>1675267</v>
@@ -14452,16 +14452,16 @@
         <v>43985</v>
       </c>
       <c r="B702" t="n">
-        <v>239.1756439208984</v>
+        <v>239.1756286621094</v>
       </c>
       <c r="C702" t="n">
-        <v>239.1756439208984</v>
+        <v>239.1756286621094</v>
       </c>
       <c r="D702" t="n">
-        <v>196.6802532298526</v>
+        <v>196.6802406821598</v>
       </c>
       <c r="E702" t="n">
-        <v>198.2376804070371</v>
+        <v>198.2376677599845</v>
       </c>
       <c r="F702" t="n">
         <v>3635130</v>
@@ -14492,16 +14492,16 @@
         <v>43987</v>
       </c>
       <c r="B704" t="n">
-        <v>239.1756439208984</v>
+        <v>239.1756286621094</v>
       </c>
       <c r="C704" t="n">
-        <v>250.9675693559012</v>
+        <v>250.9675533448177</v>
       </c>
       <c r="D704" t="n">
-        <v>231.388537552387</v>
+        <v>231.3885227903952</v>
       </c>
       <c r="E704" t="n">
-        <v>248.0752172485919</v>
+        <v>248.075201422033</v>
       </c>
       <c r="F704" t="n">
         <v>2000080</v>
@@ -14572,16 +14572,16 @@
         <v>43994</v>
       </c>
       <c r="B708" t="n">
-        <v>255.6397857666016</v>
+        <v>255.6398162841797</v>
       </c>
       <c r="C708" t="n">
-        <v>282.7834621873327</v>
+        <v>282.7834959452487</v>
       </c>
       <c r="D708" t="n">
-        <v>255.6397857666016</v>
+        <v>255.6398162841797</v>
       </c>
       <c r="E708" t="n">
-        <v>271.4364985506459</v>
+        <v>271.4365309539923</v>
       </c>
       <c r="F708" t="n">
         <v>3060334</v>
@@ -14672,16 +14672,16 @@
         <v>44001</v>
       </c>
       <c r="B713" t="n">
-        <v>231.1660461425781</v>
+        <v>231.1660614013672</v>
       </c>
       <c r="C713" t="n">
-        <v>235.3933378670069</v>
+        <v>235.3933534048307</v>
       </c>
       <c r="D713" t="n">
-        <v>226.0487897211243</v>
+        <v>226.0488046421339</v>
       </c>
       <c r="E713" t="n">
-        <v>234.5033731699819</v>
+        <v>234.503388649061</v>
       </c>
       <c r="F713" t="n">
         <v>1213992</v>
@@ -14692,16 +14692,16 @@
         <v>44004</v>
       </c>
       <c r="B714" t="n">
-        <v>269.211669921875</v>
+        <v>269.2116394042969</v>
       </c>
       <c r="C714" t="n">
-        <v>270.1016199032294</v>
+        <v>270.1015892847674</v>
       </c>
       <c r="D714" t="n">
-        <v>232.0560073023217</v>
+        <v>232.055980996674</v>
       </c>
       <c r="E714" t="n">
-        <v>233.6134345283981</v>
+        <v>233.613408046202</v>
       </c>
       <c r="F714" t="n">
         <v>3817417</v>
@@ -14732,16 +14732,16 @@
         <v>44006</v>
       </c>
       <c r="B716" t="n">
-        <v>246.0728149414062</v>
+        <v>246.0727996826172</v>
       </c>
       <c r="C716" t="n">
-        <v>270.3241297158874</v>
+        <v>270.3241129532926</v>
       </c>
       <c r="D716" t="n">
-        <v>244.7378899320483</v>
+        <v>244.7378747560369</v>
       </c>
       <c r="E716" t="n">
-        <v>261.647043361528</v>
+        <v>261.6470271369928</v>
       </c>
       <c r="F716" t="n">
         <v>2500506</v>
@@ -14752,16 +14752,16 @@
         <v>44007</v>
       </c>
       <c r="B717" t="n">
-        <v>250.3000793457031</v>
+        <v>250.3000946044922</v>
       </c>
       <c r="C717" t="n">
-        <v>255.4173355925531</v>
+        <v>255.4173511633002</v>
       </c>
       <c r="D717" t="n">
-        <v>237.3957318868463</v>
+        <v>237.3957463589608</v>
       </c>
       <c r="E717" t="n">
-        <v>248.2976772941018</v>
+        <v>248.2976924308205</v>
       </c>
       <c r="F717" t="n">
         <v>2280068</v>
@@ -14772,16 +14772,16 @@
         <v>44008</v>
       </c>
       <c r="B718" t="n">
-        <v>263.8719482421875</v>
+        <v>263.8719177246094</v>
       </c>
       <c r="C718" t="n">
-        <v>270.7691050757434</v>
+        <v>270.7690737604885</v>
       </c>
       <c r="D718" t="n">
-        <v>256.3073141443666</v>
+        <v>256.307284501661</v>
       </c>
       <c r="E718" t="n">
-        <v>266.9867732681264</v>
+        <v>266.9867423903095</v>
       </c>
       <c r="F718" t="n">
         <v>3269179</v>
@@ -14872,16 +14872,16 @@
         <v>44015</v>
       </c>
       <c r="B723" t="n">
-        <v>215.3693084716797</v>
+        <v>215.3693237304688</v>
       </c>
       <c r="C723" t="n">
-        <v>215.3693084716797</v>
+        <v>215.3693237304688</v>
       </c>
       <c r="D723" t="n">
-        <v>185.1108198571592</v>
+        <v>185.1108329721521</v>
       </c>
       <c r="E723" t="n">
-        <v>192.4529508450001</v>
+        <v>192.4529644801787</v>
       </c>
       <c r="F723" t="n">
         <v>5547968</v>
@@ -14892,16 +14892,16 @@
         <v>44018</v>
       </c>
       <c r="B724" t="n">
-        <v>211.5870056152344</v>
+        <v>211.5870208740234</v>
       </c>
       <c r="C724" t="n">
-        <v>225.1588301459637</v>
+        <v>225.1588463834972</v>
       </c>
       <c r="D724" t="n">
-        <v>208.4721514470214</v>
+        <v>208.4721664811799</v>
       </c>
       <c r="E724" t="n">
-        <v>222.0439907364555</v>
+        <v>222.0440067493595</v>
       </c>
       <c r="F724" t="n">
         <v>2999602</v>
@@ -14912,16 +14912,16 @@
         <v>44019</v>
       </c>
       <c r="B725" t="n">
-        <v>211.5870056152344</v>
+        <v>211.5870208740234</v>
       </c>
       <c r="C725" t="n">
-        <v>216.259272108849</v>
+        <v>216.2592877045829</v>
       </c>
       <c r="D725" t="n">
-        <v>206.0247744626853</v>
+        <v>206.024789320349</v>
       </c>
       <c r="E725" t="n">
-        <v>209.1396286308983</v>
+        <v>209.1396437131926</v>
       </c>
       <c r="F725" t="n">
         <v>1504661</v>
@@ -14972,16 +14972,16 @@
         <v>44022</v>
       </c>
       <c r="B728" t="n">
-        <v>204.6898498535156</v>
+        <v>204.6898651123047</v>
       </c>
       <c r="C728" t="n">
-        <v>209.5846038279549</v>
+        <v>209.5846194516278</v>
       </c>
       <c r="D728" t="n">
-        <v>202.9099352922546</v>
+        <v>202.9099504183583</v>
       </c>
       <c r="E728" t="n">
-        <v>208.0271767420134</v>
+        <v>208.0271922495865</v>
       </c>
       <c r="F728" t="n">
         <v>1246584</v>
@@ -14992,16 +14992,16 @@
         <v>44025</v>
       </c>
       <c r="B729" t="n">
-        <v>216.25927734375</v>
+        <v>216.2592926025391</v>
       </c>
       <c r="C729" t="n">
-        <v>231.3885293248135</v>
+        <v>231.38854565109</v>
       </c>
       <c r="D729" t="n">
-        <v>206.9147441303213</v>
+        <v>206.9147587297802</v>
       </c>
       <c r="E729" t="n">
-        <v>207.1372316107643</v>
+        <v>207.1372462259215</v>
       </c>
       <c r="F729" t="n">
         <v>3664113</v>
@@ -15012,16 +15012,16 @@
         <v>44026</v>
       </c>
       <c r="B730" t="n">
-        <v>223.9059448242188</v>
+        <v>223.9059753417969</v>
       </c>
       <c r="C730" t="n">
-        <v>225.8320148017794</v>
+        <v>225.8320455818739</v>
       </c>
       <c r="D730" t="n">
-        <v>211.145716464175</v>
+        <v>211.1457452425797</v>
       </c>
       <c r="E730" t="n">
-        <v>219.3315286275123</v>
+        <v>219.3315585216138</v>
       </c>
       <c r="F730" t="n">
         <v>2477565</v>
@@ -15032,16 +15032,16 @@
         <v>44027</v>
       </c>
       <c r="B731" t="n">
-        <v>220.0538330078125</v>
+        <v>220.0538177490234</v>
       </c>
       <c r="C731" t="n">
-        <v>230.6472339976995</v>
+        <v>230.6472180043517</v>
       </c>
       <c r="D731" t="n">
-        <v>217.8870040059801</v>
+        <v>217.8869888974415</v>
       </c>
       <c r="E731" t="n">
-        <v>229.9249576637553</v>
+        <v>229.924941720491</v>
       </c>
       <c r="F731" t="n">
         <v>1488094</v>
@@ -15052,16 +15052,16 @@
         <v>44028</v>
       </c>
       <c r="B732" t="n">
-        <v>215.4793853759766</v>
+        <v>215.4794006347656</v>
       </c>
       <c r="C732" t="n">
-        <v>221.0168516147299</v>
+        <v>221.0168672656448</v>
       </c>
       <c r="D732" t="n">
-        <v>214.2755915759661</v>
+        <v>214.2756067495107</v>
       </c>
       <c r="E732" t="n">
-        <v>218.368505254707</v>
+        <v>218.3685207180839</v>
       </c>
       <c r="F732" t="n">
         <v>1169687</v>
@@ -15072,16 +15072,16 @@
         <v>44029</v>
       </c>
       <c r="B733" t="n">
-        <v>216.6831817626953</v>
+        <v>216.6831970214844</v>
       </c>
       <c r="C733" t="n">
-        <v>220.0538192016677</v>
+        <v>220.0538346978164</v>
       </c>
       <c r="D733" t="n">
-        <v>215.7201467111905</v>
+        <v>215.7201619021628</v>
       </c>
       <c r="E733" t="n">
-        <v>217.6462315729056</v>
+        <v>217.6462468995125</v>
       </c>
       <c r="F733" t="n">
         <v>1022336</v>
@@ -15092,16 +15092,16 @@
         <v>44032</v>
       </c>
       <c r="B734" t="n">
-        <v>214.7570953369141</v>
+        <v>214.7571105957031</v>
       </c>
       <c r="C734" t="n">
-        <v>217.8869737751215</v>
+        <v>217.8869892562928</v>
       </c>
       <c r="D734" t="n">
-        <v>212.1087491465653</v>
+        <v>212.1087642171857</v>
       </c>
       <c r="E734" t="n">
-        <v>217.4054562859672</v>
+        <v>217.405471732926</v>
       </c>
       <c r="F734" t="n">
         <v>991145</v>
@@ -15112,16 +15112,16 @@
         <v>44033</v>
       </c>
       <c r="B735" t="n">
-        <v>205.1267242431641</v>
+        <v>205.1267395019531</v>
       </c>
       <c r="C735" t="n">
-        <v>214.0348122666898</v>
+        <v>214.034828188126</v>
       </c>
       <c r="D735" t="n">
-        <v>203.2006543480674</v>
+        <v>203.2006694635817</v>
       </c>
       <c r="E735" t="n">
-        <v>214.0348122666898</v>
+        <v>214.034828188126</v>
       </c>
       <c r="F735" t="n">
         <v>1410321</v>
@@ -15152,16 +15152,16 @@
         <v>44035</v>
       </c>
       <c r="B737" t="n">
-        <v>188.9958801269531</v>
+        <v>188.9959106445312</v>
       </c>
       <c r="C737" t="n">
-        <v>198.1447271784861</v>
+        <v>198.1447591733485</v>
       </c>
       <c r="D737" t="n">
-        <v>188.5143626378569</v>
+        <v>188.5143930776833</v>
       </c>
       <c r="E737" t="n">
-        <v>196.7001747111973</v>
+        <v>196.7002064728048</v>
       </c>
       <c r="F737" t="n">
         <v>1310991</v>
@@ -15232,16 +15232,16 @@
         <v>44041</v>
       </c>
       <c r="B741" t="n">
-        <v>196.9409484863281</v>
+        <v>196.9409332275391</v>
       </c>
       <c r="C741" t="n">
-        <v>200.3115711672486</v>
+        <v>200.311555647307</v>
       </c>
       <c r="D741" t="n">
-        <v>193.8110698096251</v>
+        <v>193.8110547933359</v>
       </c>
       <c r="E741" t="n">
-        <v>193.8110698096251</v>
+        <v>193.8110547933359</v>
       </c>
       <c r="F741" t="n">
         <v>806469</v>
@@ -15292,16 +15292,16 @@
         <v>44046</v>
       </c>
       <c r="B744" t="n">
-        <v>185.3845062255859</v>
+        <v>185.384521484375</v>
       </c>
       <c r="C744" t="n">
-        <v>189.7181637973264</v>
+        <v>189.7181794128139</v>
       </c>
       <c r="D744" t="n">
-        <v>183.6991801889819</v>
+        <v>183.6991953090537</v>
       </c>
       <c r="E744" t="n">
-        <v>186.5882999955138</v>
+        <v>186.5883153533858</v>
       </c>
       <c r="F744" t="n">
         <v>1413865</v>
@@ -15312,16 +15312,16 @@
         <v>44047</v>
       </c>
       <c r="B745" t="n">
-        <v>182.9768981933594</v>
+        <v>182.9769134521484</v>
       </c>
       <c r="C745" t="n">
-        <v>193.0887803025982</v>
+        <v>193.0887964046362</v>
       </c>
       <c r="D745" t="n">
-        <v>179.36551699674</v>
+        <v>179.3655319543691</v>
       </c>
       <c r="E745" t="n">
-        <v>183.4584156862419</v>
+        <v>183.4584309851857</v>
       </c>
       <c r="F745" t="n">
         <v>1479244</v>
@@ -15332,16 +15332,16 @@
         <v>44048</v>
       </c>
       <c r="B746" t="n">
-        <v>181.2916107177734</v>
+        <v>181.2915954589844</v>
       </c>
       <c r="C746" t="n">
-        <v>186.588318592064</v>
+        <v>186.5883028874663</v>
       </c>
       <c r="D746" t="n">
-        <v>180.5693343838302</v>
+        <v>180.569319185833</v>
       </c>
       <c r="E746" t="n">
-        <v>185.3845247021585</v>
+        <v>185.3845090988807</v>
       </c>
       <c r="F746" t="n">
         <v>872716</v>
@@ -15392,16 +15392,16 @@
         <v>44053</v>
       </c>
       <c r="B749" t="n">
-        <v>184.1806945800781</v>
+        <v>184.1807098388672</v>
       </c>
       <c r="C749" t="n">
-        <v>188.5143668371852</v>
+        <v>188.5143824550053</v>
       </c>
       <c r="D749" t="n">
-        <v>182.4953833306994</v>
+        <v>182.4953984498658</v>
       </c>
       <c r="E749" t="n">
-        <v>188.5143668371852</v>
+        <v>188.5143824550053</v>
       </c>
       <c r="F749" t="n">
         <v>940546</v>
@@ -15412,16 +15412,16 @@
         <v>44054</v>
       </c>
       <c r="B750" t="n">
-        <v>195.255615234375</v>
+        <v>195.2556304931641</v>
       </c>
       <c r="C750" t="n">
-        <v>200.0708050751437</v>
+        <v>200.0708207102291</v>
       </c>
       <c r="D750" t="n">
-        <v>184.4214565410266</v>
+        <v>184.4214709531504</v>
       </c>
       <c r="E750" t="n">
-        <v>185.8660238243507</v>
+        <v>185.8660383493642</v>
       </c>
       <c r="F750" t="n">
         <v>2032416</v>
@@ -15432,16 +15432,16 @@
         <v>44055</v>
       </c>
       <c r="B751" t="n">
-        <v>188.5143585205078</v>
+        <v>188.5143737792969</v>
       </c>
       <c r="C751" t="n">
-        <v>199.5892752865381</v>
+        <v>199.5892914417565</v>
       </c>
       <c r="D751" t="n">
-        <v>186.5882886061902</v>
+        <v>186.5883037090787</v>
       </c>
       <c r="E751" t="n">
-        <v>197.4224466329308</v>
+        <v>197.4224626127611</v>
       </c>
       <c r="F751" t="n">
         <v>1657962</v>
@@ -15452,16 +15452,16 @@
         <v>44056</v>
       </c>
       <c r="B752" t="n">
-        <v>184.9029846191406</v>
+        <v>184.9029998779297</v>
       </c>
       <c r="C752" t="n">
-        <v>195.7371283083471</v>
+        <v>195.7371444612045</v>
       </c>
       <c r="D752" t="n">
-        <v>183.9399348658399</v>
+        <v>183.9399500451549</v>
       </c>
       <c r="E752" t="n">
-        <v>189.7181595921213</v>
+        <v>189.7181752482741</v>
       </c>
       <c r="F752" t="n">
         <v>1407609</v>
@@ -45052,7 +45052,7 @@
         <v>46232</v>
       </c>
       <c r="B2232" t="n">
-        <v>53.31</v>
+        <v>53.32</v>
       </c>
       <c r="C2232" t="n">
         <v>53.67</v>
@@ -45064,7 +45064,7 @@
         <v>53.61</v>
       </c>
       <c r="F2232" t="n">
-        <v>358500</v>
+        <v>461000</v>
       </c>
     </row>
   </sheetData>
